--- a/Financial Analysis/SPOT.xlsx
+++ b/Financial Analysis/SPOT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045B089C-5A46-4350-8256-105444574747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C4EFDB-3308-45F4-9AF8-505EAB2F8B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -217,10 +217,10 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
-  </si>
-  <si>
     <t>Q125 6K</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -750,14 +750,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>573.16999999999996</v>
+        <v>658.88</v>
       </c>
       <c r="E3" s="12">
-        <v>45777</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="12">
         <v>45861</v>
@@ -771,7 +771,7 @@
         <v>204.5</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -780,7 +780,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>117213.26499999998</v>
+        <v>134740.96</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -831,7 +831,7 @@
       </c>
       <c r="D10" s="2">
         <f>D5-D9</f>
-        <v>107875.76499999998</v>
+        <v>125403.45999999999</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="AQ26" s="3">
         <f>Main!D3</f>
-        <v>573.16999999999996</v>
+        <v>658.88</v>
       </c>
     </row>
     <row r="27" spans="2:43" x14ac:dyDescent="0.3">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AQ27" s="10">
         <f>AQ25/AQ26-1</f>
-        <v>-0.20391486232627898</v>
+        <v>-0.30747310836503361</v>
       </c>
     </row>
     <row r="28" spans="2:43" x14ac:dyDescent="0.3">
@@ -4522,7 +4522,7 @@
         <v>57</v>
       </c>
       <c r="AQ28" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SPOT.xlsx
+++ b/Financial Analysis/SPOT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C4EFDB-3308-45F4-9AF8-505EAB2F8B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB69B04C-5923-4348-86A5-7E31FF12AF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>SPOT</t>
   </si>
@@ -217,10 +217,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Q125 6K</t>
-  </si>
-  <si>
-    <t>Overvalued</t>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -324,13 +321,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -348,7 +345,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12169140" y="7620"/>
+          <a:off x="12778740" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -750,17 +747,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>658.88</v>
+        <v>707.19</v>
       </c>
       <c r="E3" s="12">
-        <v>45804</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45918</v>
       </c>
       <c r="G3" s="12">
-        <v>45861</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -768,10 +765,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -780,7 +777,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>134740.96</v>
+        <v>145256.826</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -788,11 +785,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>5019+2894+1958</f>
-        <v>9871</v>
+        <f>5161+3183+2417</f>
+        <v>10761</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -800,11 +797,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>1654</f>
-        <v>1654</v>
+        <f>1929</f>
+        <v>1929</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -813,7 +810,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>8217</v>
+        <v>8832</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -822,7 +819,7 @@
       </c>
       <c r="D9" s="2">
         <f>D8/D15</f>
-        <v>9337.5</v>
+        <v>10036.363636363636</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
@@ -831,7 +828,7 @@
       </c>
       <c r="D10" s="2">
         <f>D5-D9</f>
-        <v>125403.45999999999</v>
+        <v>135220.46236363635</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -855,7 +852,7 @@
     <col min="2" max="2" width="17.109375" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
     <col min="42" max="42" width="13.6640625" customWidth="1"/>
-    <col min="43" max="43" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:149" x14ac:dyDescent="0.3">
@@ -1028,16 +1025,15 @@
         <v>4190</v>
       </c>
       <c r="T3" s="7">
-        <f t="shared" ref="T3:U3" si="0">P3*1.15</f>
-        <v>4378.0499999999993</v>
+        <v>4193</v>
       </c>
       <c r="U3" s="7">
-        <f t="shared" si="0"/>
-        <v>4586.2</v>
+        <f>Q3*1.09</f>
+        <v>4346.92</v>
       </c>
       <c r="V3" s="7">
-        <f>R3*1.12</f>
-        <v>4751.0400000000009</v>
+        <f>R3*1.08</f>
+        <v>4581.3600000000006</v>
       </c>
       <c r="Z3" s="7">
         <f>SUM(C3:F3)</f>
@@ -1057,47 +1053,47 @@
       </c>
       <c r="AD3" s="7">
         <f>SUM(S3:V3)</f>
-        <v>17905.29</v>
+        <v>17311.28</v>
       </c>
       <c r="AE3" s="7">
-        <f>AD3*1.12</f>
-        <v>20053.924800000004</v>
+        <f>AD3*1.09</f>
+        <v>18869.2952</v>
       </c>
       <c r="AF3" s="7">
-        <f>AE3*1.1</f>
-        <v>22059.317280000007</v>
+        <f>AE3*1.08</f>
+        <v>20378.838816000003</v>
       </c>
       <c r="AG3" s="7">
-        <f>AF3*1.09</f>
-        <v>24044.65583520001</v>
+        <f>AF3*1.07</f>
+        <v>21805.357533120005</v>
       </c>
       <c r="AH3" s="7">
-        <f>AG3*1.08</f>
-        <v>25968.228302016014</v>
+        <f>AG3*1.06</f>
+        <v>23113.678985107206</v>
       </c>
       <c r="AI3" s="7">
-        <f>AH3*1.07</f>
-        <v>27786.004283157137</v>
+        <f>AH3*1.05</f>
+        <v>24269.362934362569</v>
       </c>
       <c r="AJ3" s="7">
-        <f>AI3*1.06</f>
-        <v>29453.164540146568</v>
+        <f t="shared" ref="AJ3" si="0">AI3*1.05</f>
+        <v>25482.831081080698</v>
       </c>
       <c r="AK3" s="7">
-        <f>AJ3*1.05</f>
-        <v>30925.822767153899</v>
+        <f>AJ3*1.04</f>
+        <v>26502.144324323926</v>
       </c>
       <c r="AL3" s="7">
-        <f t="shared" ref="AL3:AN3" si="1">AK3*1.05</f>
-        <v>32472.113905511596</v>
+        <f>AK3*1.03</f>
+        <v>27297.208654053644</v>
       </c>
       <c r="AM3" s="7">
-        <f t="shared" si="1"/>
-        <v>34095.719600787175</v>
+        <f>AL3*1.02</f>
+        <v>27843.152827134716</v>
       </c>
       <c r="AN3" s="7">
-        <f t="shared" si="1"/>
-        <v>35800.505580826539</v>
+        <f>AM3*1.02</f>
+        <v>28400.01588367741</v>
       </c>
     </row>
     <row r="4" spans="1:149" x14ac:dyDescent="0.3">
@@ -1156,16 +1152,15 @@
         <v>2864</v>
       </c>
       <c r="T4" s="2">
-        <f t="shared" ref="T4:V4" si="2">T3-T5</f>
-        <v>2977.0739999999996</v>
+        <v>2873</v>
       </c>
       <c r="U4" s="2">
-        <f t="shared" si="2"/>
-        <v>3072.7539999999999</v>
+        <f t="shared" ref="U4:V4" si="1">U3-U5</f>
+        <v>2912.4364</v>
       </c>
       <c r="V4" s="2">
-        <f t="shared" si="2"/>
-        <v>3135.6864000000005</v>
+        <f t="shared" si="1"/>
+        <v>3023.6976000000004</v>
       </c>
       <c r="Z4" s="2">
         <f>SUM(C4:F4)</f>
@@ -1185,47 +1180,47 @@
       </c>
       <c r="AD4" s="2">
         <f>SUM(S4:V4)</f>
-        <v>12049.5144</v>
+        <v>11673.134000000002</v>
       </c>
       <c r="AE4" s="2">
         <f>AE3-AE5</f>
-        <v>13035.051120000004</v>
+        <v>12453.734832</v>
       </c>
       <c r="AF4" s="2">
-        <f t="shared" ref="AF4:AN4" si="3">AF3-AF5</f>
-        <v>14117.963059200005</v>
+        <f t="shared" ref="AF4:AN4" si="2">AF3-AF5</f>
+        <v>13246.245230400003</v>
       </c>
       <c r="AG4" s="2">
-        <f t="shared" si="3"/>
-        <v>15148.133176176007</v>
+        <f t="shared" si="2"/>
+        <v>13955.428821196803</v>
       </c>
       <c r="AH4" s="2">
-        <f t="shared" si="3"/>
-        <v>16100.301547249928</v>
+        <f t="shared" si="2"/>
+        <v>14792.754550468613</v>
       </c>
       <c r="AI4" s="2">
-        <f t="shared" si="3"/>
-        <v>16949.462612725853</v>
+        <f t="shared" si="2"/>
+        <v>15532.392277992045</v>
       </c>
       <c r="AJ4" s="2">
-        <f t="shared" si="3"/>
-        <v>17671.89872408794</v>
+        <f t="shared" si="2"/>
+        <v>16309.011891891647</v>
       </c>
       <c r="AK4" s="2">
-        <f t="shared" si="3"/>
-        <v>18555.493660292341</v>
+        <f t="shared" si="2"/>
+        <v>16961.372367567314</v>
       </c>
       <c r="AL4" s="2">
-        <f t="shared" si="3"/>
-        <v>19483.268343306958</v>
+        <f t="shared" si="2"/>
+        <v>17470.213538594333</v>
       </c>
       <c r="AM4" s="2">
-        <f t="shared" si="3"/>
-        <v>20457.431760472304</v>
+        <f t="shared" si="2"/>
+        <v>17819.617809366217</v>
       </c>
       <c r="AN4" s="2">
-        <f t="shared" si="3"/>
-        <v>21480.303348495923</v>
+        <f t="shared" si="2"/>
+        <v>18176.01016555354</v>
       </c>
     </row>
     <row r="5" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1234,84 +1229,84 @@
         <v>15</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:S5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:T5" si="3">C3-C4</f>
         <v>548</v>
       </c>
       <c r="D5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>663</v>
       </c>
       <c r="E5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>668</v>
       </c>
       <c r="F5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>712</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>671</v>
       </c>
       <c r="H5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>704</v>
       </c>
       <c r="I5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>801</v>
       </c>
       <c r="K5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>766</v>
       </c>
       <c r="L5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>766</v>
       </c>
       <c r="M5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>885</v>
       </c>
       <c r="N5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>980</v>
       </c>
       <c r="O5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1004</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1112</v>
       </c>
       <c r="Q5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1240</v>
       </c>
       <c r="R5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1368</v>
       </c>
       <c r="S5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1326</v>
       </c>
       <c r="T5" s="7">
-        <f t="shared" ref="T5" si="5">T3*0.32</f>
-        <v>1400.9759999999999</v>
+        <f t="shared" si="3"/>
+        <v>1320</v>
       </c>
       <c r="U5" s="7">
         <f>U3*0.33</f>
-        <v>1513.4459999999999</v>
+        <v>1434.4836</v>
       </c>
       <c r="V5" s="7">
         <f>V3*0.34</f>
-        <v>1615.3536000000004</v>
+        <v>1557.6624000000004</v>
       </c>
       <c r="Z5" s="7">
         <f>Z3-Z4</f>
@@ -1331,47 +1326,47 @@
       </c>
       <c r="AD5" s="7">
         <f>AD3-AD4</f>
-        <v>5855.7756000000008</v>
+        <v>5638.145999999997</v>
       </c>
       <c r="AE5" s="7">
-        <f>AE3*0.35</f>
-        <v>7018.8736800000015</v>
+        <f>AE3*0.34</f>
+        <v>6415.5603680000004</v>
       </c>
       <c r="AF5" s="7">
-        <f>AF3*0.36</f>
-        <v>7941.3542208000017</v>
+        <f>AF3*0.35</f>
+        <v>7132.5935856000006</v>
       </c>
       <c r="AG5" s="7">
-        <f>AG3*0.37</f>
-        <v>8896.5226590240036</v>
+        <f>AG3*0.36</f>
+        <v>7849.9287119232013</v>
       </c>
       <c r="AH5" s="7">
-        <f>AH3*0.38</f>
-        <v>9867.9267547660857</v>
+        <f t="shared" ref="AH5:AN5" si="4">AH3*0.36</f>
+        <v>8320.9244346385931</v>
       </c>
       <c r="AI5" s="7">
-        <f>AI3*0.39</f>
-        <v>10836.541670431285</v>
+        <f t="shared" si="4"/>
+        <v>8736.970656370524</v>
       </c>
       <c r="AJ5" s="7">
-        <f>AJ3*0.4</f>
-        <v>11781.265816058629</v>
+        <f t="shared" si="4"/>
+        <v>9173.819189189051</v>
       </c>
       <c r="AK5" s="7">
-        <f t="shared" ref="AK5:AN5" si="6">AK3*0.4</f>
-        <v>12370.32910686156</v>
+        <f t="shared" si="4"/>
+        <v>9540.7719567566128</v>
       </c>
       <c r="AL5" s="7">
-        <f t="shared" si="6"/>
-        <v>12988.845562204639</v>
+        <f t="shared" si="4"/>
+        <v>9826.9951154593109</v>
       </c>
       <c r="AM5" s="7">
-        <f t="shared" si="6"/>
-        <v>13638.287840314872</v>
+        <f t="shared" si="4"/>
+        <v>10023.535017768498</v>
       </c>
       <c r="AN5" s="7">
-        <f t="shared" si="6"/>
-        <v>14320.202232330616</v>
+        <f t="shared" si="4"/>
+        <v>10224.005718123868</v>
       </c>
     </row>
     <row r="6" spans="1:149" x14ac:dyDescent="0.3">
@@ -1430,16 +1425,15 @@
         <v>379</v>
       </c>
       <c r="T6" s="2">
-        <f t="shared" ref="T6:V6" si="7">P6*1.02</f>
-        <v>386.58</v>
+        <v>415</v>
       </c>
       <c r="U6" s="2">
-        <f t="shared" si="7"/>
-        <v>348.84000000000003</v>
+        <f>Q6*1.1</f>
+        <v>376.20000000000005</v>
       </c>
       <c r="V6" s="2">
-        <f t="shared" si="7"/>
-        <v>383.52</v>
+        <f>R6*1.12</f>
+        <v>421.12000000000006</v>
       </c>
       <c r="Z6" s="2">
         <f>SUM(C6:F6)</f>
@@ -1459,47 +1453,47 @@
       </c>
       <c r="AD6" s="2">
         <f>SUM(S6:V6)</f>
-        <v>1497.94</v>
+        <v>1591.3200000000002</v>
       </c>
       <c r="AE6" s="2">
-        <f>AD6*1.02</f>
-        <v>1527.8988000000002</v>
+        <f>AD6*1.04</f>
+        <v>1654.9728000000002</v>
       </c>
       <c r="AF6" s="2">
-        <f t="shared" ref="AF6:AN6" si="8">AE6*1.02</f>
-        <v>1558.4567760000002</v>
+        <f t="shared" ref="AF6:AN6" si="5">AE6*1.02</f>
+        <v>1688.0722560000004</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" si="8"/>
-        <v>1589.6259115200003</v>
+        <f t="shared" si="5"/>
+        <v>1721.8337011200003</v>
       </c>
       <c r="AH6" s="2">
-        <f t="shared" si="8"/>
-        <v>1621.4184297504003</v>
+        <f t="shared" si="5"/>
+        <v>1756.2703751424003</v>
       </c>
       <c r="AI6" s="2">
-        <f t="shared" si="8"/>
-        <v>1653.8467983454084</v>
+        <f t="shared" si="5"/>
+        <v>1791.3957826452483</v>
       </c>
       <c r="AJ6" s="2">
-        <f t="shared" si="8"/>
-        <v>1686.9237343123166</v>
+        <f t="shared" si="5"/>
+        <v>1827.2236982981533</v>
       </c>
       <c r="AK6" s="2">
-        <f t="shared" si="8"/>
-        <v>1720.6622089985628</v>
+        <f t="shared" si="5"/>
+        <v>1863.7681722641164</v>
       </c>
       <c r="AL6" s="2">
-        <f t="shared" si="8"/>
-        <v>1755.0754531785342</v>
+        <f t="shared" si="5"/>
+        <v>1901.0435357093988</v>
       </c>
       <c r="AM6" s="2">
-        <f t="shared" si="8"/>
-        <v>1790.176962242105</v>
+        <f t="shared" si="5"/>
+        <v>1939.0644064235869</v>
       </c>
       <c r="AN6" s="2">
-        <f t="shared" si="8"/>
-        <v>1825.9805014869471</v>
+        <f t="shared" si="5"/>
+        <v>1977.8456945520586</v>
       </c>
     </row>
     <row r="7" spans="1:149" x14ac:dyDescent="0.3">
@@ -1558,16 +1552,15 @@
         <v>314</v>
       </c>
       <c r="T7" s="2">
-        <f>T3*0.075</f>
-        <v>328.35374999999993</v>
+        <v>364</v>
       </c>
       <c r="U7" s="2">
-        <f t="shared" ref="U7:V7" si="9">U3*0.075</f>
-        <v>343.96499999999997</v>
+        <f>U3*0.09</f>
+        <v>391.22280000000001</v>
       </c>
       <c r="V7" s="2">
-        <f t="shared" si="9"/>
-        <v>356.32800000000003</v>
+        <f>V3*0.09</f>
+        <v>412.32240000000002</v>
       </c>
       <c r="Z7" s="2">
         <f>SUM(C7:F7)</f>
@@ -1587,47 +1580,47 @@
       </c>
       <c r="AD7" s="2">
         <f>SUM(S7:V7)</f>
-        <v>1342.6467499999999</v>
+        <v>1481.5452</v>
       </c>
       <c r="AE7" s="2">
-        <f>AE3*0.07</f>
-        <v>1403.7747360000005</v>
+        <f>AE3*0.09</f>
+        <v>1698.236568</v>
       </c>
       <c r="AF7" s="2">
-        <f t="shared" ref="AF7:AN7" si="10">AF3*0.07</f>
-        <v>1544.1522096000006</v>
+        <f t="shared" ref="AF7:AN7" si="6">AF3*0.09</f>
+        <v>1834.0954934400002</v>
       </c>
       <c r="AG7" s="2">
-        <f t="shared" si="10"/>
-        <v>1683.125908464001</v>
+        <f t="shared" si="6"/>
+        <v>1962.4821779808003</v>
       </c>
       <c r="AH7" s="2">
-        <f t="shared" si="10"/>
-        <v>1817.7759811411211</v>
+        <f t="shared" si="6"/>
+        <v>2080.2311086596483</v>
       </c>
       <c r="AI7" s="2">
-        <f t="shared" si="10"/>
-        <v>1945.0202998209998</v>
+        <f t="shared" si="6"/>
+        <v>2184.242664092631</v>
       </c>
       <c r="AJ7" s="2">
-        <f t="shared" si="10"/>
-        <v>2061.7215178102601</v>
+        <f t="shared" si="6"/>
+        <v>2293.4547972972628</v>
       </c>
       <c r="AK7" s="2">
-        <f t="shared" si="10"/>
-        <v>2164.8075937007729</v>
+        <f t="shared" si="6"/>
+        <v>2385.1929891891532</v>
       </c>
       <c r="AL7" s="2">
-        <f t="shared" si="10"/>
-        <v>2273.0479733858119</v>
+        <f t="shared" si="6"/>
+        <v>2456.7487788648277</v>
       </c>
       <c r="AM7" s="2">
-        <f t="shared" si="10"/>
-        <v>2386.7003720551024</v>
+        <f t="shared" si="6"/>
+        <v>2505.8837544421244</v>
       </c>
       <c r="AN7" s="2">
-        <f t="shared" si="10"/>
-        <v>2506.035390657858</v>
+        <f t="shared" si="6"/>
+        <v>2556.001429530967</v>
       </c>
     </row>
     <row r="8" spans="1:149" x14ac:dyDescent="0.3">
@@ -1686,16 +1679,15 @@
         <v>124</v>
       </c>
       <c r="T8" s="2">
-        <f t="shared" ref="T8:V8" si="11">P8*1.02</f>
-        <v>126.48</v>
+        <v>135</v>
       </c>
       <c r="U8" s="2">
-        <f t="shared" si="11"/>
-        <v>114.24000000000001</v>
+        <f>Q8*1.08</f>
+        <v>120.96000000000001</v>
       </c>
       <c r="V8" s="2">
-        <f t="shared" si="11"/>
-        <v>124.44</v>
+        <f>R8*1.14</f>
+        <v>139.07999999999998</v>
       </c>
       <c r="Z8" s="2">
         <f>SUM(C8:F8)</f>
@@ -1715,47 +1707,47 @@
       </c>
       <c r="AD8" s="2">
         <f>SUM(S8:V8)</f>
-        <v>489.16</v>
+        <v>519.04</v>
       </c>
       <c r="AE8" s="2">
-        <f>AD8*1.02</f>
-        <v>498.94320000000005</v>
+        <f>AD8*1.05</f>
+        <v>544.99199999999996</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" ref="AF8:AH8" si="12">AE8*1.02</f>
-        <v>508.92206400000003</v>
+        <f>AE8*1.03</f>
+        <v>561.34176000000002</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" si="12"/>
-        <v>519.10050527999999</v>
+        <f t="shared" ref="AG8:AH8" si="7">AF8*1.02</f>
+        <v>572.5685952</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" si="12"/>
-        <v>529.48251538559998</v>
+        <f t="shared" si="7"/>
+        <v>584.01996710399999</v>
       </c>
       <c r="AI8" s="2">
         <f>AH8*1.01</f>
-        <v>534.77734053945596</v>
+        <v>589.86016677503994</v>
       </c>
       <c r="AJ8" s="2">
-        <f t="shared" ref="AJ8:AN8" si="13">AI8*1.01</f>
-        <v>540.12511394485057</v>
+        <f t="shared" ref="AJ8:AN8" si="8">AI8*1.01</f>
+        <v>595.75876844279037</v>
       </c>
       <c r="AK8" s="2">
-        <f t="shared" si="13"/>
-        <v>545.52636508429907</v>
+        <f t="shared" si="8"/>
+        <v>601.71635612721832</v>
       </c>
       <c r="AL8" s="2">
-        <f t="shared" si="13"/>
-        <v>550.98162873514207</v>
+        <f t="shared" si="8"/>
+        <v>607.73351968849056</v>
       </c>
       <c r="AM8" s="2">
-        <f t="shared" si="13"/>
-        <v>556.49144502249351</v>
+        <f t="shared" si="8"/>
+        <v>613.81085488537542</v>
       </c>
       <c r="AN8" s="2">
-        <f t="shared" si="13"/>
-        <v>562.05635947271844</v>
+        <f t="shared" si="8"/>
+        <v>619.9489634342292</v>
       </c>
     </row>
     <row r="9" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1764,84 +1756,84 @@
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:P9" si="14">C5-SUM(C6:C8)</f>
+        <f t="shared" ref="C9:P9" si="9">C5-SUM(C6:C8)</f>
         <v>14</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-7</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-194</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-228</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-231</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-156</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-247</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>-75</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>168</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>266</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" ref="Q9:V9" si="15">Q5-SUM(Q6:Q8)</f>
+        <f t="shared" ref="Q9:V9" si="10">Q5-SUM(Q6:Q8)</f>
         <v>454</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>477</v>
       </c>
       <c r="S9" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>509</v>
       </c>
       <c r="T9" s="7">
-        <f t="shared" si="15"/>
-        <v>559.56224999999995</v>
+        <f t="shared" si="10"/>
+        <v>406</v>
       </c>
       <c r="U9" s="7">
-        <f t="shared" si="15"/>
-        <v>706.40099999999984</v>
+        <f t="shared" si="10"/>
+        <v>546.10079999999994</v>
       </c>
       <c r="V9" s="7">
-        <f t="shared" si="15"/>
-        <v>751.06560000000036</v>
+        <f t="shared" si="10"/>
+        <v>585.14000000000033</v>
       </c>
       <c r="Z9" s="7">
         <f>Z5-SUM(Z6:Z8)</f>
@@ -1861,47 +1853,47 @@
       </c>
       <c r="AD9" s="7">
         <f>AD5-SUM(AD6:AD8)</f>
-        <v>2526.0288500000011</v>
+        <v>2046.2407999999969</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" ref="AE9:AN9" si="16">AE5-SUM(AE6:AE8)</f>
-        <v>3588.2569440000007</v>
+        <f t="shared" ref="AE9:AN9" si="11">AE5-SUM(AE6:AE8)</f>
+        <v>2517.3590000000004</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="16"/>
-        <v>4329.8231712000015</v>
+        <f t="shared" si="11"/>
+        <v>3049.0840761600002</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="16"/>
-        <v>5104.670333760002</v>
+        <f t="shared" si="11"/>
+        <v>3593.0442376224</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" si="16"/>
-        <v>5899.2498284889643</v>
+        <f t="shared" si="11"/>
+        <v>3900.4029837325443</v>
       </c>
       <c r="AI9" s="7">
-        <f t="shared" si="16"/>
-        <v>6702.8972317254211</v>
+        <f t="shared" si="11"/>
+        <v>4171.4720428576047</v>
       </c>
       <c r="AJ9" s="7">
-        <f t="shared" si="16"/>
-        <v>7492.4954499912019</v>
+        <f t="shared" si="11"/>
+        <v>4457.3819251508448</v>
       </c>
       <c r="AK9" s="7">
-        <f t="shared" si="16"/>
-        <v>7939.3329390779254</v>
+        <f t="shared" si="11"/>
+        <v>4690.094439176125</v>
       </c>
       <c r="AL9" s="7">
-        <f t="shared" si="16"/>
-        <v>8409.7405069051492</v>
+        <f t="shared" si="11"/>
+        <v>4861.4692811965942</v>
       </c>
       <c r="AM9" s="7">
-        <f t="shared" si="16"/>
-        <v>8904.9190609951711</v>
+        <f t="shared" si="11"/>
+        <v>4964.776002017411</v>
       </c>
       <c r="AN9" s="7">
-        <f t="shared" si="16"/>
-        <v>9426.1299807130927</v>
+        <f t="shared" si="11"/>
+        <v>5070.2096306066132</v>
       </c>
     </row>
     <row r="10" spans="1:149" x14ac:dyDescent="0.3">
@@ -1960,15 +1952,14 @@
         <v>-71</v>
       </c>
       <c r="T10" s="2">
-        <f t="shared" ref="T10:V11" si="17">P10*1.02</f>
-        <v>-77.52</v>
+        <v>-89</v>
       </c>
       <c r="U10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="U10:V11" si="12">Q10*1.02</f>
         <v>-67.320000000000007</v>
       </c>
       <c r="V10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>-129.54</v>
       </c>
       <c r="Z10" s="2">
@@ -1989,47 +1980,47 @@
       </c>
       <c r="AD10" s="2">
         <f>SUM(S10:V10)</f>
-        <v>-345.38</v>
+        <v>-356.86</v>
       </c>
       <c r="AE10" s="2">
         <f>AD10*1.03</f>
-        <v>-355.7414</v>
+        <v>-367.56580000000002</v>
       </c>
       <c r="AF10" s="2">
-        <f t="shared" ref="AF10:AN10" si="18">AE10*1.03</f>
-        <v>-366.41364199999998</v>
+        <f t="shared" ref="AF10:AN10" si="13">AE10*1.03</f>
+        <v>-378.59277400000002</v>
       </c>
       <c r="AG10" s="2">
-        <f t="shared" si="18"/>
-        <v>-377.40605125999997</v>
+        <f t="shared" si="13"/>
+        <v>-389.95055722000001</v>
       </c>
       <c r="AH10" s="2">
-        <f t="shared" si="18"/>
-        <v>-388.72823279779999</v>
+        <f t="shared" si="13"/>
+        <v>-401.64907393660002</v>
       </c>
       <c r="AI10" s="2">
-        <f t="shared" si="18"/>
-        <v>-400.39007978173402</v>
+        <f t="shared" si="13"/>
+        <v>-413.69854615469802</v>
       </c>
       <c r="AJ10" s="2">
-        <f t="shared" si="18"/>
-        <v>-412.40178217518604</v>
+        <f t="shared" si="13"/>
+        <v>-426.10950253933896</v>
       </c>
       <c r="AK10" s="2">
-        <f t="shared" si="18"/>
-        <v>-424.77383564044163</v>
+        <f t="shared" si="13"/>
+        <v>-438.89278761551913</v>
       </c>
       <c r="AL10" s="2">
-        <f t="shared" si="18"/>
-        <v>-437.51705070965488</v>
+        <f t="shared" si="13"/>
+        <v>-452.05957124398469</v>
       </c>
       <c r="AM10" s="2">
-        <f t="shared" si="18"/>
-        <v>-450.64256223094452</v>
+        <f t="shared" si="13"/>
+        <v>-465.62135838130422</v>
       </c>
       <c r="AN10" s="2">
-        <f t="shared" si="18"/>
-        <v>-464.16183909787287</v>
+        <f t="shared" si="13"/>
+        <v>-479.58999913274334</v>
       </c>
     </row>
     <row r="11" spans="1:149" x14ac:dyDescent="0.3">
@@ -2088,15 +2079,14 @@
         <v>252</v>
       </c>
       <c r="T11" s="2">
-        <f t="shared" si="17"/>
-        <v>73.44</v>
+        <v>447</v>
       </c>
       <c r="U11" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>124.44</v>
       </c>
       <c r="V11" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>107.10000000000001</v>
       </c>
       <c r="Z11" s="2">
@@ -2117,47 +2107,47 @@
       </c>
       <c r="AD11" s="2">
         <f>SUM(S11:V11)</f>
-        <v>556.98</v>
+        <v>930.54000000000008</v>
       </c>
       <c r="AE11" s="2">
-        <f t="shared" ref="AE11:AN11" si="19">AD11*1.01</f>
-        <v>562.5498</v>
+        <f t="shared" ref="AE11:AN11" si="14">AD11*1.01</f>
+        <v>939.84540000000004</v>
       </c>
       <c r="AF11" s="2">
-        <f t="shared" si="19"/>
-        <v>568.175298</v>
+        <f t="shared" si="14"/>
+        <v>949.24385400000006</v>
       </c>
       <c r="AG11" s="2">
-        <f t="shared" si="19"/>
-        <v>573.85705098000005</v>
+        <f t="shared" si="14"/>
+        <v>958.73629254000002</v>
       </c>
       <c r="AH11" s="2">
-        <f t="shared" si="19"/>
-        <v>579.59562148980001</v>
+        <f t="shared" si="14"/>
+        <v>968.32365546540007</v>
       </c>
       <c r="AI11" s="2">
-        <f t="shared" si="19"/>
-        <v>585.39157770469797</v>
+        <f t="shared" si="14"/>
+        <v>978.00689202005412</v>
       </c>
       <c r="AJ11" s="2">
-        <f t="shared" si="19"/>
-        <v>591.24549348174492</v>
+        <f t="shared" si="14"/>
+        <v>987.78696094025463</v>
       </c>
       <c r="AK11" s="2">
-        <f t="shared" si="19"/>
-        <v>597.15794841656236</v>
+        <f t="shared" si="14"/>
+        <v>997.66483054965715</v>
       </c>
       <c r="AL11" s="2">
-        <f t="shared" si="19"/>
-        <v>603.12952790072802</v>
+        <f t="shared" si="14"/>
+        <v>1007.6414788551538</v>
       </c>
       <c r="AM11" s="2">
-        <f t="shared" si="19"/>
-        <v>609.1608231797353</v>
+        <f t="shared" si="14"/>
+        <v>1017.7178936437053</v>
       </c>
       <c r="AN11" s="2">
-        <f t="shared" si="19"/>
-        <v>615.25243141153271</v>
+        <f t="shared" si="14"/>
+        <v>1027.8950725801424</v>
       </c>
     </row>
     <row r="12" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2166,84 +2156,84 @@
         <v>22</v>
       </c>
       <c r="C12" s="7">
-        <f t="shared" ref="C12:P12" si="20">C9-C10-C11</f>
+        <f t="shared" ref="C12:P12" si="15">C9-C10-C11</f>
         <v>87</v>
       </c>
       <c r="D12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
       <c r="E12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>162</v>
       </c>
       <c r="F12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>-8</v>
       </c>
       <c r="G12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>155</v>
       </c>
       <c r="H12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>-90</v>
       </c>
       <c r="I12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>-144</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>-291</v>
       </c>
       <c r="K12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>-206</v>
       </c>
       <c r="L12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>-241</v>
       </c>
       <c r="M12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>73</v>
       </c>
       <c r="N12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>-131</v>
       </c>
       <c r="O12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>174</v>
       </c>
       <c r="P12" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>270</v>
       </c>
       <c r="Q12" s="7">
-        <f t="shared" ref="Q12:V12" si="21">Q9-Q10-Q11</f>
+        <f t="shared" ref="Q12:V12" si="16">Q9-Q10-Q11</f>
         <v>398</v>
       </c>
       <c r="R12" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>499</v>
       </c>
       <c r="S12" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>328</v>
       </c>
       <c r="T12" s="7">
-        <f t="shared" si="21"/>
-        <v>563.64224999999988</v>
+        <f t="shared" si="16"/>
+        <v>48</v>
       </c>
       <c r="U12" s="7">
-        <f t="shared" si="21"/>
-        <v>649.28099999999995</v>
+        <f t="shared" si="16"/>
+        <v>488.98079999999999</v>
       </c>
       <c r="V12" s="7">
-        <f t="shared" si="21"/>
-        <v>773.5056000000003</v>
+        <f t="shared" si="16"/>
+        <v>607.58000000000027</v>
       </c>
       <c r="Z12" s="7">
         <f>Z9-Z10-Z11</f>
@@ -2263,47 +2253,47 @@
       </c>
       <c r="AD12" s="7">
         <f>AD9-AD10-AD11</f>
-        <v>2314.4288500000011</v>
+        <v>1472.560799999997</v>
       </c>
       <c r="AE12" s="7">
-        <f t="shared" ref="AE12:AN12" si="22">AE9-AE10-AE11</f>
-        <v>3381.4485440000008</v>
+        <f t="shared" ref="AE12:AN12" si="17">AE9-AE10-AE11</f>
+        <v>1945.0794000000001</v>
       </c>
       <c r="AF12" s="7">
-        <f t="shared" si="22"/>
-        <v>4128.0615152000009</v>
+        <f t="shared" si="17"/>
+        <v>2478.4329961600006</v>
       </c>
       <c r="AG12" s="7">
-        <f t="shared" si="22"/>
-        <v>4908.2193340400017</v>
+        <f t="shared" si="17"/>
+        <v>3024.2585023024003</v>
       </c>
       <c r="AH12" s="7">
-        <f t="shared" si="22"/>
-        <v>5708.3824397969647</v>
+        <f t="shared" si="17"/>
+        <v>3333.7284022037443</v>
       </c>
       <c r="AI12" s="7">
-        <f t="shared" si="22"/>
-        <v>6517.8957338024575</v>
+        <f t="shared" si="17"/>
+        <v>3607.1636969922488</v>
       </c>
       <c r="AJ12" s="7">
-        <f t="shared" si="22"/>
-        <v>7313.6517386846426</v>
+        <f t="shared" si="17"/>
+        <v>3895.704466749929</v>
       </c>
       <c r="AK12" s="7">
-        <f t="shared" si="22"/>
-        <v>7766.9488263018056</v>
+        <f t="shared" si="17"/>
+        <v>4131.322396241987</v>
       </c>
       <c r="AL12" s="7">
-        <f t="shared" si="22"/>
-        <v>8244.1280297140765</v>
+        <f t="shared" si="17"/>
+        <v>4305.8873735854249</v>
       </c>
       <c r="AM12" s="7">
-        <f t="shared" si="22"/>
-        <v>8746.4008000463818</v>
+        <f t="shared" si="17"/>
+        <v>4412.6794667550093</v>
       </c>
       <c r="AN12" s="7">
-        <f t="shared" si="22"/>
-        <v>9275.0393883994329</v>
+        <f t="shared" si="17"/>
+        <v>4521.9045571592142</v>
       </c>
     </row>
     <row r="13" spans="1:149" x14ac:dyDescent="0.3">
@@ -2362,16 +2352,15 @@
         <v>103</v>
       </c>
       <c r="T13" s="2">
-        <f t="shared" ref="T13:V13" si="23">T12*0.25</f>
-        <v>140.91056249999997</v>
+        <v>134</v>
       </c>
       <c r="U13" s="2">
-        <f t="shared" si="23"/>
-        <v>162.32024999999999</v>
+        <f t="shared" ref="U13:V13" si="18">U12*0.25</f>
+        <v>122.2452</v>
       </c>
       <c r="V13" s="2">
-        <f t="shared" si="23"/>
-        <v>193.37640000000007</v>
+        <f t="shared" si="18"/>
+        <v>151.89500000000007</v>
       </c>
       <c r="Z13" s="2">
         <f>SUM(C13:F13)</f>
@@ -2391,47 +2380,47 @@
       </c>
       <c r="AD13" s="2">
         <f>SUM(S13:V13)</f>
-        <v>599.60721250000006</v>
+        <v>511.14020000000005</v>
       </c>
       <c r="AE13" s="2">
-        <f>AE12*0.2</f>
-        <v>676.2897088000002</v>
+        <f>AE12*0.25</f>
+        <v>486.26985000000002</v>
       </c>
       <c r="AF13" s="2">
-        <f t="shared" ref="AF13:AN13" si="24">AF12*0.2</f>
-        <v>825.61230304000026</v>
+        <f t="shared" ref="AF13:AN13" si="19">AF12*0.25</f>
+        <v>619.60824904000015</v>
       </c>
       <c r="AG13" s="2">
-        <f t="shared" si="24"/>
-        <v>981.64386680800044</v>
+        <f t="shared" si="19"/>
+        <v>756.06462557560008</v>
       </c>
       <c r="AH13" s="2">
-        <f t="shared" si="24"/>
-        <v>1141.6764879593929</v>
+        <f t="shared" si="19"/>
+        <v>833.43210055093607</v>
       </c>
       <c r="AI13" s="2">
-        <f t="shared" si="24"/>
-        <v>1303.5791467604915</v>
+        <f t="shared" si="19"/>
+        <v>901.7909242480622</v>
       </c>
       <c r="AJ13" s="2">
-        <f t="shared" si="24"/>
-        <v>1462.7303477369287</v>
+        <f t="shared" si="19"/>
+        <v>973.92611668748225</v>
       </c>
       <c r="AK13" s="2">
-        <f t="shared" si="24"/>
-        <v>1553.3897652603612</v>
+        <f t="shared" si="19"/>
+        <v>1032.8305990604968</v>
       </c>
       <c r="AL13" s="2">
-        <f t="shared" si="24"/>
-        <v>1648.8256059428154</v>
+        <f t="shared" si="19"/>
+        <v>1076.4718433963562</v>
       </c>
       <c r="AM13" s="2">
-        <f t="shared" si="24"/>
-        <v>1749.2801600092764</v>
+        <f t="shared" si="19"/>
+        <v>1103.1698666887523</v>
       </c>
       <c r="AN13" s="2">
-        <f t="shared" si="24"/>
-        <v>1855.0078776798866</v>
+        <f t="shared" si="19"/>
+        <v>1130.4761392898035</v>
       </c>
     </row>
     <row r="14" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2440,84 +2429,84 @@
         <v>24</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" ref="C14:P14" si="25">C12-C13</f>
+        <f t="shared" ref="C14:P14" si="20">C12-C13</f>
         <v>23</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-20</v>
       </c>
       <c r="E14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-39</v>
       </c>
       <c r="G14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>131</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-125</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-166</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-270</v>
       </c>
       <c r="K14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-225</v>
       </c>
       <c r="L14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-302</v>
       </c>
       <c r="M14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>65</v>
       </c>
       <c r="N14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>-70</v>
       </c>
       <c r="O14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>197</v>
       </c>
       <c r="P14" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>274</v>
       </c>
       <c r="Q14" s="7">
-        <f t="shared" ref="Q14:R14" si="26">Q12-Q13</f>
+        <f t="shared" ref="Q14:R14" si="21">Q12-Q13</f>
         <v>300</v>
       </c>
       <c r="R14" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="21"/>
         <v>367</v>
       </c>
       <c r="S14" s="7">
-        <f t="shared" ref="S14:V14" si="27">S12-S13</f>
+        <f t="shared" ref="S14:V14" si="22">S12-S13</f>
         <v>225</v>
       </c>
       <c r="T14" s="7">
-        <f t="shared" si="27"/>
-        <v>422.73168749999991</v>
+        <f t="shared" si="22"/>
+        <v>-86</v>
       </c>
       <c r="U14" s="7">
-        <f t="shared" si="27"/>
-        <v>486.96074999999996</v>
+        <f t="shared" si="22"/>
+        <v>366.73559999999998</v>
       </c>
       <c r="V14" s="7">
-        <f t="shared" si="27"/>
-        <v>580.1292000000002</v>
+        <f t="shared" si="22"/>
+        <v>455.68500000000017</v>
       </c>
       <c r="Z14" s="7">
         <f>Z12-Z13</f>
@@ -2537,483 +2526,483 @@
       </c>
       <c r="AD14" s="7">
         <f>AD12-AD13</f>
-        <v>1714.8216375000011</v>
+        <v>961.42059999999697</v>
       </c>
       <c r="AE14" s="7">
-        <f t="shared" ref="AE14:AN14" si="28">AE12-AE13</f>
-        <v>2705.1588352000008</v>
+        <f t="shared" ref="AE14:AN14" si="23">AE12-AE13</f>
+        <v>1458.8095499999999</v>
       </c>
       <c r="AF14" s="7">
-        <f t="shared" si="28"/>
-        <v>3302.4492121600006</v>
+        <f t="shared" si="23"/>
+        <v>1858.8247471200004</v>
       </c>
       <c r="AG14" s="7">
-        <f t="shared" si="28"/>
-        <v>3926.5754672320013</v>
+        <f t="shared" si="23"/>
+        <v>2268.1938767268002</v>
       </c>
       <c r="AH14" s="7">
-        <f t="shared" si="28"/>
-        <v>4566.7059518375718</v>
+        <f t="shared" si="23"/>
+        <v>2500.2963016528083</v>
       </c>
       <c r="AI14" s="7">
-        <f t="shared" si="28"/>
-        <v>5214.3165870419662</v>
+        <f t="shared" si="23"/>
+        <v>2705.3727727441865</v>
       </c>
       <c r="AJ14" s="7">
-        <f t="shared" si="28"/>
-        <v>5850.9213909477139</v>
+        <f t="shared" si="23"/>
+        <v>2921.7783500624469</v>
       </c>
       <c r="AK14" s="7">
-        <f t="shared" si="28"/>
-        <v>6213.5590610414447</v>
+        <f t="shared" si="23"/>
+        <v>3098.4917971814903</v>
       </c>
       <c r="AL14" s="7">
-        <f t="shared" si="28"/>
-        <v>6595.3024237712616</v>
+        <f t="shared" si="23"/>
+        <v>3229.4155301890687</v>
       </c>
       <c r="AM14" s="7">
-        <f t="shared" si="28"/>
-        <v>6997.1206400371057</v>
+        <f t="shared" si="23"/>
+        <v>3309.509600066257</v>
       </c>
       <c r="AN14" s="7">
-        <f t="shared" si="28"/>
-        <v>7420.0315107195465</v>
+        <f t="shared" si="23"/>
+        <v>3391.4284178694106</v>
       </c>
       <c r="AO14" s="1">
         <f>AN14*(1+$AQ$19)</f>
-        <v>7345.8311956123507</v>
+        <v>3357.5141336907163</v>
       </c>
       <c r="AP14" s="1">
-        <f t="shared" ref="AP14:DA14" si="29">AO14*(1+$AQ$19)</f>
-        <v>7272.3728836562268</v>
+        <f t="shared" ref="AP14:DA14" si="24">AO14*(1+$AQ$19)</f>
+        <v>3323.9389923538092</v>
       </c>
       <c r="AQ14" s="1">
-        <f t="shared" si="29"/>
-        <v>7199.6491548196645</v>
+        <f t="shared" si="24"/>
+        <v>3290.6996024302712</v>
       </c>
       <c r="AR14" s="1">
-        <f t="shared" si="29"/>
-        <v>7127.6526632714676</v>
+        <f t="shared" si="24"/>
+        <v>3257.7926064059684</v>
       </c>
       <c r="AS14" s="1">
-        <f t="shared" si="29"/>
-        <v>7056.3761366387525</v>
+        <f t="shared" si="24"/>
+        <v>3225.2146803419087</v>
       </c>
       <c r="AT14" s="1">
-        <f t="shared" si="29"/>
-        <v>6985.812375272365</v>
+        <f t="shared" si="24"/>
+        <v>3192.9625335384894</v>
       </c>
       <c r="AU14" s="1">
-        <f t="shared" si="29"/>
-        <v>6915.9542515196417</v>
+        <f t="shared" si="24"/>
+        <v>3161.0329082031044</v>
       </c>
       <c r="AV14" s="1">
-        <f t="shared" si="29"/>
-        <v>6846.7947090044454</v>
+        <f t="shared" si="24"/>
+        <v>3129.4225791210733</v>
       </c>
       <c r="AW14" s="1">
-        <f t="shared" si="29"/>
-        <v>6778.3267619144008</v>
+        <f t="shared" si="24"/>
+        <v>3098.1283533298624</v>
       </c>
       <c r="AX14" s="1">
-        <f t="shared" si="29"/>
-        <v>6710.543494295257</v>
+        <f t="shared" si="24"/>
+        <v>3067.1470697965638</v>
       </c>
       <c r="AY14" s="1">
-        <f t="shared" si="29"/>
-        <v>6643.4380593523047</v>
+        <f t="shared" si="24"/>
+        <v>3036.4755990985982</v>
       </c>
       <c r="AZ14" s="1">
-        <f t="shared" si="29"/>
-        <v>6577.0036787587815</v>
+        <f t="shared" si="24"/>
+        <v>3006.1108431076123</v>
       </c>
       <c r="BA14" s="1">
-        <f t="shared" si="29"/>
-        <v>6511.2336419711937</v>
+        <f t="shared" si="24"/>
+        <v>2976.049734676536</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="29"/>
-        <v>6446.1213055514818</v>
+        <f t="shared" si="24"/>
+        <v>2946.2892373297705</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="29"/>
-        <v>6381.6600924959666</v>
+        <f t="shared" si="24"/>
+        <v>2916.8263449564729</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="29"/>
-        <v>6317.8434915710068</v>
+        <f t="shared" si="24"/>
+        <v>2887.6580815069083</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="29"/>
-        <v>6254.6650566552962</v>
+        <f t="shared" si="24"/>
+        <v>2858.781500691839</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="29"/>
-        <v>6192.1184060887435</v>
+        <f t="shared" si="24"/>
+        <v>2830.1936856849206</v>
       </c>
       <c r="BG14" s="1">
-        <f t="shared" si="29"/>
-        <v>6130.1972220278558</v>
+        <f t="shared" si="24"/>
+        <v>2801.8917488280713</v>
       </c>
       <c r="BH14" s="1">
-        <f t="shared" si="29"/>
-        <v>6068.8952498075769</v>
+        <f t="shared" si="24"/>
+        <v>2773.8728313397905</v>
       </c>
       <c r="BI14" s="1">
-        <f t="shared" si="29"/>
-        <v>6008.2062973095008</v>
+        <f t="shared" si="24"/>
+        <v>2746.1341030263925</v>
       </c>
       <c r="BJ14" s="1">
-        <f t="shared" si="29"/>
-        <v>5948.1242343364056</v>
+        <f t="shared" si="24"/>
+        <v>2718.6727619961284</v>
       </c>
       <c r="BK14" s="1">
-        <f t="shared" si="29"/>
-        <v>5888.6429919930415</v>
+        <f t="shared" si="24"/>
+        <v>2691.486034376167</v>
       </c>
       <c r="BL14" s="1">
-        <f t="shared" si="29"/>
-        <v>5829.7565620731111</v>
+        <f t="shared" si="24"/>
+        <v>2664.5711740324055</v>
       </c>
       <c r="BM14" s="1">
-        <f t="shared" si="29"/>
-        <v>5771.4589964523802</v>
+        <f t="shared" si="24"/>
+        <v>2637.9254622920812</v>
       </c>
       <c r="BN14" s="1">
-        <f t="shared" si="29"/>
-        <v>5713.7444064878564</v>
+        <f t="shared" si="24"/>
+        <v>2611.5462076691601</v>
       </c>
       <c r="BO14" s="1">
-        <f t="shared" si="29"/>
-        <v>5656.6069624229776</v>
+        <f t="shared" si="24"/>
+        <v>2585.4307455924686</v>
       </c>
       <c r="BP14" s="1">
-        <f t="shared" si="29"/>
-        <v>5600.0408927987482</v>
+        <f t="shared" si="24"/>
+        <v>2559.5764381365439</v>
       </c>
       <c r="BQ14" s="1">
-        <f t="shared" si="29"/>
-        <v>5544.0404838707609</v>
+        <f t="shared" si="24"/>
+        <v>2533.9806737551785</v>
       </c>
       <c r="BR14" s="1">
-        <f t="shared" si="29"/>
-        <v>5488.6000790320531</v>
+        <f t="shared" si="24"/>
+        <v>2508.6408670176265</v>
       </c>
       <c r="BS14" s="1">
-        <f t="shared" si="29"/>
-        <v>5433.7140782417328</v>
+        <f t="shared" si="24"/>
+        <v>2483.5544583474502</v>
       </c>
       <c r="BT14" s="1">
-        <f t="shared" si="29"/>
-        <v>5379.3769374593157</v>
+        <f t="shared" si="24"/>
+        <v>2458.7189137639757</v>
       </c>
       <c r="BU14" s="1">
-        <f t="shared" si="29"/>
-        <v>5325.5831680847223</v>
+        <f t="shared" si="24"/>
+        <v>2434.1317246263361</v>
       </c>
       <c r="BV14" s="1">
-        <f t="shared" si="29"/>
-        <v>5272.3273364038751</v>
+        <f t="shared" si="24"/>
+        <v>2409.7904073800728</v>
       </c>
       <c r="BW14" s="1">
-        <f t="shared" si="29"/>
-        <v>5219.6040630398365</v>
+        <f t="shared" si="24"/>
+        <v>2385.6925033062721</v>
       </c>
       <c r="BX14" s="1">
-        <f t="shared" si="29"/>
-        <v>5167.4080224094378</v>
+        <f t="shared" si="24"/>
+        <v>2361.8355782732092</v>
       </c>
       <c r="BY14" s="1">
-        <f t="shared" si="29"/>
-        <v>5115.733942185343</v>
+        <f t="shared" si="24"/>
+        <v>2338.2172224904771</v>
       </c>
       <c r="BZ14" s="1">
-        <f t="shared" si="29"/>
-        <v>5064.57660276349</v>
+        <f t="shared" si="24"/>
+        <v>2314.8350502655721</v>
       </c>
       <c r="CA14" s="1">
-        <f t="shared" si="29"/>
-        <v>5013.9308367358553</v>
+        <f t="shared" si="24"/>
+        <v>2291.6866997629163</v>
       </c>
       <c r="CB14" s="1">
-        <f t="shared" si="29"/>
-        <v>4963.791528368497</v>
+        <f t="shared" si="24"/>
+        <v>2268.769832765287</v>
       </c>
       <c r="CC14" s="1">
-        <f t="shared" si="29"/>
-        <v>4914.1536130848117</v>
+        <f t="shared" si="24"/>
+        <v>2246.0821344376341</v>
       </c>
       <c r="CD14" s="1">
-        <f t="shared" si="29"/>
-        <v>4865.0120769539635</v>
+        <f t="shared" si="24"/>
+        <v>2223.6213130932579</v>
       </c>
       <c r="CE14" s="1">
-        <f t="shared" si="29"/>
-        <v>4816.3619561844234</v>
+        <f t="shared" si="24"/>
+        <v>2201.3850999623251</v>
       </c>
       <c r="CF14" s="1">
-        <f t="shared" si="29"/>
-        <v>4768.1983366225795</v>
+        <f t="shared" si="24"/>
+        <v>2179.3712489627019</v>
       </c>
       <c r="CG14" s="1">
-        <f t="shared" si="29"/>
-        <v>4720.5163532563538</v>
+        <f t="shared" si="24"/>
+        <v>2157.5775364730748</v>
       </c>
       <c r="CH14" s="1">
-        <f t="shared" si="29"/>
-        <v>4673.3111897237904</v>
+        <f t="shared" si="24"/>
+        <v>2136.001761108344</v>
       </c>
       <c r="CI14" s="1">
-        <f t="shared" si="29"/>
-        <v>4626.5780778265525</v>
+        <f t="shared" si="24"/>
+        <v>2114.6417434972604</v>
       </c>
       <c r="CJ14" s="1">
-        <f t="shared" si="29"/>
-        <v>4580.3122970482873</v>
+        <f t="shared" si="24"/>
+        <v>2093.4953260622879</v>
       </c>
       <c r="CK14" s="1">
-        <f t="shared" si="29"/>
-        <v>4534.5091740778043</v>
+        <f t="shared" si="24"/>
+        <v>2072.5603728016649</v>
       </c>
       <c r="CL14" s="1">
-        <f t="shared" si="29"/>
-        <v>4489.1640823370262</v>
+        <f t="shared" si="24"/>
+        <v>2051.8347690736482</v>
       </c>
       <c r="CM14" s="1">
-        <f t="shared" si="29"/>
-        <v>4444.2724415136563</v>
+        <f t="shared" si="24"/>
+        <v>2031.3164213829118</v>
       </c>
       <c r="CN14" s="1">
-        <f t="shared" si="29"/>
-        <v>4399.8297170985197</v>
+        <f t="shared" si="24"/>
+        <v>2011.0032571690826</v>
       </c>
       <c r="CO14" s="1">
-        <f t="shared" si="29"/>
-        <v>4355.8314199275346</v>
+        <f t="shared" si="24"/>
+        <v>1990.8932245973917</v>
       </c>
       <c r="CP14" s="1">
-        <f t="shared" si="29"/>
-        <v>4312.273105728259</v>
+        <f t="shared" si="24"/>
+        <v>1970.9842923514177</v>
       </c>
       <c r="CQ14" s="1">
-        <f t="shared" si="29"/>
-        <v>4269.1503746709768</v>
+        <f t="shared" si="24"/>
+        <v>1951.2744494279036</v>
       </c>
       <c r="CR14" s="1">
-        <f t="shared" si="29"/>
-        <v>4226.4588709242671</v>
+        <f t="shared" si="24"/>
+        <v>1931.7617049336245</v>
       </c>
       <c r="CS14" s="1">
-        <f t="shared" si="29"/>
-        <v>4184.194282215024</v>
+        <f t="shared" si="24"/>
+        <v>1912.4440878842884</v>
       </c>
       <c r="CT14" s="1">
-        <f t="shared" si="29"/>
-        <v>4142.3523393928735</v>
+        <f t="shared" si="24"/>
+        <v>1893.3196470054454</v>
       </c>
       <c r="CU14" s="1">
-        <f t="shared" si="29"/>
-        <v>4100.9288159989446</v>
+        <f t="shared" si="24"/>
+        <v>1874.3864505353908</v>
       </c>
       <c r="CV14" s="1">
-        <f t="shared" si="29"/>
-        <v>4059.9195278389552</v>
+        <f t="shared" si="24"/>
+        <v>1855.6425860300369</v>
       </c>
       <c r="CW14" s="1">
-        <f t="shared" si="29"/>
-        <v>4019.3203325605655</v>
+        <f t="shared" si="24"/>
+        <v>1837.0861601697366</v>
       </c>
       <c r="CX14" s="1">
-        <f t="shared" si="29"/>
-        <v>3979.1271292349597</v>
+        <f t="shared" si="24"/>
+        <v>1818.7152985680391</v>
       </c>
       <c r="CY14" s="1">
-        <f t="shared" si="29"/>
-        <v>3939.3358579426099</v>
+        <f t="shared" si="24"/>
+        <v>1800.5281455823588</v>
       </c>
       <c r="CZ14" s="1">
-        <f t="shared" si="29"/>
-        <v>3899.9424993631837</v>
+        <f t="shared" si="24"/>
+        <v>1782.5228641265351</v>
       </c>
       <c r="DA14" s="1">
-        <f t="shared" si="29"/>
-        <v>3860.9430743695521</v>
+        <f t="shared" si="24"/>
+        <v>1764.6976354852698</v>
       </c>
       <c r="DB14" s="1">
-        <f t="shared" ref="DB14:ES14" si="30">DA14*(1+$AQ$19)</f>
-        <v>3822.3336436258564</v>
+        <f t="shared" ref="DB14:ES14" si="25">DA14*(1+$AQ$19)</f>
+        <v>1747.050659130417</v>
       </c>
       <c r="DC14" s="1">
-        <f t="shared" si="30"/>
-        <v>3784.1103071895977</v>
+        <f t="shared" si="25"/>
+        <v>1729.5801525391128</v>
       </c>
       <c r="DD14" s="1">
-        <f t="shared" si="30"/>
-        <v>3746.2692041177015</v>
+        <f t="shared" si="25"/>
+        <v>1712.2843510137216</v>
       </c>
       <c r="DE14" s="1">
-        <f t="shared" si="30"/>
-        <v>3708.8065120765245</v>
+        <f t="shared" si="25"/>
+        <v>1695.1615075035843</v>
       </c>
       <c r="DF14" s="1">
-        <f t="shared" si="30"/>
-        <v>3671.7184469557592</v>
+        <f t="shared" si="25"/>
+        <v>1678.2098924285485</v>
       </c>
       <c r="DG14" s="1">
-        <f t="shared" si="30"/>
-        <v>3635.0012624862015</v>
+        <f t="shared" si="25"/>
+        <v>1661.427793504263</v>
       </c>
       <c r="DH14" s="1">
-        <f t="shared" si="30"/>
-        <v>3598.6512498613397</v>
+        <f t="shared" si="25"/>
+        <v>1644.8135155692205</v>
       </c>
       <c r="DI14" s="1">
-        <f t="shared" si="30"/>
-        <v>3562.6647373627261</v>
+        <f t="shared" si="25"/>
+        <v>1628.3653804135283</v>
       </c>
       <c r="DJ14" s="1">
-        <f t="shared" si="30"/>
-        <v>3527.0380899890988</v>
+        <f t="shared" si="25"/>
+        <v>1612.0817266093929</v>
       </c>
       <c r="DK14" s="1">
-        <f t="shared" si="30"/>
-        <v>3491.767709089208</v>
+        <f t="shared" si="25"/>
+        <v>1595.9609093432989</v>
       </c>
       <c r="DL14" s="1">
-        <f t="shared" si="30"/>
-        <v>3456.8500319983159</v>
+        <f t="shared" si="25"/>
+        <v>1580.0013002498658</v>
       </c>
       <c r="DM14" s="1">
-        <f t="shared" si="30"/>
-        <v>3422.2815316783326</v>
+        <f t="shared" si="25"/>
+        <v>1564.2012872473672</v>
       </c>
       <c r="DN14" s="1">
-        <f t="shared" si="30"/>
-        <v>3388.0587163615492</v>
+        <f t="shared" si="25"/>
+        <v>1548.5592743748934</v>
       </c>
       <c r="DO14" s="1">
-        <f t="shared" si="30"/>
-        <v>3354.1781291979337</v>
+        <f t="shared" si="25"/>
+        <v>1533.0736816311446</v>
       </c>
       <c r="DP14" s="1">
-        <f t="shared" si="30"/>
-        <v>3320.6363479059542</v>
+        <f t="shared" si="25"/>
+        <v>1517.7429448148332</v>
       </c>
       <c r="DQ14" s="1">
-        <f t="shared" si="30"/>
-        <v>3287.4299844268944</v>
+        <f t="shared" si="25"/>
+        <v>1502.5655153666848</v>
       </c>
       <c r="DR14" s="1">
-        <f t="shared" si="30"/>
-        <v>3254.5556845826254</v>
+        <f t="shared" si="25"/>
+        <v>1487.5398602130181</v>
       </c>
       <c r="DS14" s="1">
-        <f t="shared" si="30"/>
-        <v>3222.0101277367989</v>
+        <f t="shared" si="25"/>
+        <v>1472.6644616108879</v>
       </c>
       <c r="DT14" s="1">
-        <f t="shared" si="30"/>
-        <v>3189.7900264594309</v>
+        <f t="shared" si="25"/>
+        <v>1457.937816994779</v>
       </c>
       <c r="DU14" s="1">
-        <f t="shared" si="30"/>
-        <v>3157.8921261948367</v>
+        <f t="shared" si="25"/>
+        <v>1443.3584388248312</v>
       </c>
       <c r="DV14" s="1">
-        <f t="shared" si="30"/>
-        <v>3126.3132049328883</v>
+        <f t="shared" si="25"/>
+        <v>1428.9248544365828</v>
       </c>
       <c r="DW14" s="1">
-        <f t="shared" si="30"/>
-        <v>3095.0500728835596</v>
+        <f t="shared" si="25"/>
+        <v>1414.635605892217</v>
       </c>
       <c r="DX14" s="1">
-        <f t="shared" si="30"/>
-        <v>3064.0995721547238</v>
+        <f t="shared" si="25"/>
+        <v>1400.4892498332947</v>
       </c>
       <c r="DY14" s="1">
-        <f t="shared" si="30"/>
-        <v>3033.4585764331764</v>
+        <f t="shared" si="25"/>
+        <v>1386.4843573349617</v>
       </c>
       <c r="DZ14" s="1">
-        <f t="shared" si="30"/>
-        <v>3003.1239906688447</v>
+        <f t="shared" si="25"/>
+        <v>1372.6195137616121</v>
       </c>
       <c r="EA14" s="1">
-        <f t="shared" si="30"/>
-        <v>2973.0927507621564</v>
+        <f t="shared" si="25"/>
+        <v>1358.893318623996</v>
       </c>
       <c r="EB14" s="1">
-        <f t="shared" si="30"/>
-        <v>2943.3618232545346</v>
+        <f t="shared" si="25"/>
+        <v>1345.3043854377561</v>
       </c>
       <c r="EC14" s="1">
-        <f t="shared" si="30"/>
-        <v>2913.928205021989</v>
+        <f t="shared" si="25"/>
+        <v>1331.8513415833786</v>
       </c>
       <c r="ED14" s="1">
-        <f t="shared" si="30"/>
-        <v>2884.7889229717689</v>
+        <f t="shared" si="25"/>
+        <v>1318.5328281675447</v>
       </c>
       <c r="EE14" s="1">
-        <f t="shared" si="30"/>
-        <v>2855.9410337420513</v>
+        <f t="shared" si="25"/>
+        <v>1305.3474998858692</v>
       </c>
       <c r="EF14" s="1">
-        <f t="shared" si="30"/>
-        <v>2827.3816234046308</v>
+        <f t="shared" si="25"/>
+        <v>1292.2940248870104</v>
       </c>
       <c r="EG14" s="1">
-        <f t="shared" si="30"/>
-        <v>2799.1078071705842</v>
+        <f t="shared" si="25"/>
+        <v>1279.3710846381402</v>
       </c>
       <c r="EH14" s="1">
-        <f t="shared" si="30"/>
-        <v>2771.1167290988783</v>
+        <f t="shared" si="25"/>
+        <v>1266.5773737917589</v>
       </c>
       <c r="EI14" s="1">
-        <f t="shared" si="30"/>
-        <v>2743.4055618078896</v>
+        <f t="shared" si="25"/>
+        <v>1253.9116000538413</v>
       </c>
       <c r="EJ14" s="1">
-        <f t="shared" si="30"/>
-        <v>2715.9715061898105</v>
+        <f t="shared" si="25"/>
+        <v>1241.372484053303</v>
       </c>
       <c r="EK14" s="1">
-        <f t="shared" si="30"/>
-        <v>2688.8117911279123</v>
+        <f t="shared" si="25"/>
+        <v>1228.95875921277</v>
       </c>
       <c r="EL14" s="1">
-        <f t="shared" si="30"/>
-        <v>2661.9236732166332</v>
+        <f t="shared" si="25"/>
+        <v>1216.6691716206424</v>
       </c>
       <c r="EM14" s="1">
-        <f t="shared" si="30"/>
-        <v>2635.3044364844668</v>
+        <f t="shared" si="25"/>
+        <v>1204.5024799044359</v>
       </c>
       <c r="EN14" s="1">
-        <f t="shared" si="30"/>
-        <v>2608.9513921196221</v>
+        <f t="shared" si="25"/>
+        <v>1192.4574551053915</v>
       </c>
       <c r="EO14" s="1">
-        <f t="shared" si="30"/>
-        <v>2582.861878198426</v>
+        <f t="shared" si="25"/>
+        <v>1180.5328805543377</v>
       </c>
       <c r="EP14" s="1">
-        <f t="shared" si="30"/>
-        <v>2557.0332594164415</v>
+        <f t="shared" si="25"/>
+        <v>1168.7275517487942</v>
       </c>
       <c r="EQ14" s="1">
-        <f t="shared" si="30"/>
-        <v>2531.462926822277</v>
+        <f t="shared" si="25"/>
+        <v>1157.0402762313063</v>
       </c>
       <c r="ER14" s="1">
-        <f t="shared" si="30"/>
-        <v>2506.1482975540544</v>
+        <f t="shared" si="25"/>
+        <v>1145.4698734689932</v>
       </c>
       <c r="ES14" s="1">
-        <f t="shared" si="30"/>
-        <v>2481.0868145785139</v>
+        <f t="shared" si="25"/>
+        <v>1134.0151747343032</v>
       </c>
     </row>
     <row r="15" spans="1:149" x14ac:dyDescent="0.3">
@@ -3073,13 +3062,13 @@
         <v>204.5</v>
       </c>
       <c r="T15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="U15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="V15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="Z15" s="2">
         <v>200</v>
@@ -3095,37 +3084,37 @@
         <v>203.8</v>
       </c>
       <c r="AD15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AE15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AF15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AG15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AH15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AI15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AJ15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AK15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AL15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AM15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
       <c r="AN15" s="2">
-        <v>204.5</v>
+        <v>205.4</v>
       </c>
     </row>
     <row r="16" spans="1:149" x14ac:dyDescent="0.3">
@@ -3133,84 +3122,84 @@
         <v>25</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:P16" si="31">C14/C15</f>
+        <f t="shared" ref="C16:P16" si="26">C14/C15</f>
         <v>0.11923276308968377</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-0.10368066355624676</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>1.0368066355624676E-2</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-0.20217729393468117</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>0.67910834629341621</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-0.6480041472265422</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-0.859658208182289</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-1.3975155279503106</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-1.1621900826446281</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-1.5534979423868311</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>0.33436213991769548</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>-0.35714285714285715</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>0.99494949494949492</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>1.37</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" ref="Q16:R16" si="32">Q14/Q15</f>
+        <f t="shared" ref="Q16:R16" si="27">Q14/Q15</f>
         <v>1.4880952380952381</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>1.8007850834151127</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" ref="S16:V16" si="33">S14/S15</f>
+        <f t="shared" ref="S16:V16" si="28">S14/S15</f>
         <v>1.1002444987775062</v>
       </c>
       <c r="T16" s="8">
-        <f t="shared" si="33"/>
-        <v>2.0671476161369187</v>
+        <f t="shared" si="28"/>
+        <v>-0.41869522882181109</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" si="33"/>
-        <v>2.381226161369193</v>
+        <f t="shared" si="28"/>
+        <v>1.7854703018500486</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="33"/>
-        <v>2.8368176039119812</v>
+        <f t="shared" si="28"/>
+        <v>2.2185248296007796</v>
       </c>
       <c r="Z16" s="8">
         <f>Z14/Z15</f>
@@ -3230,47 +3219,47 @@
       </c>
       <c r="AD16" s="8">
         <f>AD14/AD15</f>
-        <v>8.3854358801956046</v>
+        <v>4.6807234664069961</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" ref="AE16:AN16" si="34">AE14/AE15</f>
-        <v>13.228160563325186</v>
+        <f t="shared" ref="AE16:AN16" si="29">AE14/AE15</f>
+        <v>7.102286027263875</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="34"/>
-        <v>16.148895902982886</v>
+        <f t="shared" si="29"/>
+        <v>9.0497796841285307</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="34"/>
-        <v>19.200858030474333</v>
+        <f t="shared" si="29"/>
+        <v>11.04281342125998</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="34"/>
-        <v>22.33108044908348</v>
+        <f t="shared" si="29"/>
+        <v>12.172815490033146</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="34"/>
-        <v>25.49788062123211</v>
+        <f t="shared" si="29"/>
+        <v>13.171240373632845</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="34"/>
-        <v>28.610862547421583</v>
+        <f t="shared" si="29"/>
+        <v>14.224821567976859</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="34"/>
-        <v>30.384151887733225</v>
+        <f t="shared" si="29"/>
+        <v>15.0851596746908</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="34"/>
-        <v>32.250867597903479</v>
+        <f t="shared" si="29"/>
+        <v>15.722568306665378</v>
       </c>
       <c r="AM16" s="8">
-        <f t="shared" si="34"/>
-        <v>34.215748851037191</v>
+        <f t="shared" si="29"/>
+        <v>16.112510224275837</v>
       </c>
       <c r="AN16" s="8">
-        <f t="shared" si="34"/>
-        <v>36.283772668555237</v>
+        <f t="shared" si="29"/>
+        <v>16.511336016890997</v>
       </c>
     </row>
     <row r="18" spans="2:43" x14ac:dyDescent="0.3">
@@ -3282,39 +3271,39 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9">
-        <f t="shared" ref="G18:O18" si="35">G3/C3-1</f>
+        <f t="shared" ref="G18:O18" si="30">G3/C3-1</f>
         <v>0.23940381928272014</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.2286572286572286</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.21391443422630951</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.17738936407586459</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.14317925591882741</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.10928770949720668</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.10573122529644263</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.15950726468730259</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0.19526627218934922</v>
       </c>
       <c r="P18" s="9">
@@ -3322,28 +3311,28 @@
         <v>0.19830028328611893</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" ref="Q18:R18" si="36">Q3/M3-1</f>
+        <f t="shared" ref="Q18:R18" si="31">Q3/M3-1</f>
         <v>0.18796544533809945</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>0.15554344865159364</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" ref="S18" si="37">S3/O3-1</f>
+        <f t="shared" ref="S18" si="32">S3/O3-1</f>
         <v>0.1523652365236523</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18" si="38">T3/P3-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="T18" si="33">T3/P3-1</f>
+        <v>0.1013921723141582</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" ref="U18" si="39">U3/Q3-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="U18" si="34">U3/Q3-1</f>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" ref="V18" si="40">V3/R3-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="V18" si="35">V3/R3-1</f>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="X18" s="9"/>
       <c r="Y18" s="9" t="e">
@@ -3351,64 +3340,64 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z18" s="9" t="e">
-        <f t="shared" ref="Z18:AN18" si="41">Z3/Y3-1</f>
+        <f t="shared" ref="Z18:AN18" si="36">Z3/Y3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="36"/>
         <v>0.21297062474141493</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="36"/>
         <v>0.12961541741280813</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="36"/>
         <v>0.18313580433305665</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="41"/>
-        <v>0.14242901805653041</v>
+        <f t="shared" si="36"/>
+        <v>0.1045288075033497</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="41"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="36"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="41"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="36"/>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="41"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="36"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="41"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="36"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="41"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="36"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="41"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="36"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="41"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="36"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="41"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM18" s="9">
-        <f t="shared" si="41"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="36"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN18" s="9">
-        <f t="shared" si="41"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="36"/>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="19" spans="2:43" x14ac:dyDescent="0.3">
@@ -3416,55 +3405,55 @@
         <v>43</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:O19" si="42">C5/C3</f>
+        <f t="shared" ref="C19:O19" si="37">C5/C3</f>
         <v>0.25523986958546807</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.28442728442728443</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.26709316273490602</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.26478244700632203</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.25216084178880122</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.24581005586592178</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.24703557312252963</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.25300063171193937</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.2518080210387903</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.24110796348756688</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.26362823949955316</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.26695723236175428</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>0.27612761276127612</v>
       </c>
       <c r="P19" s="9">
@@ -3472,96 +3461,96 @@
         <v>0.29209351195166799</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" ref="Q19:R19" si="43">Q5/Q3</f>
+        <f t="shared" ref="Q19:R19" si="38">Q5/Q3</f>
         <v>0.31093279839518556</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="38"/>
         <v>0.32248939179632247</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="44">S5/S3</f>
+        <f t="shared" ref="S19:V19" si="39">S5/S3</f>
         <v>0.31646778042959428</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="44"/>
-        <v>0.32</v>
+        <f t="shared" si="39"/>
+        <v>0.3148103982828524</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>0.33</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>0.34</v>
       </c>
       <c r="X19" s="9" t="e">
-        <f t="shared" ref="X19:AN19" si="45">X5/X3</f>
+        <f t="shared" ref="X19:AN19" si="40">X5/X3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y19" s="9" t="e">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>0.26799751758378154</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>0.2495096785196555</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>0.25643541934022795</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>0.30141006827027372</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.32704165081939474</v>
+        <f t="shared" si="40"/>
+        <v>0.32569203432675098</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
+        <v>0.34</v>
+      </c>
+      <c r="AF19" s="9">
+        <f t="shared" si="40"/>
         <v>0.35</v>
       </c>
-      <c r="AF19" s="9">
-        <f t="shared" si="45"/>
+      <c r="AG19" s="9">
+        <f t="shared" si="40"/>
         <v>0.36</v>
       </c>
-      <c r="AG19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.37</v>
-      </c>
       <c r="AH19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.38</v>
+        <f t="shared" si="40"/>
+        <v>0.35999999999999993</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.39000000000000007</v>
+        <f t="shared" si="40"/>
+        <v>0.36</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.4</v>
+        <f t="shared" si="40"/>
+        <v>0.36</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.4</v>
+        <f t="shared" si="40"/>
+        <v>0.36</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.4</v>
+        <f t="shared" si="40"/>
+        <v>0.36</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.4</v>
+        <f t="shared" si="40"/>
+        <v>0.36</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" si="45"/>
-        <v>0.4</v>
+        <f t="shared" si="40"/>
+        <v>0.36000000000000004</v>
       </c>
       <c r="AP19" t="s">
         <v>49</v>
@@ -3579,39 +3568,39 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:O20" si="46">G6/C6-1</f>
+        <f t="shared" ref="G20:O20" si="41">G6/C6-1</f>
         <v>0.27551020408163263</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>0.31764705882352939</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>0.85576923076923084</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>0.64031620553359692</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>0.74</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>0.34821428571428581</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>-4.4041450777202118E-2</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>0.12771084337349392</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>-0.10574712643678164</v>
       </c>
       <c r="P20" s="9">
@@ -3619,28 +3608,28 @@
         <v>-0.16335540838852092</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20:R20" si="47">Q6/M6-1</f>
+        <f t="shared" ref="Q20:R20" si="42">Q6/M6-1</f>
         <v>-7.3170731707317027E-2</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>-0.19658119658119655</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20" si="48">S6/O6-1</f>
+        <f t="shared" ref="S20" si="43">S6/O6-1</f>
         <v>-2.5706940874036022E-2</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="49">T6/P6-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="T20" si="44">T6/P6-1</f>
+        <v>9.4986807387862804E-2</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="50">U6/Q6-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="U20" si="45">U6/Q6-1</f>
+        <v>0.10000000000000009</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20" si="51">V6/R6-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="V20" si="46">V6/R6-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="X20" s="9"/>
       <c r="Y20" s="9" t="e">
@@ -3648,63 +3637,63 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z20" s="9" t="e">
-        <f t="shared" ref="Z20:AN20" si="52">Z6/Y6-1</f>
+        <f t="shared" ref="Z20:AN20" si="47">Z6/Y6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>0.52083333333333326</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>0.24369142033165114</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>-0.13855072463768114</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" si="52"/>
-        <v>8.0349932705250371E-3</v>
+        <f t="shared" si="47"/>
+        <v>7.0874831763122481E-2</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AF20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="52"/>
+      <c r="AG20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="52"/>
+      <c r="AH20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="52"/>
+      <c r="AI20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI20" s="9">
-        <f t="shared" si="52"/>
+      <c r="AJ20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ20" s="9">
-        <f t="shared" si="52"/>
+      <c r="AK20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="52"/>
+      <c r="AL20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="52"/>
+      <c r="AM20" s="9">
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AM20" s="9">
-        <f t="shared" si="52"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AN20" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AP20" t="s">
@@ -3719,55 +3708,55 @@
         <v>45</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:O21" si="53">C7/C3</f>
+        <f t="shared" ref="C21:O21" si="48">C7/C3</f>
         <v>0.10992081974848626</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.11969111969111969</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.11195521791283487</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.12644105615470436</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.11123637730176625</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.13652234636871508</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.14229249011857709</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.14308275426405559</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.11406969099276791</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.12559017941454201</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.10574918081620495</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>0.1176791065104876</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>8.9108910891089105E-2</v>
       </c>
       <c r="P21" s="9">
@@ -3775,103 +3764,103 @@
         <v>9.0097189387969526E-2</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" ref="Q21:R21" si="54">Q7/Q3</f>
+        <f t="shared" ref="Q21:R21" si="49">Q7/Q3</f>
         <v>8.3249749247743227E-2</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>9.2644978783592638E-2</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="55">S7/S3</f>
+        <f t="shared" ref="S21:V21" si="50">S7/S3</f>
         <v>7.494033412887828E-2</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="55"/>
-        <v>7.4999999999999997E-2</v>
+        <f t="shared" si="50"/>
+        <v>8.681135225375626E-2</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="55"/>
-        <v>7.4999999999999997E-2</v>
+        <f t="shared" si="50"/>
+        <v>0.09</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="55"/>
-        <v>7.4999999999999997E-2</v>
+        <f t="shared" si="50"/>
+        <v>0.09</v>
       </c>
       <c r="X21" s="9" t="e">
-        <f t="shared" ref="X21:AN21" si="56">X7/X3</f>
+        <f t="shared" ref="X21:AN21" si="51">X7/X3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y21" s="9" t="e">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.11739760033098882</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.13404962906114096</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.11572431493923152</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>8.88151598290053E-2</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.498603764585772E-2</v>
+        <f t="shared" si="51"/>
+        <v>8.5582649001113731E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>8.9999999999999983E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>0.09</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="56"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="51"/>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="AP21" t="s">
         <v>51</v>
       </c>
       <c r="AQ21" s="2">
         <f>NPV(AQ20,AC14:ES14)</f>
-        <v>73897.329620145974</v>
+        <v>36216.724398892606</v>
       </c>
     </row>
     <row r="22" spans="2:43" x14ac:dyDescent="0.3">
@@ -3883,39 +3872,39 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:O22" si="57">G8/C8-1</f>
+        <f t="shared" ref="G22:O22" si="52">G8/C8-1</f>
         <v>0.28431372549019618</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>0.46153846153846145</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>0.52380952380952372</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>0.30158730158730163</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>6.8702290076335881E-2</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>-5.8479532163742687E-2</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>-0.19374999999999998</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>-5.4878048780487854E-2</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>-0.12142857142857144</v>
       </c>
       <c r="P22" s="9">
@@ -3923,28 +3912,28 @@
         <v>-0.22981366459627328</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22:R22" si="58">Q8/M8-1</f>
+        <f t="shared" ref="Q22:R22" si="53">Q8/M8-1</f>
         <v>-0.13178294573643412</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="53"/>
         <v>-0.2129032258064516</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="59">S8/O8-1</f>
+        <f t="shared" ref="S22" si="54">S8/O8-1</f>
         <v>8.1300813008129413E-3</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="60">T8/P8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="T22" si="55">T8/P8-1</f>
+        <v>8.870967741935476E-2</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="61">U8/Q8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="U22" si="56">U8/Q8-1</f>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="62">V8/R8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="V22" si="57">V8/R8-1</f>
+        <v>0.1399999999999999</v>
       </c>
       <c r="X22" s="9"/>
       <c r="Y22" s="9" t="e">
@@ -3952,63 +3941,63 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z22" s="9" t="e">
-        <f t="shared" ref="Z22:AN22" si="63">Z8/Y8-1</f>
+        <f t="shared" ref="Z22:AN22" si="58">Z8/Y8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.39111111111111119</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>-6.5495207667731647E-2</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>-0.17777777777777781</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="63"/>
-        <v>1.6964656964657099E-2</v>
+        <f t="shared" si="58"/>
+        <v>7.9085239085239012E-2</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" si="58"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="63"/>
+      <c r="AH22" s="9">
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AI22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP22" t="s">
@@ -4016,7 +4005,7 @@
       </c>
       <c r="AQ22" s="2">
         <f>Main!D8</f>
-        <v>8217</v>
+        <v>8832</v>
       </c>
     </row>
     <row r="23" spans="2:43" x14ac:dyDescent="0.3">
@@ -4024,55 +4013,55 @@
         <v>47</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:O23" si="64">C9/C3</f>
+        <f t="shared" ref="C23:O23" si="59">C9/C3</f>
         <v>6.5207265952491851E-3</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>5.1480051480051478E-3</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>2.9988004798080767E-2</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-2.6031982149497955E-3</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-2.2547914317925591E-3</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-6.773743016759777E-2</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-7.5098814229249009E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-7.2962728995578013E-2</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-5.128205128205128E-2</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-7.7746301542335541E-2</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>9.5323205242776286E-3</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>-2.0430400435848543E-2</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>4.6204620462046202E-2</v>
       </c>
       <c r="P23" s="9">
@@ -4080,103 +4069,103 @@
         <v>6.9871289729445757E-2</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" ref="Q23:R23" si="65">Q9/Q3</f>
+        <f t="shared" ref="Q23:R23" si="60">Q9/Q3</f>
         <v>0.11384152457372117</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="60"/>
         <v>0.11244695898161244</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="66">S9/S3</f>
+        <f t="shared" ref="S23:V23" si="61">S9/S3</f>
         <v>0.12147971360381861</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="66"/>
-        <v>0.12781084044266283</v>
+        <f t="shared" si="61"/>
+        <v>9.6828046744574292E-2</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="66"/>
-        <v>0.15402751733461251</v>
+        <f t="shared" si="61"/>
+        <v>0.12562936515969927</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="66"/>
-        <v>0.15808446150737526</v>
+        <f t="shared" si="61"/>
+        <v>0.12772189917404445</v>
       </c>
       <c r="X23" s="9" t="e">
-        <f t="shared" ref="X23:AN23" si="67">X9/X3</f>
+        <f t="shared" ref="X23:AN23" si="62">X9/X3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y23" s="9" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="62"/>
         <v>9.722796855606123E-3</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="62"/>
         <v>-5.6195105312526646E-2</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="62"/>
         <v>-3.3668000301955159E-2</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="62"/>
         <v>8.7092451987494421E-2</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.14107723750913842</v>
+        <f t="shared" si="62"/>
+        <v>0.11820274410673255</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.17893040787706554</v>
+        <f t="shared" si="62"/>
+        <v>0.13341033532614405</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.19628092366782443</v>
+        <f t="shared" si="62"/>
+        <v>0.14962010856899649</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.21229957994603751</v>
+        <f t="shared" si="62"/>
+        <v>0.16477804742091251</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.22717182550459103</v>
+        <f t="shared" si="62"/>
+        <v>0.16874868714087807</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.2412328582195056</v>
+        <f t="shared" si="62"/>
+        <v>0.17188222262527089</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.25438677191302977</v>
+        <f t="shared" si="62"/>
+        <v>0.17491706125463247</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.25672180167540232</v>
+        <f t="shared" si="62"/>
+        <v>0.17697037574697344</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.25898346289915353</v>
+        <f t="shared" si="62"/>
+        <v>0.17809400744257653</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.2611741052911985</v>
+        <f t="shared" si="62"/>
+        <v>0.17831227780996692</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="67"/>
-        <v>0.26329600176823725</v>
+        <f t="shared" si="62"/>
+        <v>0.17852840827179464</v>
       </c>
       <c r="AP23" t="s">
         <v>53</v>
       </c>
       <c r="AQ23" s="2">
         <f>AQ21+AQ22</f>
-        <v>82114.329620145974</v>
+        <v>45048.724398892606</v>
       </c>
     </row>
     <row r="24" spans="2:43" x14ac:dyDescent="0.3">
@@ -4184,55 +4173,55 @@
         <v>23</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:O24" si="68">C13/C12</f>
+        <f t="shared" ref="C24:O24" si="63">C13/C12</f>
         <v>0.73563218390804597</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>3.5</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0.98765432098765427</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>-3.875</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0.15483870967741936</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>-0.3888888888888889</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>-0.15277777777777779</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>7.2164948453608241E-2</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>-9.2233009708737865E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>-0.25311203319502074</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0.1095890410958904</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>0.46564885496183206</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="63"/>
         <v>-0.13218390804597702</v>
       </c>
       <c r="P24" s="9">
@@ -4240,103 +4229,103 @@
         <v>-1.4814814814814815E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:R24" si="69">Q13/Q12</f>
+        <f t="shared" ref="Q24:R24" si="64">Q13/Q12</f>
         <v>0.24623115577889448</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="64"/>
         <v>0.26452905811623245</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:V24" si="70">S13/S12</f>
+        <f t="shared" ref="S24:V24" si="65">S13/S12</f>
         <v>0.31402439024390244</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="65"/>
+        <v>2.7916666666666665</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="65"/>
         <v>0.25</v>
       </c>
-      <c r="U24" s="9">
-        <f t="shared" si="70"/>
+      <c r="V24" s="9">
+        <f t="shared" si="65"/>
         <v>0.25</v>
       </c>
-      <c r="V24" s="9">
-        <f t="shared" si="70"/>
+      <c r="X24" s="9" t="e">
+        <f t="shared" ref="X24:AN24" si="66">X13/X12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y24" s="9" t="e">
+        <f t="shared" si="66"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="66"/>
+        <v>1.1365461847389557</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="66"/>
+        <v>-0.16216216216216217</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="66"/>
+        <v>-5.3465346534653464E-2</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" si="66"/>
+        <v>0.15137956748695003</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="66"/>
+        <v>0.3471097424296512</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="66"/>
         <v>0.25</v>
       </c>
-      <c r="X24" s="9" t="e">
-        <f t="shared" ref="X24:AN24" si="71">X13/X12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y24" s="9" t="e">
-        <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="71"/>
-        <v>1.1365461847389557</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="71"/>
-        <v>-0.16216216216216217</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="71"/>
-        <v>-5.3465346534653464E-2</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.15137956748695003</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.25907351288850367</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
-      </c>
       <c r="AF24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="71"/>
-        <v>0.2</v>
+        <f t="shared" si="66"/>
+        <v>0.25</v>
       </c>
       <c r="AP24" t="s">
         <v>58</v>
       </c>
       <c r="AQ24" s="2">
         <f>AQ23/Main!D15</f>
-        <v>93311.738204711335</v>
+        <v>51191.732271468871</v>
       </c>
     </row>
     <row r="25" spans="2:43" x14ac:dyDescent="0.3">
@@ -4344,55 +4333,55 @@
         <v>48</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:O25" si="72">C14/C3</f>
+        <f t="shared" ref="C25:O25" si="67">C14/C3</f>
         <v>1.0712622263623661E-2</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-8.5800085800085794E-3</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>7.9968012794882047E-4</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-1.4503532911863145E-2</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>4.9229612927470877E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-4.3645251396648044E-2</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-5.4677206851119896E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-8.5281111813013261E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-7.3964497041420121E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-9.5058231035568153E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>1.9362526064938934E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>-1.9068373740125308E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="67"/>
         <v>5.4180418041804179E-2</v>
       </c>
       <c r="P25" s="9">
@@ -4400,103 +4389,103 @@
         <v>7.1972681901759913E-2</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25:R25" si="73">Q14/Q3</f>
+        <f t="shared" ref="Q25:R25" si="68">Q14/Q3</f>
         <v>7.5225677031093285E-2</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>8.651579443658651E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="74">S14/S3</f>
+        <f t="shared" ref="S25:V25" si="69">S14/S3</f>
         <v>5.3699284009546537E-2</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="74"/>
-        <v>9.6557071641484221E-2</v>
+        <f t="shared" si="69"/>
+        <v>-2.0510374433579774E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10617957132266363</v>
+        <f t="shared" si="69"/>
+        <v>8.4366770034875263E-2</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="74"/>
-        <v>0.12210572842998588</v>
+        <f t="shared" si="69"/>
+        <v>9.9465006024411995E-2</v>
       </c>
       <c r="X25" s="9" t="e">
-        <f t="shared" ref="X25:AN25" si="75">X14/X3</f>
+        <f t="shared" ref="X25:AN25" si="70">X14/X3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y25" s="9" t="e">
-        <f t="shared" si="75"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="70"/>
         <v>-3.5167563094745551E-3</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="70"/>
         <v>-3.6667519399675962E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="70"/>
         <v>-4.0160036234619161E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="70"/>
         <v>7.2608945319977025E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="75"/>
-        <v>9.5771787974391981E-2</v>
+        <f t="shared" si="70"/>
+        <v>5.5537233526347964E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.1348942345290933</v>
+        <f t="shared" si="70"/>
+        <v>7.731128982496388E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.14970767999035733</v>
+        <f t="shared" si="70"/>
+        <v>9.1213477073118832E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.16330345895339113</v>
+        <f t="shared" si="70"/>
+        <v>0.10402002688016725</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.17585743234870746</v>
+        <f t="shared" si="70"/>
+        <v>0.10817387847533141</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.18765982089057312</v>
+        <f t="shared" si="70"/>
+        <v>0.11147275600356597</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.19865170626988246</v>
+        <f t="shared" si="70"/>
+        <v>0.11465674048405369</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.20091814881771949</v>
+        <f t="shared" si="70"/>
+        <v>0.11691475826496289</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.20310665461948321</v>
+        <f t="shared" si="70"/>
+        <v>0.11830570558024801</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.20521991387668384</v>
+        <f t="shared" si="70"/>
+        <v>0.11886260225677295</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="75"/>
-        <v>0.20726052301041939</v>
+        <f t="shared" si="70"/>
+        <v>0.11941642679920457</v>
       </c>
       <c r="AP25" t="s">
         <v>54</v>
       </c>
       <c r="AQ25" s="3">
         <f>AQ24/AN15</f>
-        <v>456.29211836044664</v>
+        <v>249.22946578125058</v>
       </c>
     </row>
     <row r="26" spans="2:43" x14ac:dyDescent="0.3">
@@ -4505,7 +4494,7 @@
       </c>
       <c r="AQ26" s="3">
         <f>Main!D3</f>
-        <v>658.88</v>
+        <v>707.19</v>
       </c>
     </row>
     <row r="27" spans="2:43" x14ac:dyDescent="0.3">
@@ -4514,7 +4503,7 @@
       </c>
       <c r="AQ27" s="10">
         <f>AQ25/AQ26-1</f>
-        <v>-0.30747310836503361</v>
+        <v>-0.64757778562868462</v>
       </c>
     </row>
     <row r="28" spans="2:43" x14ac:dyDescent="0.3">
@@ -4522,7 +4511,7 @@
         <v>57</v>
       </c>
       <c r="AQ28" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SPOT.xlsx
+++ b/Financial Analysis/SPOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB69B04C-5923-4348-86A5-7E31FF12AF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FAF218-CA54-4218-89D7-056EFE3B8D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
   </bookViews>
@@ -754,7 +754,7 @@
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="G3" s="12">
         <v>45958</v>

--- a/Financial Analysis/SPOT.xlsx
+++ b/Financial Analysis/SPOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FAF218-CA54-4218-89D7-056EFE3B8D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7098021-3C2E-4EF2-B668-11A1DB1261B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
   </bookViews>
@@ -747,14 +747,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>707.19</v>
+        <v>680.29</v>
       </c>
       <c r="E3" s="12">
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45930</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="12">
         <v>45958</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>145256.826</v>
+        <v>139731.56599999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -828,7 +828,7 @@
       </c>
       <c r="D10" s="2">
         <f>D5-D9</f>
-        <v>135220.46236363635</v>
+        <v>129695.20236363636</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AQ26" s="3">
         <f>Main!D3</f>
-        <v>707.19</v>
+        <v>680.29</v>
       </c>
     </row>
     <row r="27" spans="2:43" x14ac:dyDescent="0.3">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AQ27" s="10">
         <f>AQ25/AQ26-1</f>
-        <v>-0.64757778562868462</v>
+        <v>-0.6336423205085322</v>
       </c>
     </row>
     <row r="28" spans="2:43" x14ac:dyDescent="0.3">

--- a/Financial Analysis/SPOT.xlsx
+++ b/Financial Analysis/SPOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7098021-3C2E-4EF2-B668-11A1DB1261B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99E88CF-465B-4945-9C89-9349B980E41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
   </bookViews>
@@ -321,14 +321,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -345,7 +345,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12778740" y="7620"/>
+          <a:off x="13395960" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -747,17 +747,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>680.29</v>
+        <v>632.54</v>
       </c>
       <c r="E3" s="12">
-        <v>45937</v>
+        <v>45965</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="12">
-        <v>45958</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -765,10 +765,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -777,7 +778,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>139731.56599999999</v>
+        <v>130303.23999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,11 +786,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>5161+3183+2417</f>
-        <v>10761</v>
+        <f>5456+3606+61+2888</f>
+        <v>12011</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -797,11 +798,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>1929</f>
-        <v>1929</v>
+        <f>1741</f>
+        <v>1741</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -810,7 +811,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>8832</v>
+        <v>10270</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +820,7 @@
       </c>
       <c r="D9" s="2">
         <f>D8/D15</f>
-        <v>10036.363636363636</v>
+        <v>11804.597701149425</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
@@ -828,7 +829,7 @@
       </c>
       <c r="D10" s="2">
         <f>D5-D9</f>
-        <v>129695.20236363636</v>
+        <v>118498.64229885057</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -836,7 +837,7 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -1028,12 +1029,11 @@
         <v>4193</v>
       </c>
       <c r="U3" s="7">
-        <f>Q3*1.09</f>
-        <v>4346.92</v>
+        <v>4272</v>
       </c>
       <c r="V3" s="7">
-        <f>R3*1.08</f>
-        <v>4581.3600000000006</v>
+        <f>R3*1.06</f>
+        <v>4496.5200000000004</v>
       </c>
       <c r="Z3" s="7">
         <f>SUM(C3:F3)</f>
@@ -1053,47 +1053,47 @@
       </c>
       <c r="AD3" s="7">
         <f>SUM(S3:V3)</f>
-        <v>17311.28</v>
+        <v>17151.52</v>
       </c>
       <c r="AE3" s="7">
-        <f>AD3*1.09</f>
-        <v>18869.2952</v>
+        <f>AD3*1.07</f>
+        <v>18352.126400000001</v>
       </c>
       <c r="AF3" s="7">
-        <f>AE3*1.08</f>
-        <v>20378.838816000003</v>
+        <f>AE3*1.06</f>
+        <v>19453.253984000003</v>
       </c>
       <c r="AG3" s="7">
-        <f>AF3*1.07</f>
-        <v>21805.357533120005</v>
+        <f>AF3*1.05</f>
+        <v>20425.916683200005</v>
       </c>
       <c r="AH3" s="7">
-        <f>AG3*1.06</f>
-        <v>23113.678985107206</v>
+        <f>AG3*1.04</f>
+        <v>21242.953350528005</v>
       </c>
       <c r="AI3" s="7">
-        <f>AH3*1.05</f>
-        <v>24269.362934362569</v>
+        <f>AH3*1.03</f>
+        <v>21880.241951043845</v>
       </c>
       <c r="AJ3" s="7">
-        <f t="shared" ref="AJ3" si="0">AI3*1.05</f>
-        <v>25482.831081080698</v>
+        <f t="shared" ref="AJ3:AN3" si="0">AI3*1.03</f>
+        <v>22536.64920957516</v>
       </c>
       <c r="AK3" s="7">
-        <f>AJ3*1.04</f>
-        <v>26502.144324323926</v>
+        <f t="shared" si="0"/>
+        <v>23212.748685862414</v>
       </c>
       <c r="AL3" s="7">
-        <f>AK3*1.03</f>
-        <v>27297.208654053644</v>
+        <f t="shared" si="0"/>
+        <v>23909.131146438289</v>
       </c>
       <c r="AM3" s="7">
-        <f>AL3*1.02</f>
-        <v>27843.152827134716</v>
+        <f t="shared" si="0"/>
+        <v>24626.405080831439</v>
       </c>
       <c r="AN3" s="7">
-        <f>AM3*1.02</f>
-        <v>28400.01588367741</v>
+        <f t="shared" si="0"/>
+        <v>25365.197233256382</v>
       </c>
     </row>
     <row r="4" spans="1:149" x14ac:dyDescent="0.3">
@@ -1155,12 +1155,11 @@
         <v>2873</v>
       </c>
       <c r="U4" s="2">
-        <f t="shared" ref="U4:V4" si="1">U3-U5</f>
-        <v>2912.4364</v>
+        <v>2921</v>
       </c>
       <c r="V4" s="2">
-        <f t="shared" si="1"/>
-        <v>3023.6976000000004</v>
+        <f t="shared" ref="U4:V4" si="1">V3-V5</f>
+        <v>3057.6336000000001</v>
       </c>
       <c r="Z4" s="2">
         <f>SUM(C4:F4)</f>
@@ -1180,47 +1179,47 @@
       </c>
       <c r="AD4" s="2">
         <f>SUM(S4:V4)</f>
-        <v>11673.134000000002</v>
+        <v>11715.633600000001</v>
       </c>
       <c r="AE4" s="2">
         <f>AE3-AE5</f>
-        <v>12453.734832</v>
+        <v>12479.445952000002</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" ref="AF4:AN4" si="2">AF3-AF5</f>
-        <v>13246.245230400003</v>
+        <v>13033.680169280002</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="2"/>
-        <v>13955.428821196803</v>
+        <v>13685.364177744003</v>
       </c>
       <c r="AH4" s="2">
         <f t="shared" si="2"/>
-        <v>14792.754550468613</v>
+        <v>14232.778744853764</v>
       </c>
       <c r="AI4" s="2">
         <f t="shared" si="2"/>
-        <v>15532.392277992045</v>
+        <v>14659.762107199374</v>
       </c>
       <c r="AJ4" s="2">
         <f t="shared" si="2"/>
-        <v>16309.011891891647</v>
+        <v>15099.554970415356</v>
       </c>
       <c r="AK4" s="2">
         <f t="shared" si="2"/>
-        <v>16961.372367567314</v>
+        <v>15552.541619527818</v>
       </c>
       <c r="AL4" s="2">
         <f t="shared" si="2"/>
-        <v>17470.213538594333</v>
+        <v>16019.117868113653</v>
       </c>
       <c r="AM4" s="2">
         <f t="shared" si="2"/>
-        <v>17819.617809366217</v>
+        <v>16499.691404157064</v>
       </c>
       <c r="AN4" s="2">
         <f t="shared" si="2"/>
-        <v>18176.01016555354</v>
+        <v>16994.682146281775</v>
       </c>
     </row>
     <row r="5" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1229,7 +1228,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:T5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:U5" si="3">C3-C4</f>
         <v>548</v>
       </c>
       <c r="D5" s="7">
@@ -1301,12 +1300,12 @@
         <v>1320</v>
       </c>
       <c r="U5" s="7">
-        <f>U3*0.33</f>
-        <v>1434.4836</v>
+        <f t="shared" si="3"/>
+        <v>1351</v>
       </c>
       <c r="V5" s="7">
-        <f>V3*0.34</f>
-        <v>1557.6624000000004</v>
+        <f>V3*0.32</f>
+        <v>1438.8864000000001</v>
       </c>
       <c r="Z5" s="7">
         <f>Z3-Z4</f>
@@ -1326,47 +1325,47 @@
       </c>
       <c r="AD5" s="7">
         <f>AD3-AD4</f>
-        <v>5638.145999999997</v>
+        <v>5435.8863999999994</v>
       </c>
       <c r="AE5" s="7">
-        <f>AE3*0.34</f>
-        <v>6415.5603680000004</v>
+        <f>AE3*0.32</f>
+        <v>5872.6804480000001</v>
       </c>
       <c r="AF5" s="7">
-        <f>AF3*0.35</f>
-        <v>7132.5935856000006</v>
+        <f>AF3*0.33</f>
+        <v>6419.5738147200009</v>
       </c>
       <c r="AG5" s="7">
-        <f>AG3*0.36</f>
-        <v>7849.9287119232013</v>
+        <f t="shared" ref="AG5:AN5" si="4">AG3*0.33</f>
+        <v>6740.5525054560021</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" ref="AH5:AN5" si="4">AH3*0.36</f>
-        <v>8320.9244346385931</v>
+        <f t="shared" si="4"/>
+        <v>7010.1746056742422</v>
       </c>
       <c r="AI5" s="7">
         <f t="shared" si="4"/>
-        <v>8736.970656370524</v>
+        <v>7220.4798438444695</v>
       </c>
       <c r="AJ5" s="7">
         <f t="shared" si="4"/>
-        <v>9173.819189189051</v>
+        <v>7437.0942391598028</v>
       </c>
       <c r="AK5" s="7">
         <f t="shared" si="4"/>
-        <v>9540.7719567566128</v>
+        <v>7660.2070663345967</v>
       </c>
       <c r="AL5" s="7">
         <f t="shared" si="4"/>
-        <v>9826.9951154593109</v>
+        <v>7890.0132783246354</v>
       </c>
       <c r="AM5" s="7">
         <f t="shared" si="4"/>
-        <v>10023.535017768498</v>
+        <v>8126.7136766743752</v>
       </c>
       <c r="AN5" s="7">
         <f t="shared" si="4"/>
-        <v>10224.005718123868</v>
+        <v>8370.5150869746067</v>
       </c>
     </row>
     <row r="6" spans="1:149" x14ac:dyDescent="0.3">
@@ -1428,8 +1427,7 @@
         <v>415</v>
       </c>
       <c r="U6" s="2">
-        <f>Q6*1.1</f>
-        <v>376.20000000000005</v>
+        <v>309</v>
       </c>
       <c r="V6" s="2">
         <f>R6*1.12</f>
@@ -1453,47 +1451,47 @@
       </c>
       <c r="AD6" s="2">
         <f>SUM(S6:V6)</f>
-        <v>1591.3200000000002</v>
+        <v>1524.1200000000001</v>
       </c>
       <c r="AE6" s="2">
         <f>AD6*1.04</f>
-        <v>1654.9728000000002</v>
+        <v>1585.0848000000001</v>
       </c>
       <c r="AF6" s="2">
-        <f t="shared" ref="AF6:AN6" si="5">AE6*1.02</f>
-        <v>1688.0722560000004</v>
+        <f>AE6*1.03</f>
+        <v>1632.6373440000002</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" si="5"/>
-        <v>1721.8337011200003</v>
+        <f t="shared" ref="AF6:AN6" si="5">AF6*1.02</f>
+        <v>1665.2900908800002</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="5"/>
-        <v>1756.2703751424003</v>
+        <v>1698.5958926976002</v>
       </c>
       <c r="AI6" s="2">
         <f t="shared" si="5"/>
-        <v>1791.3957826452483</v>
+        <v>1732.5678105515522</v>
       </c>
       <c r="AJ6" s="2">
         <f t="shared" si="5"/>
-        <v>1827.2236982981533</v>
+        <v>1767.2191667625832</v>
       </c>
       <c r="AK6" s="2">
         <f t="shared" si="5"/>
-        <v>1863.7681722641164</v>
+        <v>1802.5635500978349</v>
       </c>
       <c r="AL6" s="2">
         <f t="shared" si="5"/>
-        <v>1901.0435357093988</v>
+        <v>1838.6148210997917</v>
       </c>
       <c r="AM6" s="2">
         <f t="shared" si="5"/>
-        <v>1939.0644064235869</v>
+        <v>1875.3871175217876</v>
       </c>
       <c r="AN6" s="2">
         <f t="shared" si="5"/>
-        <v>1977.8456945520586</v>
+        <v>1912.8948598722234</v>
       </c>
     </row>
     <row r="7" spans="1:149" x14ac:dyDescent="0.3">
@@ -1555,12 +1553,11 @@
         <v>364</v>
       </c>
       <c r="U7" s="2">
-        <f>U3*0.09</f>
-        <v>391.22280000000001</v>
+        <v>349</v>
       </c>
       <c r="V7" s="2">
         <f>V3*0.09</f>
-        <v>412.32240000000002</v>
+        <v>404.68680000000001</v>
       </c>
       <c r="Z7" s="2">
         <f>SUM(C7:F7)</f>
@@ -1580,47 +1577,47 @@
       </c>
       <c r="AD7" s="2">
         <f>SUM(S7:V7)</f>
-        <v>1481.5452</v>
+        <v>1431.6867999999999</v>
       </c>
       <c r="AE7" s="2">
         <f>AE3*0.09</f>
-        <v>1698.236568</v>
+        <v>1651.691376</v>
       </c>
       <c r="AF7" s="2">
         <f t="shared" ref="AF7:AN7" si="6">AF3*0.09</f>
-        <v>1834.0954934400002</v>
+        <v>1750.7928585600002</v>
       </c>
       <c r="AG7" s="2">
         <f t="shared" si="6"/>
-        <v>1962.4821779808003</v>
+        <v>1838.3325014880004</v>
       </c>
       <c r="AH7" s="2">
         <f t="shared" si="6"/>
-        <v>2080.2311086596483</v>
+        <v>1911.8658015475203</v>
       </c>
       <c r="AI7" s="2">
         <f t="shared" si="6"/>
-        <v>2184.242664092631</v>
+        <v>1969.2217755939459</v>
       </c>
       <c r="AJ7" s="2">
         <f t="shared" si="6"/>
-        <v>2293.4547972972628</v>
+        <v>2028.2984288617643</v>
       </c>
       <c r="AK7" s="2">
         <f t="shared" si="6"/>
-        <v>2385.1929891891532</v>
+        <v>2089.1473817276174</v>
       </c>
       <c r="AL7" s="2">
         <f t="shared" si="6"/>
-        <v>2456.7487788648277</v>
+        <v>2151.8218031794459</v>
       </c>
       <c r="AM7" s="2">
         <f t="shared" si="6"/>
-        <v>2505.8837544421244</v>
+        <v>2216.3764572748296</v>
       </c>
       <c r="AN7" s="2">
         <f t="shared" si="6"/>
-        <v>2556.001429530967</v>
+        <v>2282.8677509930744</v>
       </c>
     </row>
     <row r="8" spans="1:149" x14ac:dyDescent="0.3">
@@ -1682,8 +1679,7 @@
         <v>135</v>
       </c>
       <c r="U8" s="2">
-        <f>Q8*1.08</f>
-        <v>120.96000000000001</v>
+        <v>111</v>
       </c>
       <c r="V8" s="2">
         <f>R8*1.14</f>
@@ -1707,47 +1703,47 @@
       </c>
       <c r="AD8" s="2">
         <f>SUM(S8:V8)</f>
-        <v>519.04</v>
+        <v>509.08</v>
       </c>
       <c r="AE8" s="2">
         <f>AD8*1.05</f>
-        <v>544.99199999999996</v>
+        <v>534.53399999999999</v>
       </c>
       <c r="AF8" s="2">
         <f>AE8*1.03</f>
-        <v>561.34176000000002</v>
+        <v>550.57002</v>
       </c>
       <c r="AG8" s="2">
         <f t="shared" ref="AG8:AH8" si="7">AF8*1.02</f>
-        <v>572.5685952</v>
+        <v>561.58142039999996</v>
       </c>
       <c r="AH8" s="2">
         <f t="shared" si="7"/>
-        <v>584.01996710399999</v>
+        <v>572.81304880799996</v>
       </c>
       <c r="AI8" s="2">
         <f>AH8*1.01</f>
-        <v>589.86016677503994</v>
+        <v>578.54117929607992</v>
       </c>
       <c r="AJ8" s="2">
         <f t="shared" ref="AJ8:AN8" si="8">AI8*1.01</f>
-        <v>595.75876844279037</v>
+        <v>584.32659108904068</v>
       </c>
       <c r="AK8" s="2">
         <f t="shared" si="8"/>
-        <v>601.71635612721832</v>
+        <v>590.16985699993108</v>
       </c>
       <c r="AL8" s="2">
         <f t="shared" si="8"/>
-        <v>607.73351968849056</v>
+        <v>596.07155556993041</v>
       </c>
       <c r="AM8" s="2">
         <f t="shared" si="8"/>
-        <v>613.81085488537542</v>
+        <v>602.03227112562968</v>
       </c>
       <c r="AN8" s="2">
         <f t="shared" si="8"/>
-        <v>619.9489634342292</v>
+        <v>608.05259383688599</v>
       </c>
     </row>
     <row r="9" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1829,11 +1825,11 @@
       </c>
       <c r="U9" s="7">
         <f t="shared" si="10"/>
-        <v>546.10079999999994</v>
+        <v>582</v>
       </c>
       <c r="V9" s="7">
         <f t="shared" si="10"/>
-        <v>585.14000000000033</v>
+        <v>473.9996000000001</v>
       </c>
       <c r="Z9" s="7">
         <f>Z5-SUM(Z6:Z8)</f>
@@ -1853,47 +1849,47 @@
       </c>
       <c r="AD9" s="7">
         <f>AD5-SUM(AD6:AD8)</f>
-        <v>2046.2407999999969</v>
+        <v>1970.9995999999992</v>
       </c>
       <c r="AE9" s="7">
         <f t="shared" ref="AE9:AN9" si="11">AE5-SUM(AE6:AE8)</f>
-        <v>2517.3590000000004</v>
+        <v>2101.3702719999997</v>
       </c>
       <c r="AF9" s="7">
         <f t="shared" si="11"/>
-        <v>3049.0840761600002</v>
+        <v>2485.5735921600003</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="11"/>
-        <v>3593.0442376224</v>
+        <v>2675.3484926880019</v>
       </c>
       <c r="AH9" s="7">
         <f t="shared" si="11"/>
-        <v>3900.4029837325443</v>
+        <v>2826.8998626211223</v>
       </c>
       <c r="AI9" s="7">
         <f t="shared" si="11"/>
-        <v>4171.4720428576047</v>
+        <v>2940.1490784028911</v>
       </c>
       <c r="AJ9" s="7">
         <f t="shared" si="11"/>
-        <v>4457.3819251508448</v>
+        <v>3057.2500524464149</v>
       </c>
       <c r="AK9" s="7">
         <f t="shared" si="11"/>
-        <v>4690.094439176125</v>
+        <v>3178.3262775092135</v>
       </c>
       <c r="AL9" s="7">
         <f t="shared" si="11"/>
-        <v>4861.4692811965942</v>
+        <v>3303.5050984754671</v>
       </c>
       <c r="AM9" s="7">
         <f t="shared" si="11"/>
-        <v>4964.776002017411</v>
+        <v>3432.9178307521288</v>
       </c>
       <c r="AN9" s="7">
         <f t="shared" si="11"/>
-        <v>5070.2096306066132</v>
+        <v>3566.6998822724236</v>
       </c>
     </row>
     <row r="10" spans="1:149" x14ac:dyDescent="0.3">
@@ -1955,11 +1951,10 @@
         <v>-89</v>
       </c>
       <c r="U10" s="2">
-        <f t="shared" ref="U10:V11" si="12">Q10*1.02</f>
-        <v>-67.320000000000007</v>
+        <v>-262</v>
       </c>
       <c r="V10" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="U10:V11" si="12">R10*1.02</f>
         <v>-129.54</v>
       </c>
       <c r="Z10" s="2">
@@ -1980,47 +1975,47 @@
       </c>
       <c r="AD10" s="2">
         <f>SUM(S10:V10)</f>
-        <v>-356.86</v>
+        <v>-551.54</v>
       </c>
       <c r="AE10" s="2">
         <f>AD10*1.03</f>
-        <v>-367.56580000000002</v>
+        <v>-568.08619999999996</v>
       </c>
       <c r="AF10" s="2">
         <f t="shared" ref="AF10:AN10" si="13">AE10*1.03</f>
-        <v>-378.59277400000002</v>
+        <v>-585.12878599999999</v>
       </c>
       <c r="AG10" s="2">
         <f t="shared" si="13"/>
-        <v>-389.95055722000001</v>
+        <v>-602.68264957999997</v>
       </c>
       <c r="AH10" s="2">
         <f t="shared" si="13"/>
-        <v>-401.64907393660002</v>
+        <v>-620.76312906739997</v>
       </c>
       <c r="AI10" s="2">
         <f t="shared" si="13"/>
-        <v>-413.69854615469802</v>
+        <v>-639.38602293942199</v>
       </c>
       <c r="AJ10" s="2">
         <f t="shared" si="13"/>
-        <v>-426.10950253933896</v>
+        <v>-658.56760362760463</v>
       </c>
       <c r="AK10" s="2">
         <f t="shared" si="13"/>
-        <v>-438.89278761551913</v>
+        <v>-678.32463173643282</v>
       </c>
       <c r="AL10" s="2">
         <f t="shared" si="13"/>
-        <v>-452.05957124398469</v>
+        <v>-698.67437068852587</v>
       </c>
       <c r="AM10" s="2">
         <f t="shared" si="13"/>
-        <v>-465.62135838130422</v>
+        <v>-719.63460180918162</v>
       </c>
       <c r="AN10" s="2">
         <f t="shared" si="13"/>
-        <v>-479.58999913274334</v>
+        <v>-741.22363986345704</v>
       </c>
     </row>
     <row r="11" spans="1:149" x14ac:dyDescent="0.3">
@@ -2082,8 +2077,7 @@
         <v>447</v>
       </c>
       <c r="U11" s="2">
-        <f t="shared" si="12"/>
-        <v>124.44</v>
+        <v>17</v>
       </c>
       <c r="V11" s="2">
         <f t="shared" si="12"/>
@@ -2107,47 +2101,47 @@
       </c>
       <c r="AD11" s="2">
         <f>SUM(S11:V11)</f>
-        <v>930.54000000000008</v>
+        <v>823.1</v>
       </c>
       <c r="AE11" s="2">
         <f t="shared" ref="AE11:AN11" si="14">AD11*1.01</f>
-        <v>939.84540000000004</v>
+        <v>831.33100000000002</v>
       </c>
       <c r="AF11" s="2">
         <f t="shared" si="14"/>
-        <v>949.24385400000006</v>
+        <v>839.64431000000002</v>
       </c>
       <c r="AG11" s="2">
         <f t="shared" si="14"/>
-        <v>958.73629254000002</v>
+        <v>848.04075310000007</v>
       </c>
       <c r="AH11" s="2">
         <f t="shared" si="14"/>
-        <v>968.32365546540007</v>
+        <v>856.52116063100004</v>
       </c>
       <c r="AI11" s="2">
         <f t="shared" si="14"/>
-        <v>978.00689202005412</v>
+        <v>865.08637223731</v>
       </c>
       <c r="AJ11" s="2">
         <f t="shared" si="14"/>
-        <v>987.78696094025463</v>
+        <v>873.73723595968306</v>
       </c>
       <c r="AK11" s="2">
         <f t="shared" si="14"/>
-        <v>997.66483054965715</v>
+        <v>882.47460831927992</v>
       </c>
       <c r="AL11" s="2">
         <f t="shared" si="14"/>
-        <v>1007.6414788551538</v>
+        <v>891.29935440247277</v>
       </c>
       <c r="AM11" s="2">
         <f t="shared" si="14"/>
-        <v>1017.7178936437053</v>
+        <v>900.21234794649752</v>
       </c>
       <c r="AN11" s="2">
         <f t="shared" si="14"/>
-        <v>1027.8950725801424</v>
+        <v>909.21447142596253</v>
       </c>
     </row>
     <row r="12" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2229,11 +2223,11 @@
       </c>
       <c r="U12" s="7">
         <f t="shared" si="16"/>
-        <v>488.98079999999999</v>
+        <v>827</v>
       </c>
       <c r="V12" s="7">
         <f t="shared" si="16"/>
-        <v>607.58000000000027</v>
+        <v>496.43960000000004</v>
       </c>
       <c r="Z12" s="7">
         <f>Z9-Z10-Z11</f>
@@ -2253,47 +2247,47 @@
       </c>
       <c r="AD12" s="7">
         <f>AD9-AD10-AD11</f>
-        <v>1472.560799999997</v>
+        <v>1699.4395999999992</v>
       </c>
       <c r="AE12" s="7">
         <f t="shared" ref="AE12:AN12" si="17">AE9-AE10-AE11</f>
-        <v>1945.0794000000001</v>
+        <v>1838.1254719999997</v>
       </c>
       <c r="AF12" s="7">
         <f t="shared" si="17"/>
-        <v>2478.4329961600006</v>
+        <v>2231.0580681599999</v>
       </c>
       <c r="AG12" s="7">
         <f t="shared" si="17"/>
-        <v>3024.2585023024003</v>
+        <v>2429.9903891680019</v>
       </c>
       <c r="AH12" s="7">
         <f t="shared" si="17"/>
-        <v>3333.7284022037443</v>
+        <v>2591.1418310575223</v>
       </c>
       <c r="AI12" s="7">
         <f t="shared" si="17"/>
-        <v>3607.1636969922488</v>
+        <v>2714.4487291050032</v>
       </c>
       <c r="AJ12" s="7">
         <f t="shared" si="17"/>
-        <v>3895.704466749929</v>
+        <v>2842.0804201143364</v>
       </c>
       <c r="AK12" s="7">
         <f t="shared" si="17"/>
-        <v>4131.322396241987</v>
+        <v>2974.1763009263664</v>
       </c>
       <c r="AL12" s="7">
         <f t="shared" si="17"/>
-        <v>4305.8873735854249</v>
+        <v>3110.8801147615204</v>
       </c>
       <c r="AM12" s="7">
         <f t="shared" si="17"/>
-        <v>4412.6794667550093</v>
+        <v>3252.3400846148129</v>
       </c>
       <c r="AN12" s="7">
         <f t="shared" si="17"/>
-        <v>4521.9045571592142</v>
+        <v>3398.7090507099178</v>
       </c>
     </row>
     <row r="13" spans="1:149" x14ac:dyDescent="0.3">
@@ -2355,12 +2349,11 @@
         <v>134</v>
       </c>
       <c r="U13" s="2">
-        <f t="shared" ref="U13:V13" si="18">U12*0.25</f>
-        <v>122.2452</v>
+        <v>-72</v>
       </c>
       <c r="V13" s="2">
-        <f t="shared" si="18"/>
-        <v>151.89500000000007</v>
+        <f t="shared" ref="U13:V13" si="18">V12*0.25</f>
+        <v>124.10990000000001</v>
       </c>
       <c r="Z13" s="2">
         <f>SUM(C13:F13)</f>
@@ -2380,47 +2373,47 @@
       </c>
       <c r="AD13" s="2">
         <f>SUM(S13:V13)</f>
-        <v>511.14020000000005</v>
+        <v>289.10990000000004</v>
       </c>
       <c r="AE13" s="2">
         <f>AE12*0.25</f>
-        <v>486.26985000000002</v>
+        <v>459.53136799999993</v>
       </c>
       <c r="AF13" s="2">
         <f t="shared" ref="AF13:AN13" si="19">AF12*0.25</f>
-        <v>619.60824904000015</v>
+        <v>557.76451703999999</v>
       </c>
       <c r="AG13" s="2">
         <f t="shared" si="19"/>
-        <v>756.06462557560008</v>
+        <v>607.49759729200048</v>
       </c>
       <c r="AH13" s="2">
         <f t="shared" si="19"/>
-        <v>833.43210055093607</v>
+        <v>647.78545776438057</v>
       </c>
       <c r="AI13" s="2">
         <f t="shared" si="19"/>
-        <v>901.7909242480622</v>
+        <v>678.61218227625079</v>
       </c>
       <c r="AJ13" s="2">
         <f t="shared" si="19"/>
-        <v>973.92611668748225</v>
+        <v>710.52010502858411</v>
       </c>
       <c r="AK13" s="2">
         <f t="shared" si="19"/>
-        <v>1032.8305990604968</v>
+        <v>743.54407523159159</v>
       </c>
       <c r="AL13" s="2">
         <f t="shared" si="19"/>
-        <v>1076.4718433963562</v>
+        <v>777.7200286903801</v>
       </c>
       <c r="AM13" s="2">
         <f t="shared" si="19"/>
-        <v>1103.1698666887523</v>
+        <v>813.08502115370322</v>
       </c>
       <c r="AN13" s="2">
         <f t="shared" si="19"/>
-        <v>1130.4761392898035</v>
+        <v>849.67726267747946</v>
       </c>
     </row>
     <row r="14" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2502,11 +2495,11 @@
       </c>
       <c r="U14" s="7">
         <f t="shared" si="22"/>
-        <v>366.73559999999998</v>
+        <v>899</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="22"/>
-        <v>455.68500000000017</v>
+        <v>372.3297</v>
       </c>
       <c r="Z14" s="7">
         <f>Z12-Z13</f>
@@ -2526,483 +2519,483 @@
       </c>
       <c r="AD14" s="7">
         <f>AD12-AD13</f>
-        <v>961.42059999999697</v>
+        <v>1410.3296999999993</v>
       </c>
       <c r="AE14" s="7">
         <f t="shared" ref="AE14:AN14" si="23">AE12-AE13</f>
-        <v>1458.8095499999999</v>
+        <v>1378.5941039999998</v>
       </c>
       <c r="AF14" s="7">
         <f t="shared" si="23"/>
-        <v>1858.8247471200004</v>
+        <v>1673.2935511199998</v>
       </c>
       <c r="AG14" s="7">
         <f t="shared" si="23"/>
-        <v>2268.1938767268002</v>
+        <v>1822.4927918760013</v>
       </c>
       <c r="AH14" s="7">
         <f t="shared" si="23"/>
-        <v>2500.2963016528083</v>
+        <v>1943.3563732931416</v>
       </c>
       <c r="AI14" s="7">
         <f t="shared" si="23"/>
-        <v>2705.3727727441865</v>
+        <v>2035.8365468287525</v>
       </c>
       <c r="AJ14" s="7">
         <f t="shared" si="23"/>
-        <v>2921.7783500624469</v>
+        <v>2131.5603150857523</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" si="23"/>
-        <v>3098.4917971814903</v>
+        <v>2230.6322256947747</v>
       </c>
       <c r="AL14" s="7">
         <f t="shared" si="23"/>
-        <v>3229.4155301890687</v>
+        <v>2333.1600860711405</v>
       </c>
       <c r="AM14" s="7">
         <f t="shared" si="23"/>
-        <v>3309.509600066257</v>
+        <v>2439.2550634611098</v>
       </c>
       <c r="AN14" s="7">
         <f t="shared" si="23"/>
-        <v>3391.4284178694106</v>
+        <v>2549.0317880324383</v>
       </c>
       <c r="AO14" s="1">
         <f>AN14*(1+$AQ$19)</f>
-        <v>3357.5141336907163</v>
+        <v>2523.541470152114</v>
       </c>
       <c r="AP14" s="1">
         <f t="shared" ref="AP14:DA14" si="24">AO14*(1+$AQ$19)</f>
-        <v>3323.9389923538092</v>
+        <v>2498.3060554505928</v>
       </c>
       <c r="AQ14" s="1">
         <f t="shared" si="24"/>
-        <v>3290.6996024302712</v>
+        <v>2473.322994896087</v>
       </c>
       <c r="AR14" s="1">
         <f t="shared" si="24"/>
-        <v>3257.7926064059684</v>
+        <v>2448.5897649471262</v>
       </c>
       <c r="AS14" s="1">
         <f t="shared" si="24"/>
-        <v>3225.2146803419087</v>
+        <v>2424.1038672976551</v>
       </c>
       <c r="AT14" s="1">
         <f t="shared" si="24"/>
-        <v>3192.9625335384894</v>
+        <v>2399.8628286246785</v>
       </c>
       <c r="AU14" s="1">
         <f t="shared" si="24"/>
-        <v>3161.0329082031044</v>
+        <v>2375.8642003384316</v>
       </c>
       <c r="AV14" s="1">
         <f t="shared" si="24"/>
-        <v>3129.4225791210733</v>
+        <v>2352.1055583350471</v>
       </c>
       <c r="AW14" s="1">
         <f t="shared" si="24"/>
-        <v>3098.1283533298624</v>
+        <v>2328.5845027516966</v>
       </c>
       <c r="AX14" s="1">
         <f t="shared" si="24"/>
-        <v>3067.1470697965638</v>
+        <v>2305.2986577241795</v>
       </c>
       <c r="AY14" s="1">
         <f t="shared" si="24"/>
-        <v>3036.4755990985982</v>
+        <v>2282.2456711469376</v>
       </c>
       <c r="AZ14" s="1">
         <f t="shared" si="24"/>
-        <v>3006.1108431076123</v>
+        <v>2259.4232144354683</v>
       </c>
       <c r="BA14" s="1">
         <f t="shared" si="24"/>
-        <v>2976.049734676536</v>
+        <v>2236.8289822911133</v>
       </c>
       <c r="BB14" s="1">
         <f t="shared" si="24"/>
-        <v>2946.2892373297705</v>
+        <v>2214.4606924682021</v>
       </c>
       <c r="BC14" s="1">
         <f t="shared" si="24"/>
-        <v>2916.8263449564729</v>
+        <v>2192.3160855435199</v>
       </c>
       <c r="BD14" s="1">
         <f t="shared" si="24"/>
-        <v>2887.6580815069083</v>
+        <v>2170.3929246880848</v>
       </c>
       <c r="BE14" s="1">
         <f t="shared" si="24"/>
-        <v>2858.781500691839</v>
+        <v>2148.688995441204</v>
       </c>
       <c r="BF14" s="1">
         <f t="shared" si="24"/>
-        <v>2830.1936856849206</v>
+        <v>2127.2021054867919</v>
       </c>
       <c r="BG14" s="1">
         <f t="shared" si="24"/>
-        <v>2801.8917488280713</v>
+        <v>2105.9300844319241</v>
       </c>
       <c r="BH14" s="1">
         <f t="shared" si="24"/>
-        <v>2773.8728313397905</v>
+        <v>2084.8707835876048</v>
       </c>
       <c r="BI14" s="1">
         <f t="shared" si="24"/>
-        <v>2746.1341030263925</v>
+        <v>2064.0220757517286</v>
       </c>
       <c r="BJ14" s="1">
         <f t="shared" si="24"/>
-        <v>2718.6727619961284</v>
+        <v>2043.3818549942114</v>
       </c>
       <c r="BK14" s="1">
         <f t="shared" si="24"/>
-        <v>2691.486034376167</v>
+        <v>2022.9480364442693</v>
       </c>
       <c r="BL14" s="1">
         <f t="shared" si="24"/>
-        <v>2664.5711740324055</v>
+        <v>2002.7185560798266</v>
       </c>
       <c r="BM14" s="1">
         <f t="shared" si="24"/>
-        <v>2637.9254622920812</v>
+        <v>1982.6913705190284</v>
       </c>
       <c r="BN14" s="1">
         <f t="shared" si="24"/>
-        <v>2611.5462076691601</v>
+        <v>1962.8644568138382</v>
       </c>
       <c r="BO14" s="1">
         <f t="shared" si="24"/>
-        <v>2585.4307455924686</v>
+        <v>1943.2358122456997</v>
       </c>
       <c r="BP14" s="1">
         <f t="shared" si="24"/>
-        <v>2559.5764381365439</v>
+        <v>1923.8034541232425</v>
       </c>
       <c r="BQ14" s="1">
         <f t="shared" si="24"/>
-        <v>2533.9806737551785</v>
+        <v>1904.56541958201</v>
       </c>
       <c r="BR14" s="1">
         <f t="shared" si="24"/>
-        <v>2508.6408670176265</v>
+        <v>1885.5197653861899</v>
       </c>
       <c r="BS14" s="1">
         <f t="shared" si="24"/>
-        <v>2483.5544583474502</v>
+        <v>1866.6645677323279</v>
       </c>
       <c r="BT14" s="1">
         <f t="shared" si="24"/>
-        <v>2458.7189137639757</v>
+        <v>1847.9979220550047</v>
       </c>
       <c r="BU14" s="1">
         <f t="shared" si="24"/>
-        <v>2434.1317246263361</v>
+        <v>1829.5179428344545</v>
       </c>
       <c r="BV14" s="1">
         <f t="shared" si="24"/>
-        <v>2409.7904073800728</v>
+        <v>1811.2227634061101</v>
       </c>
       <c r="BW14" s="1">
         <f t="shared" si="24"/>
-        <v>2385.6925033062721</v>
+        <v>1793.1105357720489</v>
       </c>
       <c r="BX14" s="1">
         <f t="shared" si="24"/>
-        <v>2361.8355782732092</v>
+        <v>1775.1794304143284</v>
       </c>
       <c r="BY14" s="1">
         <f t="shared" si="24"/>
-        <v>2338.2172224904771</v>
+        <v>1757.4276361101852</v>
       </c>
       <c r="BZ14" s="1">
         <f t="shared" si="24"/>
-        <v>2314.8350502655721</v>
+        <v>1739.8533597490832</v>
       </c>
       <c r="CA14" s="1">
         <f t="shared" si="24"/>
-        <v>2291.6866997629163</v>
+        <v>1722.4548261515924</v>
       </c>
       <c r="CB14" s="1">
         <f t="shared" si="24"/>
-        <v>2268.769832765287</v>
+        <v>1705.2302778900764</v>
       </c>
       <c r="CC14" s="1">
         <f t="shared" si="24"/>
-        <v>2246.0821344376341</v>
+        <v>1688.1779751111756</v>
       </c>
       <c r="CD14" s="1">
         <f t="shared" si="24"/>
-        <v>2223.6213130932579</v>
+        <v>1671.2961953600638</v>
       </c>
       <c r="CE14" s="1">
         <f t="shared" si="24"/>
-        <v>2201.3850999623251</v>
+        <v>1654.5832334064633</v>
       </c>
       <c r="CF14" s="1">
         <f t="shared" si="24"/>
-        <v>2179.3712489627019</v>
+        <v>1638.0374010723986</v>
       </c>
       <c r="CG14" s="1">
         <f t="shared" si="24"/>
-        <v>2157.5775364730748</v>
+        <v>1621.6570270616746</v>
       </c>
       <c r="CH14" s="1">
         <f t="shared" si="24"/>
-        <v>2136.001761108344</v>
+        <v>1605.4404567910578</v>
       </c>
       <c r="CI14" s="1">
         <f t="shared" si="24"/>
-        <v>2114.6417434972604</v>
+        <v>1589.3860522231473</v>
       </c>
       <c r="CJ14" s="1">
         <f t="shared" si="24"/>
-        <v>2093.4953260622879</v>
+        <v>1573.4921917009158</v>
       </c>
       <c r="CK14" s="1">
         <f t="shared" si="24"/>
-        <v>2072.5603728016649</v>
+        <v>1557.7572697839066</v>
       </c>
       <c r="CL14" s="1">
         <f t="shared" si="24"/>
-        <v>2051.8347690736482</v>
+        <v>1542.1796970860676</v>
       </c>
       <c r="CM14" s="1">
         <f t="shared" si="24"/>
-        <v>2031.3164213829118</v>
+        <v>1526.7579001152069</v>
       </c>
       <c r="CN14" s="1">
         <f t="shared" si="24"/>
-        <v>2011.0032571690826</v>
+        <v>1511.4903211140547</v>
       </c>
       <c r="CO14" s="1">
         <f t="shared" si="24"/>
-        <v>1990.8932245973917</v>
+        <v>1496.3754179029143</v>
       </c>
       <c r="CP14" s="1">
         <f t="shared" si="24"/>
-        <v>1970.9842923514177</v>
+        <v>1481.4116637238851</v>
       </c>
       <c r="CQ14" s="1">
         <f t="shared" si="24"/>
-        <v>1951.2744494279036</v>
+        <v>1466.5975470866463</v>
       </c>
       <c r="CR14" s="1">
         <f t="shared" si="24"/>
-        <v>1931.7617049336245</v>
+        <v>1451.9315716157798</v>
       </c>
       <c r="CS14" s="1">
         <f t="shared" si="24"/>
-        <v>1912.4440878842884</v>
+        <v>1437.4122558996221</v>
       </c>
       <c r="CT14" s="1">
         <f t="shared" si="24"/>
-        <v>1893.3196470054454</v>
+        <v>1423.0381333406258</v>
       </c>
       <c r="CU14" s="1">
         <f t="shared" si="24"/>
-        <v>1874.3864505353908</v>
+        <v>1408.8077520072195</v>
       </c>
       <c r="CV14" s="1">
         <f t="shared" si="24"/>
-        <v>1855.6425860300369</v>
+        <v>1394.7196744871474</v>
       </c>
       <c r="CW14" s="1">
         <f t="shared" si="24"/>
-        <v>1837.0861601697366</v>
+        <v>1380.7724777422759</v>
       </c>
       <c r="CX14" s="1">
         <f t="shared" si="24"/>
-        <v>1818.7152985680391</v>
+        <v>1366.9647529648532</v>
       </c>
       <c r="CY14" s="1">
         <f t="shared" si="24"/>
-        <v>1800.5281455823588</v>
+        <v>1353.2951054352047</v>
       </c>
       <c r="CZ14" s="1">
         <f t="shared" si="24"/>
-        <v>1782.5228641265351</v>
+        <v>1339.7621543808527</v>
       </c>
       <c r="DA14" s="1">
         <f t="shared" si="24"/>
-        <v>1764.6976354852698</v>
+        <v>1326.3645328370442</v>
       </c>
       <c r="DB14" s="1">
         <f t="shared" ref="DB14:ES14" si="25">DA14*(1+$AQ$19)</f>
-        <v>1747.050659130417</v>
+        <v>1313.1008875086736</v>
       </c>
       <c r="DC14" s="1">
         <f t="shared" si="25"/>
-        <v>1729.5801525391128</v>
+        <v>1299.9698786335869</v>
       </c>
       <c r="DD14" s="1">
         <f t="shared" si="25"/>
-        <v>1712.2843510137216</v>
+        <v>1286.9701798472511</v>
       </c>
       <c r="DE14" s="1">
         <f t="shared" si="25"/>
-        <v>1695.1615075035843</v>
+        <v>1274.1004780487785</v>
       </c>
       <c r="DF14" s="1">
         <f t="shared" si="25"/>
-        <v>1678.2098924285485</v>
+        <v>1261.3594732682907</v>
       </c>
       <c r="DG14" s="1">
         <f t="shared" si="25"/>
-        <v>1661.427793504263</v>
+        <v>1248.7458785356077</v>
       </c>
       <c r="DH14" s="1">
         <f t="shared" si="25"/>
-        <v>1644.8135155692205</v>
+        <v>1236.2584197502517</v>
       </c>
       <c r="DI14" s="1">
         <f t="shared" si="25"/>
-        <v>1628.3653804135283</v>
+        <v>1223.8958355527493</v>
       </c>
       <c r="DJ14" s="1">
         <f t="shared" si="25"/>
-        <v>1612.0817266093929</v>
+        <v>1211.6568771972218</v>
       </c>
       <c r="DK14" s="1">
         <f t="shared" si="25"/>
-        <v>1595.9609093432989</v>
+        <v>1199.5403084252496</v>
       </c>
       <c r="DL14" s="1">
         <f t="shared" si="25"/>
-        <v>1580.0013002498658</v>
+        <v>1187.544905340997</v>
       </c>
       <c r="DM14" s="1">
         <f t="shared" si="25"/>
-        <v>1564.2012872473672</v>
+        <v>1175.6694562875871</v>
       </c>
       <c r="DN14" s="1">
         <f t="shared" si="25"/>
-        <v>1548.5592743748934</v>
+        <v>1163.9127617247111</v>
       </c>
       <c r="DO14" s="1">
         <f t="shared" si="25"/>
-        <v>1533.0736816311446</v>
+        <v>1152.273634107464</v>
       </c>
       <c r="DP14" s="1">
         <f t="shared" si="25"/>
-        <v>1517.7429448148332</v>
+        <v>1140.7508977663892</v>
       </c>
       <c r="DQ14" s="1">
         <f t="shared" si="25"/>
-        <v>1502.5655153666848</v>
+        <v>1129.3433887887254</v>
       </c>
       <c r="DR14" s="1">
         <f t="shared" si="25"/>
-        <v>1487.5398602130181</v>
+        <v>1118.0499549008382</v>
       </c>
       <c r="DS14" s="1">
         <f t="shared" si="25"/>
-        <v>1472.6644616108879</v>
+        <v>1106.8694553518299</v>
       </c>
       <c r="DT14" s="1">
         <f t="shared" si="25"/>
-        <v>1457.937816994779</v>
+        <v>1095.8007607983116</v>
       </c>
       <c r="DU14" s="1">
         <f t="shared" si="25"/>
-        <v>1443.3584388248312</v>
+        <v>1084.8427531903285</v>
       </c>
       <c r="DV14" s="1">
         <f t="shared" si="25"/>
-        <v>1428.9248544365828</v>
+        <v>1073.9943256584252</v>
       </c>
       <c r="DW14" s="1">
         <f t="shared" si="25"/>
-        <v>1414.635605892217</v>
+        <v>1063.254382401841</v>
       </c>
       <c r="DX14" s="1">
         <f t="shared" si="25"/>
-        <v>1400.4892498332947</v>
+        <v>1052.6218385778225</v>
       </c>
       <c r="DY14" s="1">
         <f t="shared" si="25"/>
-        <v>1386.4843573349617</v>
+        <v>1042.0956201920442</v>
       </c>
       <c r="DZ14" s="1">
         <f t="shared" si="25"/>
-        <v>1372.6195137616121</v>
+        <v>1031.6746639901237</v>
       </c>
       <c r="EA14" s="1">
         <f t="shared" si="25"/>
-        <v>1358.893318623996</v>
+        <v>1021.3579173502225</v>
       </c>
       <c r="EB14" s="1">
         <f t="shared" si="25"/>
-        <v>1345.3043854377561</v>
+        <v>1011.1443381767202</v>
       </c>
       <c r="EC14" s="1">
         <f t="shared" si="25"/>
-        <v>1331.8513415833786</v>
+        <v>1001.032894794953</v>
       </c>
       <c r="ED14" s="1">
         <f t="shared" si="25"/>
-        <v>1318.5328281675447</v>
+        <v>991.02256584700342</v>
       </c>
       <c r="EE14" s="1">
         <f t="shared" si="25"/>
-        <v>1305.3474998858692</v>
+        <v>981.11234018853338</v>
       </c>
       <c r="EF14" s="1">
         <f t="shared" si="25"/>
-        <v>1292.2940248870104</v>
+        <v>971.30121678664807</v>
       </c>
       <c r="EG14" s="1">
         <f t="shared" si="25"/>
-        <v>1279.3710846381402</v>
+        <v>961.58820461878156</v>
       </c>
       <c r="EH14" s="1">
         <f t="shared" si="25"/>
-        <v>1266.5773737917589</v>
+        <v>951.97232257259373</v>
       </c>
       <c r="EI14" s="1">
         <f t="shared" si="25"/>
-        <v>1253.9116000538413</v>
+        <v>942.45259934686783</v>
       </c>
       <c r="EJ14" s="1">
         <f t="shared" si="25"/>
-        <v>1241.372484053303</v>
+        <v>933.02807335339912</v>
       </c>
       <c r="EK14" s="1">
         <f t="shared" si="25"/>
-        <v>1228.95875921277</v>
+        <v>923.69779261986514</v>
       </c>
       <c r="EL14" s="1">
         <f t="shared" si="25"/>
-        <v>1216.6691716206424</v>
+        <v>914.46081469366652</v>
       </c>
       <c r="EM14" s="1">
         <f t="shared" si="25"/>
-        <v>1204.5024799044359</v>
+        <v>905.31620654672986</v>
       </c>
       <c r="EN14" s="1">
         <f t="shared" si="25"/>
-        <v>1192.4574551053915</v>
+        <v>896.26304448126257</v>
       </c>
       <c r="EO14" s="1">
         <f t="shared" si="25"/>
-        <v>1180.5328805543377</v>
+        <v>887.30041403644998</v>
       </c>
       <c r="EP14" s="1">
         <f t="shared" si="25"/>
-        <v>1168.7275517487942</v>
+        <v>878.42740989608546</v>
       </c>
       <c r="EQ14" s="1">
         <f t="shared" si="25"/>
-        <v>1157.0402762313063</v>
+        <v>869.64313579712461</v>
       </c>
       <c r="ER14" s="1">
         <f t="shared" si="25"/>
-        <v>1145.4698734689932</v>
+        <v>860.94670443915334</v>
       </c>
       <c r="ES14" s="1">
         <f t="shared" si="25"/>
-        <v>1134.0151747343032</v>
+        <v>852.33723739476181</v>
       </c>
     </row>
     <row r="15" spans="1:149" x14ac:dyDescent="0.3">
@@ -3065,10 +3058,12 @@
         <v>205.4</v>
       </c>
       <c r="U15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="V15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="Z15" s="2">
         <v>200</v>
@@ -3084,37 +3079,48 @@
         <v>203.8</v>
       </c>
       <c r="AD15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AE15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AF15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AG15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AH15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AI15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AJ15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AK15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AL15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AM15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
       <c r="AN15" s="2">
-        <v>205.4</v>
+        <f>206</f>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:149" x14ac:dyDescent="0.3">
@@ -3195,11 +3201,11 @@
       </c>
       <c r="U16" s="8">
         <f t="shared" si="28"/>
-        <v>1.7854703018500486</v>
+        <v>4.3640776699029127</v>
       </c>
       <c r="V16" s="8">
         <f t="shared" si="28"/>
-        <v>2.2185248296007796</v>
+        <v>1.8074257281553399</v>
       </c>
       <c r="Z16" s="8">
         <f>Z14/Z15</f>
@@ -3219,47 +3225,47 @@
       </c>
       <c r="AD16" s="8">
         <f>AD14/AD15</f>
-        <v>4.6807234664069961</v>
+        <v>6.846260679611647</v>
       </c>
       <c r="AE16" s="8">
         <f t="shared" ref="AE16:AN16" si="29">AE14/AE15</f>
-        <v>7.102286027263875</v>
+        <v>6.6922043883495137</v>
       </c>
       <c r="AF16" s="8">
         <f t="shared" si="29"/>
-        <v>9.0497796841285307</v>
+        <v>8.1227842287378635</v>
       </c>
       <c r="AG16" s="8">
         <f t="shared" si="29"/>
-        <v>11.04281342125998</v>
+        <v>8.8470523877475795</v>
       </c>
       <c r="AH16" s="8">
         <f t="shared" si="29"/>
-        <v>12.172815490033146</v>
+        <v>9.4337688023938906</v>
       </c>
       <c r="AI16" s="8">
         <f t="shared" si="29"/>
-        <v>13.171240373632845</v>
+        <v>9.8827016836347212</v>
       </c>
       <c r="AJ16" s="8">
         <f t="shared" si="29"/>
-        <v>14.224821567976859</v>
+        <v>10.347380170319186</v>
       </c>
       <c r="AK16" s="8">
         <f t="shared" si="29"/>
-        <v>15.0851596746908</v>
+        <v>10.828311775217353</v>
       </c>
       <c r="AL16" s="8">
         <f t="shared" si="29"/>
-        <v>15.722568306665378</v>
+        <v>11.326019835296799</v>
       </c>
       <c r="AM16" s="8">
         <f t="shared" si="29"/>
-        <v>16.112510224275837</v>
+        <v>11.841043997384029</v>
       </c>
       <c r="AN16" s="8">
         <f t="shared" si="29"/>
-        <v>16.511336016890997</v>
+        <v>12.37394071860407</v>
       </c>
     </row>
     <row r="18" spans="2:43" x14ac:dyDescent="0.3">
@@ -3328,11 +3334,11 @@
       </c>
       <c r="U18" s="9">
         <f t="shared" ref="U18" si="34">U3/Q3-1</f>
-        <v>9.000000000000008E-2</v>
+        <v>7.1213640922768384E-2</v>
       </c>
       <c r="V18" s="9">
         <f t="shared" ref="V18" si="35">V3/R3-1</f>
-        <v>8.0000000000000071E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="X18" s="9"/>
       <c r="Y18" s="9" t="e">
@@ -3357,35 +3363,35 @@
       </c>
       <c r="AD18" s="9">
         <f t="shared" si="36"/>
-        <v>0.1045288075033497</v>
+        <v>9.4335481401135679E-2</v>
       </c>
       <c r="AE18" s="9">
         <f t="shared" si="36"/>
-        <v>9.000000000000008E-2</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AF18" s="9">
         <f t="shared" si="36"/>
-        <v>8.0000000000000071E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AG18" s="9">
         <f t="shared" si="36"/>
-        <v>7.0000000000000062E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH18" s="9">
         <f t="shared" si="36"/>
-        <v>6.0000000000000053E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI18" s="9">
         <f t="shared" si="36"/>
-        <v>5.0000000000000044E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ18" s="9">
         <f t="shared" si="36"/>
-        <v>5.0000000000000044E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK18" s="9">
         <f t="shared" si="36"/>
-        <v>4.0000000000000036E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL18" s="9">
         <f t="shared" si="36"/>
@@ -3393,11 +3399,11 @@
       </c>
       <c r="AM18" s="9">
         <f t="shared" si="36"/>
-        <v>2.0000000000000018E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN18" s="9">
         <f t="shared" si="36"/>
-        <v>2.0000000000000018E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
     </row>
     <row r="19" spans="2:43" x14ac:dyDescent="0.3">
@@ -3478,11 +3484,11 @@
       </c>
       <c r="U19" s="9">
         <f t="shared" si="39"/>
-        <v>0.33</v>
+        <v>0.31624531835205993</v>
       </c>
       <c r="V19" s="9">
         <f t="shared" si="39"/>
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="X19" s="9" t="e">
         <f t="shared" ref="X19:AN19" si="40">X5/X3</f>
@@ -3510,47 +3516,47 @@
       </c>
       <c r="AD19" s="9">
         <f t="shared" si="40"/>
-        <v>0.32569203432675098</v>
+        <v>0.31693321641463845</v>
       </c>
       <c r="AE19" s="9">
         <f t="shared" si="40"/>
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="AF19" s="9">
         <f t="shared" si="40"/>
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="AG19" s="9">
         <f t="shared" si="40"/>
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AH19" s="9">
         <f t="shared" si="40"/>
-        <v>0.35999999999999993</v>
+        <v>0.33</v>
       </c>
       <c r="AI19" s="9">
         <f t="shared" si="40"/>
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AJ19" s="9">
         <f t="shared" si="40"/>
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AK19" s="9">
         <f t="shared" si="40"/>
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AL19" s="9">
         <f t="shared" si="40"/>
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AM19" s="9">
         <f t="shared" si="40"/>
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" s="9">
         <f t="shared" si="40"/>
-        <v>0.36000000000000004</v>
+        <v>0.33</v>
       </c>
       <c r="AP19" t="s">
         <v>49</v>
@@ -3625,7 +3631,7 @@
       </c>
       <c r="U20" s="9">
         <f t="shared" ref="U20" si="45">U6/Q6-1</f>
-        <v>0.10000000000000009</v>
+        <v>-9.6491228070175405E-2</v>
       </c>
       <c r="V20" s="9">
         <f t="shared" ref="V20" si="46">V6/R6-1</f>
@@ -3654,7 +3660,7 @@
       </c>
       <c r="AD20" s="9">
         <f t="shared" si="47"/>
-        <v>7.0874831763122481E-2</v>
+        <v>2.5652759084791477E-2</v>
       </c>
       <c r="AE20" s="9">
         <f t="shared" si="47"/>
@@ -3662,7 +3668,7 @@
       </c>
       <c r="AF20" s="9">
         <f t="shared" si="47"/>
-        <v>2.0000000000000018E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG20" s="9">
         <f t="shared" si="47"/>
@@ -3781,7 +3787,7 @@
       </c>
       <c r="U21" s="9">
         <f t="shared" si="50"/>
-        <v>0.09</v>
+        <v>8.1694756554307121E-2</v>
       </c>
       <c r="V21" s="9">
         <f t="shared" si="50"/>
@@ -3813,7 +3819,7 @@
       </c>
       <c r="AD21" s="9">
         <f t="shared" si="51"/>
-        <v>8.5582649001113731E-2</v>
+        <v>8.347288170377902E-2</v>
       </c>
       <c r="AE21" s="9">
         <f t="shared" si="51"/>
@@ -3829,7 +3835,7 @@
       </c>
       <c r="AH21" s="9">
         <f t="shared" si="51"/>
-        <v>8.9999999999999983E-2</v>
+        <v>0.09</v>
       </c>
       <c r="AI21" s="9">
         <f t="shared" si="51"/>
@@ -3849,18 +3855,18 @@
       </c>
       <c r="AM21" s="9">
         <f t="shared" si="51"/>
-        <v>0.09</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="AN21" s="9">
         <f t="shared" si="51"/>
-        <v>9.0000000000000011E-2</v>
+        <v>0.09</v>
       </c>
       <c r="AP21" t="s">
         <v>51</v>
       </c>
       <c r="AQ21" s="2">
         <f>NPV(AQ20,AC14:ES14)</f>
-        <v>36216.724398892606</v>
+        <v>28493.182006877181</v>
       </c>
     </row>
     <row r="22" spans="2:43" x14ac:dyDescent="0.3">
@@ -3929,7 +3935,7 @@
       </c>
       <c r="U22" s="9">
         <f t="shared" ref="U22" si="56">U8/Q8-1</f>
-        <v>8.0000000000000071E-2</v>
+        <v>-8.9285714285713969E-3</v>
       </c>
       <c r="V22" s="9">
         <f t="shared" ref="V22" si="57">V8/R8-1</f>
@@ -3958,7 +3964,7 @@
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="58"/>
-        <v>7.9085239085239012E-2</v>
+        <v>5.8378378378378448E-2</v>
       </c>
       <c r="AE22" s="9">
         <f t="shared" si="58"/>
@@ -4005,7 +4011,7 @@
       </c>
       <c r="AQ22" s="2">
         <f>Main!D8</f>
-        <v>8832</v>
+        <v>10270</v>
       </c>
     </row>
     <row r="23" spans="2:43" x14ac:dyDescent="0.3">
@@ -4086,11 +4092,11 @@
       </c>
       <c r="U23" s="9">
         <f t="shared" si="61"/>
-        <v>0.12562936515969927</v>
+        <v>0.13623595505617977</v>
       </c>
       <c r="V23" s="9">
         <f t="shared" si="61"/>
-        <v>0.12772189917404445</v>
+        <v>0.10541476519619618</v>
       </c>
       <c r="X23" s="9" t="e">
         <f t="shared" ref="X23:AN23" si="62">X9/X3</f>
@@ -4118,54 +4124,54 @@
       </c>
       <c r="AD23" s="9">
         <f t="shared" si="62"/>
-        <v>0.11820274410673255</v>
+        <v>0.11491690532384297</v>
       </c>
       <c r="AE23" s="9">
         <f t="shared" si="62"/>
-        <v>0.13341033532614405</v>
+        <v>0.11450282251761297</v>
       </c>
       <c r="AF23" s="9">
         <f t="shared" si="62"/>
-        <v>0.14962010856899649</v>
+        <v>0.12777161055956734</v>
       </c>
       <c r="AG23" s="9">
         <f t="shared" si="62"/>
-        <v>0.16477804742091251</v>
+        <v>0.13097813597215119</v>
       </c>
       <c r="AH23" s="9">
         <f t="shared" si="62"/>
-        <v>0.16874868714087807</v>
+        <v>0.13307471028037907</v>
       </c>
       <c r="AI23" s="9">
         <f t="shared" si="62"/>
-        <v>0.17188222262527089</v>
+        <v>0.1343746145486579</v>
       </c>
       <c r="AJ23" s="9">
         <f t="shared" si="62"/>
-        <v>0.17491706125463247</v>
+        <v>0.13565681499570395</v>
       </c>
       <c r="AK23" s="9">
         <f t="shared" si="62"/>
-        <v>0.17697037574697344</v>
+        <v>0.13692158220990666</v>
       </c>
       <c r="AL23" s="9">
         <f t="shared" si="62"/>
-        <v>0.17809400744257653</v>
+        <v>0.13816918223595029</v>
       </c>
       <c r="AM23" s="9">
         <f t="shared" si="62"/>
-        <v>0.17831227780996692</v>
+        <v>0.13939987665614353</v>
       </c>
       <c r="AN23" s="9">
         <f t="shared" si="62"/>
-        <v>0.17852840827179464</v>
+        <v>0.14061392267023703</v>
       </c>
       <c r="AP23" t="s">
         <v>53</v>
       </c>
       <c r="AQ23" s="2">
         <f>AQ21+AQ22</f>
-        <v>45048.724398892606</v>
+        <v>38763.182006877178</v>
       </c>
     </row>
     <row r="24" spans="2:43" x14ac:dyDescent="0.3">
@@ -4246,7 +4252,7 @@
       </c>
       <c r="U24" s="9">
         <f t="shared" si="65"/>
-        <v>0.25</v>
+        <v>-8.7061668681983076E-2</v>
       </c>
       <c r="V24" s="9">
         <f t="shared" si="65"/>
@@ -4278,7 +4284,7 @@
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="66"/>
-        <v>0.3471097424296512</v>
+        <v>0.17012072685607665</v>
       </c>
       <c r="AE24" s="9">
         <f t="shared" si="66"/>
@@ -4325,7 +4331,7 @@
       </c>
       <c r="AQ24" s="2">
         <f>AQ23/Main!D15</f>
-        <v>51191.732271468871</v>
+        <v>44555.381617100204</v>
       </c>
     </row>
     <row r="25" spans="2:43" x14ac:dyDescent="0.3">
@@ -4406,11 +4412,11 @@
       </c>
       <c r="U25" s="9">
         <f t="shared" si="69"/>
-        <v>8.4366770034875263E-2</v>
+        <v>0.21044007490636704</v>
       </c>
       <c r="V25" s="9">
         <f t="shared" si="69"/>
-        <v>9.9465006024411995E-2</v>
+        <v>8.2803968402231046E-2</v>
       </c>
       <c r="X25" s="9" t="e">
         <f t="shared" ref="X25:AN25" si="70">X14/X3</f>
@@ -4438,54 +4444,54 @@
       </c>
       <c r="AD25" s="9">
         <f t="shared" si="70"/>
-        <v>5.5537233526347964E-2</v>
+        <v>8.2227680112316529E-2</v>
       </c>
       <c r="AE25" s="9">
         <f t="shared" si="70"/>
-        <v>7.731128982496388E-2</v>
+        <v>7.5119039284733763E-2</v>
       </c>
       <c r="AF25" s="9">
         <f t="shared" si="70"/>
-        <v>9.1213477073118832E-2</v>
+        <v>8.6016126273591953E-2</v>
       </c>
       <c r="AG25" s="9">
         <f t="shared" si="70"/>
-        <v>0.10402002688016725</v>
+        <v>8.9224528824939989E-2</v>
       </c>
       <c r="AH25" s="9">
         <f t="shared" si="70"/>
-        <v>0.10817387847533141</v>
+        <v>9.1482400833160907E-2</v>
       </c>
       <c r="AI25" s="9">
         <f t="shared" si="70"/>
-        <v>0.11147275600356597</v>
+        <v>9.3044517121147668E-2</v>
       </c>
       <c r="AJ25" s="9">
         <f t="shared" si="70"/>
-        <v>0.11465674048405369</v>
+        <v>9.4581953832786947E-2</v>
       </c>
       <c r="AK25" s="9">
         <f t="shared" si="70"/>
-        <v>0.11691475826496289</v>
+        <v>9.6095135301806286E-2</v>
       </c>
       <c r="AL25" s="9">
         <f t="shared" si="70"/>
-        <v>0.11830570558024801</v>
+        <v>9.7584478155271992E-2</v>
       </c>
       <c r="AM25" s="9">
         <f t="shared" si="70"/>
-        <v>0.11886260225677295</v>
+        <v>9.9050391458059925E-2</v>
       </c>
       <c r="AN25" s="9">
         <f t="shared" si="70"/>
-        <v>0.11941642679920457</v>
+        <v>0.10049327685457125</v>
       </c>
       <c r="AP25" t="s">
         <v>54</v>
       </c>
       <c r="AQ25" s="3">
         <f>AQ24/AN15</f>
-        <v>249.22946578125058</v>
+        <v>216.28826027718546</v>
       </c>
     </row>
     <row r="26" spans="2:43" x14ac:dyDescent="0.3">
@@ -4494,7 +4500,7 @@
       </c>
       <c r="AQ26" s="3">
         <f>Main!D3</f>
-        <v>680.29</v>
+        <v>632.54</v>
       </c>
     </row>
     <row r="27" spans="2:43" x14ac:dyDescent="0.3">
@@ -4503,7 +4509,7 @@
       </c>
       <c r="AQ27" s="10">
         <f>AQ25/AQ26-1</f>
-        <v>-0.6336423205085322</v>
+        <v>-0.6580639006589537</v>
       </c>
     </row>
     <row r="28" spans="2:43" x14ac:dyDescent="0.3">

--- a/Financial Analysis/SPOT.xlsx
+++ b/Financial Analysis/SPOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99E88CF-465B-4945-9C89-9349B980E41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4722DF-0E13-46CC-9FE3-24F9EF0289CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
   </bookViews>
@@ -747,14 +747,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>632.54</v>
+        <v>510.47</v>
       </c>
       <c r="E3" s="12">
-        <v>45965</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45965</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="12">
         <v>46063</v>
@@ -778,7 +778,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>130303.23999999999</v>
+        <v>105156.82</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -829,7 +829,7 @@
       </c>
       <c r="D10" s="2">
         <f>D5-D9</f>
-        <v>118498.64229885057</v>
+        <v>93352.222298850582</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -1158,7 +1158,7 @@
         <v>2921</v>
       </c>
       <c r="V4" s="2">
-        <f t="shared" ref="U4:V4" si="1">V3-V5</f>
+        <f t="shared" ref="V4" si="1">V3-V5</f>
         <v>3057.6336000000001</v>
       </c>
       <c r="Z4" s="2">
@@ -1462,7 +1462,7 @@
         <v>1632.6373440000002</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" ref="AF6:AN6" si="5">AF6*1.02</f>
+        <f t="shared" ref="AG6:AN6" si="5">AF6*1.02</f>
         <v>1665.2900908800002</v>
       </c>
       <c r="AH6" s="2">
@@ -1954,7 +1954,7 @@
         <v>-262</v>
       </c>
       <c r="V10" s="2">
-        <f t="shared" ref="U10:V11" si="12">R10*1.02</f>
+        <f t="shared" ref="V10:V11" si="12">R10*1.02</f>
         <v>-129.54</v>
       </c>
       <c r="Z10" s="2">
@@ -2352,7 +2352,7 @@
         <v>-72</v>
       </c>
       <c r="V13" s="2">
-        <f t="shared" ref="U13:V13" si="18">V12*0.25</f>
+        <f t="shared" ref="V13" si="18">V12*0.25</f>
         <v>124.10990000000001</v>
       </c>
       <c r="Z13" s="2">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AQ26" s="3">
         <f>Main!D3</f>
-        <v>632.54</v>
+        <v>510.47</v>
       </c>
     </row>
     <row r="27" spans="2:43" x14ac:dyDescent="0.3">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AQ27" s="10">
         <f>AQ25/AQ26-1</f>
-        <v>-0.6580639006589537</v>
+        <v>-0.57629584446258264</v>
       </c>
     </row>
     <row r="28" spans="2:43" x14ac:dyDescent="0.3">

--- a/Financial Analysis/SPOT.xlsx
+++ b/Financial Analysis/SPOT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4722DF-0E13-46CC-9FE3-24F9EF0289CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6E2B38-DC51-4CD5-9E3D-89DB02B6BD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E254F39D-7CC4-4B6C-BDE0-D6C4D40F2C97}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>SPOT</t>
   </si>
@@ -217,7 +217,19 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -280,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -300,6 +312,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -321,16 +334,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -345,7 +358,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13395960" y="7620"/>
+          <a:off x="13990320" y="0"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -371,14 +384,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
@@ -395,7 +408,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18272760" y="0"/>
+          <a:off x="21313140" y="0"/>
           <a:ext cx="0" cy="6057900"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -747,17 +760,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>510.47</v>
+        <v>458.34</v>
       </c>
       <c r="E3" s="12">
-        <v>46052</v>
+        <v>46067</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46067</v>
       </c>
       <c r="G3" s="12">
-        <v>46063</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -765,11 +778,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -778,7 +791,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>105156.82</v>
+        <v>94326.372000000003</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -786,11 +799,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>5456+3606+61+2888</f>
-        <v>12011</v>
+        <f>5258+4209+2181</f>
+        <v>11648</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -798,11 +811,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>1741</f>
-        <v>1741</v>
+        <f>1458</f>
+        <v>1458</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -811,7 +824,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>10270</v>
+        <v>10190</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -820,7 +833,7 @@
       </c>
       <c r="D9" s="2">
         <f>D8/D15</f>
-        <v>11804.597701149425</v>
+        <v>11712.643678160919</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
@@ -829,7 +842,7 @@
       </c>
       <c r="D10" s="2">
         <f>D5-D9</f>
-        <v>93352.222298850582</v>
+        <v>82613.72832183908</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,16 +860,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9024E141-0626-49BA-AB25-4AB63369CE3B}">
-  <dimension ref="A2:ES28"/>
+  <dimension ref="A2:EW28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.109375" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
-    <col min="42" max="42" width="13.6640625" customWidth="1"/>
-    <col min="43" max="43" width="16.5546875" customWidth="1"/>
+    <col min="46" max="46" width="13.6640625" customWidth="1"/>
+    <col min="47" max="47" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:153" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>38</v>
       </c>
@@ -917,59 +930,71 @@
       <c r="V2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="X2">
+      <c r="W2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB2">
         <v>2019</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>2020</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2021</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2022</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2023</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2024</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2025</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2026</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2027</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2028</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2029</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2030</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2031</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2032</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2033</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2034</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3" s="1" t="s">
         <v>10</v>
@@ -1032,71 +1057,85 @@
         <v>4272</v>
       </c>
       <c r="V3" s="7">
-        <f>R3*1.06</f>
-        <v>4496.5200000000004</v>
+        <f>AH3-U3-T3-S3</f>
+        <v>4531</v>
+      </c>
+      <c r="W3" s="7">
+        <v>4500</v>
+      </c>
+      <c r="X3" s="7">
+        <f>T3*1.06</f>
+        <v>4444.58</v>
+      </c>
+      <c r="Y3" s="7">
+        <f t="shared" ref="Y3:Z3" si="0">U3*1.06</f>
+        <v>4528.3200000000006</v>
       </c>
       <c r="Z3" s="7">
+        <f>V3*1.05</f>
+        <v>4757.55</v>
+      </c>
+      <c r="AD3" s="7">
         <f>SUM(C3:F3)</f>
         <v>9668</v>
       </c>
-      <c r="AA3" s="7">
+      <c r="AE3" s="7">
         <f>SUM(G3:J3)</f>
         <v>11727</v>
       </c>
-      <c r="AB3" s="7">
+      <c r="AF3" s="7">
         <f>SUM(K3:N3)</f>
         <v>13247</v>
       </c>
-      <c r="AC3" s="7">
+      <c r="AG3" s="7">
         <f>SUM(O3:R3)</f>
         <v>15673</v>
       </c>
-      <c r="AD3" s="7">
-        <f>SUM(S3:V3)</f>
-        <v>17151.52</v>
-      </c>
-      <c r="AE3" s="7">
-        <f>AD3*1.07</f>
-        <v>18352.126400000001</v>
-      </c>
-      <c r="AF3" s="7">
-        <f>AE3*1.06</f>
-        <v>19453.253984000003</v>
-      </c>
-      <c r="AG3" s="7">
-        <f>AF3*1.05</f>
-        <v>20425.916683200005</v>
-      </c>
       <c r="AH3" s="7">
-        <f>AG3*1.04</f>
-        <v>21242.953350528005</v>
+        <v>17186</v>
       </c>
       <c r="AI3" s="7">
-        <f>AH3*1.03</f>
-        <v>21880.241951043845</v>
+        <f>SUM(W3:Z3)</f>
+        <v>18230.45</v>
       </c>
       <c r="AJ3" s="7">
-        <f t="shared" ref="AJ3:AN3" si="0">AI3*1.03</f>
-        <v>22536.64920957516</v>
+        <f>AI3*1.06</f>
+        <v>19324.277000000002</v>
       </c>
       <c r="AK3" s="7">
-        <f t="shared" si="0"/>
-        <v>23212.748685862414</v>
+        <f>AJ3*1.05</f>
+        <v>20290.490850000002</v>
       </c>
       <c r="AL3" s="7">
-        <f t="shared" si="0"/>
-        <v>23909.131146438289</v>
+        <f>AK3*1.04</f>
+        <v>21102.110484000004</v>
       </c>
       <c r="AM3" s="7">
-        <f t="shared" si="0"/>
-        <v>24626.405080831439</v>
+        <f>AL3*1.03</f>
+        <v>21735.173798520005</v>
       </c>
       <c r="AN3" s="7">
-        <f t="shared" si="0"/>
-        <v>25365.197233256382</v>
+        <f t="shared" ref="AN3:AR3" si="1">AM3*1.03</f>
+        <v>22387.229012475607</v>
+      </c>
+      <c r="AO3" s="7">
+        <f t="shared" si="1"/>
+        <v>23058.845882849877</v>
+      </c>
+      <c r="AP3" s="7">
+        <f t="shared" si="1"/>
+        <v>23750.611259335376</v>
+      </c>
+      <c r="AQ3" s="7">
+        <f t="shared" si="1"/>
+        <v>24463.129597115436</v>
+      </c>
+      <c r="AR3" s="7">
+        <f t="shared" si="1"/>
+        <v>25197.023485028898</v>
       </c>
     </row>
-    <row r="4" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -1157,78 +1196,81 @@
       <c r="U4" s="2">
         <v>2921</v>
       </c>
-      <c r="V4" s="2">
-        <f t="shared" ref="V4" si="1">V3-V5</f>
-        <v>3057.6336000000001</v>
-      </c>
-      <c r="Z4" s="2">
+      <c r="V4" s="13">
+        <f>AH4-U4-T4-S4</f>
+        <v>3032</v>
+      </c>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AD4" s="2">
         <f>SUM(C4:F4)</f>
         <v>7077</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AE4" s="2">
         <f>SUM(G4:J4)</f>
         <v>8801</v>
       </c>
-      <c r="AB4" s="2">
+      <c r="AF4" s="2">
         <f>SUM(K4:N4)</f>
         <v>9850</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AG4" s="2">
         <f>SUM(O4:R4)</f>
         <v>10949</v>
       </c>
-      <c r="AD4" s="2">
-        <f>SUM(S4:V4)</f>
-        <v>11715.633600000001</v>
-      </c>
-      <c r="AE4" s="2">
-        <f>AE3-AE5</f>
-        <v>12479.445952000002</v>
-      </c>
-      <c r="AF4" s="2">
-        <f t="shared" ref="AF4:AN4" si="2">AF3-AF5</f>
-        <v>13033.680169280002</v>
-      </c>
-      <c r="AG4" s="2">
-        <f t="shared" si="2"/>
-        <v>13685.364177744003</v>
-      </c>
       <c r="AH4" s="2">
-        <f t="shared" si="2"/>
-        <v>14232.778744853764</v>
+        <v>11690</v>
       </c>
       <c r="AI4" s="2">
-        <f t="shared" si="2"/>
-        <v>14659.762107199374</v>
+        <f>AI3-AI5</f>
+        <v>12214.4015</v>
       </c>
       <c r="AJ4" s="2">
-        <f t="shared" si="2"/>
-        <v>15099.554970415356</v>
+        <f t="shared" ref="AJ4:AR4" si="2">AJ3-AJ5</f>
+        <v>12754.022820000002</v>
       </c>
       <c r="AK4" s="2">
         <f t="shared" si="2"/>
-        <v>15552.541619527818</v>
+        <v>13391.723961</v>
       </c>
       <c r="AL4" s="2">
         <f t="shared" si="2"/>
-        <v>16019.117868113653</v>
+        <v>13927.392919440003</v>
       </c>
       <c r="AM4" s="2">
         <f t="shared" si="2"/>
-        <v>16499.691404157064</v>
+        <v>14345.214707023202</v>
       </c>
       <c r="AN4" s="2">
         <f t="shared" si="2"/>
-        <v>16994.682146281775</v>
+        <v>14775.571148233899</v>
+      </c>
+      <c r="AO4" s="2">
+        <f t="shared" si="2"/>
+        <v>15218.838282680917</v>
+      </c>
+      <c r="AP4" s="2">
+        <f t="shared" si="2"/>
+        <v>15675.403431161347</v>
+      </c>
+      <c r="AQ4" s="2">
+        <f t="shared" si="2"/>
+        <v>16145.665534096188</v>
+      </c>
+      <c r="AR4" s="2">
+        <f t="shared" si="2"/>
+        <v>16630.035500119073</v>
       </c>
     </row>
-    <row r="5" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:U5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:V5" si="3">C3-C4</f>
         <v>548</v>
       </c>
       <c r="D5" s="7">
@@ -1304,71 +1346,75 @@
         <v>1351</v>
       </c>
       <c r="V5" s="7">
-        <f>V3*0.32</f>
-        <v>1438.8864000000001</v>
-      </c>
-      <c r="Z5" s="7">
-        <f>Z3-Z4</f>
-        <v>2591</v>
-      </c>
-      <c r="AA5" s="7">
-        <f>AA3-AA4</f>
-        <v>2926</v>
-      </c>
-      <c r="AB5" s="7">
-        <f>AB3-AB4</f>
-        <v>3397</v>
-      </c>
-      <c r="AC5" s="7">
-        <f>AC3-AC4</f>
-        <v>4724</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>1499</v>
+      </c>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
       <c r="AD5" s="7">
         <f>AD3-AD4</f>
-        <v>5435.8863999999994</v>
+        <v>2591</v>
       </c>
       <c r="AE5" s="7">
-        <f>AE3*0.32</f>
-        <v>5872.6804480000001</v>
+        <f>AE3-AE4</f>
+        <v>2926</v>
       </c>
       <c r="AF5" s="7">
-        <f>AF3*0.33</f>
-        <v>6419.5738147200009</v>
+        <f>AF3-AF4</f>
+        <v>3397</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" ref="AG5:AN5" si="4">AG3*0.33</f>
-        <v>6740.5525054560021</v>
+        <f>AG3-AG4</f>
+        <v>4724</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="4"/>
-        <v>7010.1746056742422</v>
+        <f>AH3-AH4</f>
+        <v>5496</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" si="4"/>
-        <v>7220.4798438444695</v>
+        <f>AI3*0.33</f>
+        <v>6016.0485000000008</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="4"/>
-        <v>7437.0942391598028</v>
+        <f>AJ3*0.34</f>
+        <v>6570.2541800000008</v>
       </c>
       <c r="AK5" s="7">
-        <f t="shared" si="4"/>
-        <v>7660.2070663345967</v>
+        <f t="shared" ref="AK5:AR5" si="4">AK3*0.34</f>
+        <v>6898.7668890000014</v>
       </c>
       <c r="AL5" s="7">
         <f t="shared" si="4"/>
-        <v>7890.0132783246354</v>
+        <v>7174.7175645600018</v>
       </c>
       <c r="AM5" s="7">
         <f t="shared" si="4"/>
-        <v>8126.7136766743752</v>
+        <v>7389.9590914968021</v>
       </c>
       <c r="AN5" s="7">
         <f t="shared" si="4"/>
-        <v>8370.5150869746067</v>
+        <v>7611.6578642417071</v>
+      </c>
+      <c r="AO5" s="7">
+        <f t="shared" si="4"/>
+        <v>7840.0076001689586</v>
+      </c>
+      <c r="AP5" s="7">
+        <f t="shared" si="4"/>
+        <v>8075.2078281740287</v>
+      </c>
+      <c r="AQ5" s="7">
+        <f t="shared" si="4"/>
+        <v>8317.464063019248</v>
+      </c>
+      <c r="AR5" s="7">
+        <f t="shared" si="4"/>
+        <v>8566.9879849098252</v>
       </c>
     </row>
-    <row r="6" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -1429,72 +1475,75 @@
       <c r="U6" s="2">
         <v>309</v>
       </c>
-      <c r="V6" s="2">
-        <f>R6*1.12</f>
-        <v>421.12000000000006</v>
-      </c>
-      <c r="Z6" s="2">
+      <c r="V6" s="13">
+        <f t="shared" ref="V6:V11" si="5">AH6-U6-T6-S6</f>
+        <v>290</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AD6" s="2">
         <f>SUM(C6:F6)</f>
         <v>912</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AE6" s="2">
         <f>SUM(G6:J6)</f>
         <v>1387</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AF6" s="2">
         <f>SUM(K6:N6)</f>
         <v>1725</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AG6" s="2">
         <f>SUM(O6:R6)</f>
         <v>1486</v>
       </c>
-      <c r="AD6" s="2">
-        <f>SUM(S6:V6)</f>
-        <v>1524.1200000000001</v>
-      </c>
-      <c r="AE6" s="2">
-        <f>AD6*1.04</f>
-        <v>1585.0848000000001</v>
-      </c>
-      <c r="AF6" s="2">
-        <f>AE6*1.03</f>
-        <v>1632.6373440000002</v>
-      </c>
-      <c r="AG6" s="2">
-        <f t="shared" ref="AG6:AN6" si="5">AF6*1.02</f>
-        <v>1665.2900908800002</v>
-      </c>
       <c r="AH6" s="2">
-        <f t="shared" si="5"/>
-        <v>1698.5958926976002</v>
+        <v>1393</v>
       </c>
       <c r="AI6" s="2">
-        <f t="shared" si="5"/>
-        <v>1732.5678105515522</v>
+        <f>AH6*1.04</f>
+        <v>1448.72</v>
       </c>
       <c r="AJ6" s="2">
-        <f t="shared" si="5"/>
-        <v>1767.2191667625832</v>
+        <f>AI6*1.03</f>
+        <v>1492.1816000000001</v>
       </c>
       <c r="AK6" s="2">
-        <f t="shared" si="5"/>
-        <v>1802.5635500978349</v>
+        <f t="shared" ref="AK6:AR6" si="6">AJ6*1.02</f>
+        <v>1522.0252320000002</v>
       </c>
       <c r="AL6" s="2">
-        <f t="shared" si="5"/>
-        <v>1838.6148210997917</v>
+        <f t="shared" si="6"/>
+        <v>1552.4657366400002</v>
       </c>
       <c r="AM6" s="2">
-        <f t="shared" si="5"/>
-        <v>1875.3871175217876</v>
+        <f t="shared" si="6"/>
+        <v>1583.5150513728001</v>
       </c>
       <c r="AN6" s="2">
-        <f t="shared" si="5"/>
-        <v>1912.8948598722234</v>
+        <f t="shared" si="6"/>
+        <v>1615.1853524002561</v>
+      </c>
+      <c r="AO6" s="2">
+        <f t="shared" si="6"/>
+        <v>1647.4890594482613</v>
+      </c>
+      <c r="AP6" s="2">
+        <f t="shared" si="6"/>
+        <v>1680.4388406372266</v>
+      </c>
+      <c r="AQ6" s="2">
+        <f t="shared" si="6"/>
+        <v>1714.0476174499711</v>
+      </c>
+      <c r="AR6" s="2">
+        <f t="shared" si="6"/>
+        <v>1748.3285697989706</v>
       </c>
     </row>
-    <row r="7" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -1555,72 +1604,75 @@
       <c r="U7" s="2">
         <v>349</v>
       </c>
-      <c r="V7" s="2">
-        <f>V3*0.09</f>
-        <v>404.68680000000001</v>
-      </c>
-      <c r="Z7" s="2">
+      <c r="V7" s="13">
+        <f t="shared" si="5"/>
+        <v>399</v>
+      </c>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AD7" s="2">
         <f>SUM(C7:F7)</f>
         <v>1135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <f>SUM(G7:J7)</f>
         <v>1572</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <f>SUM(K7:N7)</f>
         <v>1533</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <f>SUM(O7:R7)</f>
         <v>1392</v>
       </c>
-      <c r="AD7" s="2">
-        <f>SUM(S7:V7)</f>
-        <v>1431.6867999999999</v>
-      </c>
-      <c r="AE7" s="2">
-        <f>AE3*0.09</f>
-        <v>1651.691376</v>
-      </c>
-      <c r="AF7" s="2">
-        <f t="shared" ref="AF7:AN7" si="6">AF3*0.09</f>
-        <v>1750.7928585600002</v>
-      </c>
-      <c r="AG7" s="2">
-        <f t="shared" si="6"/>
-        <v>1838.3325014880004</v>
-      </c>
       <c r="AH7" s="2">
-        <f t="shared" si="6"/>
-        <v>1911.8658015475203</v>
+        <v>1426</v>
       </c>
       <c r="AI7" s="2">
-        <f t="shared" si="6"/>
-        <v>1969.2217755939459</v>
+        <f>AI3*0.08</f>
+        <v>1458.4360000000001</v>
       </c>
       <c r="AJ7" s="2">
-        <f t="shared" si="6"/>
-        <v>2028.2984288617643</v>
+        <f t="shared" ref="AJ7:AR7" si="7">AJ3*0.08</f>
+        <v>1545.9421600000003</v>
       </c>
       <c r="AK7" s="2">
-        <f t="shared" si="6"/>
-        <v>2089.1473817276174</v>
+        <f t="shared" si="7"/>
+        <v>1623.2392680000003</v>
       </c>
       <c r="AL7" s="2">
-        <f t="shared" si="6"/>
-        <v>2151.8218031794459</v>
+        <f t="shared" si="7"/>
+        <v>1688.1688387200004</v>
       </c>
       <c r="AM7" s="2">
-        <f t="shared" si="6"/>
-        <v>2216.3764572748296</v>
+        <f t="shared" si="7"/>
+        <v>1738.8139038816005</v>
       </c>
       <c r="AN7" s="2">
-        <f t="shared" si="6"/>
-        <v>2282.8677509930744</v>
+        <f t="shared" si="7"/>
+        <v>1790.9783209980487</v>
+      </c>
+      <c r="AO7" s="2">
+        <f t="shared" si="7"/>
+        <v>1844.7076706279902</v>
+      </c>
+      <c r="AP7" s="2">
+        <f t="shared" si="7"/>
+        <v>1900.04890074683</v>
+      </c>
+      <c r="AQ7" s="2">
+        <f t="shared" si="7"/>
+        <v>1957.050367769235</v>
+      </c>
+      <c r="AR7" s="2">
+        <f t="shared" si="7"/>
+        <v>2015.7618788023119</v>
       </c>
     </row>
-    <row r="8" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>18</v>
       </c>
@@ -1681,218 +1733,225 @@
       <c r="U8" s="2">
         <v>111</v>
       </c>
-      <c r="V8" s="2">
-        <f>R8*1.14</f>
-        <v>139.07999999999998</v>
-      </c>
-      <c r="Z8" s="2">
+      <c r="V8" s="13">
+        <f t="shared" si="5"/>
+        <v>109</v>
+      </c>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AD8" s="2">
         <f>SUM(C8:F8)</f>
         <v>450</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AE8" s="2">
         <f>SUM(G8:J8)</f>
         <v>626</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AF8" s="2">
         <f>SUM(K8:N8)</f>
         <v>585</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AG8" s="2">
         <f>SUM(O8:R8)</f>
         <v>481</v>
       </c>
-      <c r="AD8" s="2">
-        <f>SUM(S8:V8)</f>
-        <v>509.08</v>
-      </c>
-      <c r="AE8" s="2">
-        <f>AD8*1.05</f>
-        <v>534.53399999999999</v>
-      </c>
-      <c r="AF8" s="2">
-        <f>AE8*1.03</f>
-        <v>550.57002</v>
-      </c>
-      <c r="AG8" s="2">
-        <f t="shared" ref="AG8:AH8" si="7">AF8*1.02</f>
-        <v>561.58142039999996</v>
-      </c>
       <c r="AH8" s="2">
-        <f t="shared" si="7"/>
-        <v>572.81304880799996</v>
+        <v>479</v>
       </c>
       <c r="AI8" s="2">
-        <f>AH8*1.01</f>
-        <v>578.54117929607992</v>
+        <f>AH8*1.03</f>
+        <v>493.37</v>
       </c>
       <c r="AJ8" s="2">
-        <f t="shared" ref="AJ8:AN8" si="8">AI8*1.01</f>
-        <v>584.32659108904068</v>
+        <f>AI8*1.02</f>
+        <v>503.23740000000004</v>
       </c>
       <c r="AK8" s="2">
-        <f t="shared" si="8"/>
-        <v>590.16985699993108</v>
+        <f t="shared" ref="AK8:AL8" si="8">AJ8*1.02</f>
+        <v>513.3021480000001</v>
       </c>
       <c r="AL8" s="2">
         <f t="shared" si="8"/>
-        <v>596.07155556993041</v>
+        <v>523.56819096000015</v>
       </c>
       <c r="AM8" s="2">
-        <f t="shared" si="8"/>
-        <v>602.03227112562968</v>
+        <f>AL8*1.01</f>
+        <v>528.80387286960013</v>
       </c>
       <c r="AN8" s="2">
-        <f t="shared" si="8"/>
-        <v>608.05259383688599</v>
+        <f t="shared" ref="AN8:AR8" si="9">AM8*1.01</f>
+        <v>534.09191159829618</v>
+      </c>
+      <c r="AO8" s="2">
+        <f t="shared" si="9"/>
+        <v>539.43283071427913</v>
+      </c>
+      <c r="AP8" s="2">
+        <f t="shared" si="9"/>
+        <v>544.82715902142195</v>
+      </c>
+      <c r="AQ8" s="2">
+        <f t="shared" si="9"/>
+        <v>550.27543061163612</v>
+      </c>
+      <c r="AR8" s="2">
+        <f t="shared" si="9"/>
+        <v>555.77818491775247</v>
       </c>
     </row>
-    <row r="9" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:P9" si="9">C5-SUM(C6:C8)</f>
+        <f t="shared" ref="C9:P9" si="10">C5-SUM(C6:C8)</f>
         <v>14</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-7</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-6</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-194</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-228</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-231</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-156</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-247</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-75</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>168</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>266</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" ref="Q9:V9" si="10">Q5-SUM(Q6:Q8)</f>
+        <f t="shared" ref="Q9:V9" si="11">Q5-SUM(Q6:Q8)</f>
         <v>454</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>477</v>
       </c>
       <c r="S9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>509</v>
       </c>
       <c r="T9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>406</v>
       </c>
       <c r="U9" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>582</v>
       </c>
       <c r="V9" s="7">
-        <f t="shared" si="10"/>
-        <v>473.9996000000001</v>
-      </c>
-      <c r="Z9" s="7">
-        <f>Z5-SUM(Z6:Z8)</f>
-        <v>94</v>
-      </c>
-      <c r="AA9" s="7">
-        <f>AA5-SUM(AA6:AA8)</f>
-        <v>-659</v>
-      </c>
-      <c r="AB9" s="7">
-        <f>AB5-SUM(AB6:AB8)</f>
-        <v>-446</v>
-      </c>
-      <c r="AC9" s="7">
-        <f>AC5-SUM(AC6:AC8)</f>
-        <v>1365</v>
-      </c>
+        <f t="shared" si="11"/>
+        <v>701</v>
+      </c>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
       <c r="AD9" s="7">
         <f>AD5-SUM(AD6:AD8)</f>
-        <v>1970.9995999999992</v>
+        <v>94</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" ref="AE9:AN9" si="11">AE5-SUM(AE6:AE8)</f>
-        <v>2101.3702719999997</v>
+        <f>AE5-SUM(AE6:AE8)</f>
+        <v>-659</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="11"/>
-        <v>2485.5735921600003</v>
+        <f>AF5-SUM(AF6:AF8)</f>
+        <v>-446</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="11"/>
-        <v>2675.3484926880019</v>
+        <f>AG5-SUM(AG6:AG8)</f>
+        <v>1365</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" si="11"/>
-        <v>2826.8998626211223</v>
+        <f>AH5-SUM(AH6:AH8)</f>
+        <v>2198</v>
       </c>
       <c r="AI9" s="7">
-        <f t="shared" si="11"/>
-        <v>2940.1490784028911</v>
+        <f t="shared" ref="AI9:AR9" si="12">AI5-SUM(AI6:AI8)</f>
+        <v>2615.5225000000009</v>
       </c>
       <c r="AJ9" s="7">
-        <f t="shared" si="11"/>
-        <v>3057.2500524464149</v>
+        <f t="shared" si="12"/>
+        <v>3028.8930200000004</v>
       </c>
       <c r="AK9" s="7">
-        <f t="shared" si="11"/>
-        <v>3178.3262775092135</v>
+        <f t="shared" si="12"/>
+        <v>3240.2002410000009</v>
       </c>
       <c r="AL9" s="7">
-        <f t="shared" si="11"/>
-        <v>3303.5050984754671</v>
+        <f t="shared" si="12"/>
+        <v>3410.5147982400008</v>
       </c>
       <c r="AM9" s="7">
-        <f t="shared" si="11"/>
-        <v>3432.9178307521288</v>
+        <f t="shared" si="12"/>
+        <v>3538.8262633728013</v>
       </c>
       <c r="AN9" s="7">
-        <f t="shared" si="11"/>
-        <v>3566.6998822724236</v>
+        <f t="shared" si="12"/>
+        <v>3671.402279245106</v>
+      </c>
+      <c r="AO9" s="7">
+        <f t="shared" si="12"/>
+        <v>3808.3780393784277</v>
+      </c>
+      <c r="AP9" s="7">
+        <f t="shared" si="12"/>
+        <v>3949.8929277685502</v>
+      </c>
+      <c r="AQ9" s="7">
+        <f t="shared" si="12"/>
+        <v>4096.0906471884064</v>
+      </c>
+      <c r="AR9" s="7">
+        <f t="shared" si="12"/>
+        <v>4247.1193513907901</v>
       </c>
     </row>
-    <row r="10" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>20</v>
       </c>
@@ -1953,72 +2012,74 @@
       <c r="U10" s="2">
         <v>-262</v>
       </c>
-      <c r="V10" s="2">
-        <f t="shared" ref="V10:V11" si="12">R10*1.02</f>
-        <v>-129.54</v>
-      </c>
-      <c r="Z10" s="2">
+      <c r="V10" s="13">
+        <v>-349</v>
+      </c>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AD10" s="2">
         <f>SUM(C10:F10)</f>
         <v>-246</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AE10" s="2">
         <f>SUM(G10:J10)</f>
         <v>-421</v>
       </c>
-      <c r="AB10" s="2">
+      <c r="AF10" s="2">
         <f>SUM(K10:N10)</f>
         <v>-161</v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AG10" s="2">
         <f>SUM(O10:R10)</f>
         <v>-328</v>
       </c>
-      <c r="AD10" s="2">
-        <f>SUM(S10:V10)</f>
-        <v>-551.54</v>
-      </c>
-      <c r="AE10" s="2">
-        <f>AD10*1.03</f>
-        <v>-568.08619999999996</v>
-      </c>
-      <c r="AF10" s="2">
-        <f t="shared" ref="AF10:AN10" si="13">AE10*1.03</f>
-        <v>-585.12878599999999</v>
-      </c>
-      <c r="AG10" s="2">
-        <f t="shared" si="13"/>
-        <v>-602.68264957999997</v>
-      </c>
       <c r="AH10" s="2">
-        <f t="shared" si="13"/>
-        <v>-620.76312906739997</v>
+        <v>-292</v>
       </c>
       <c r="AI10" s="2">
-        <f t="shared" si="13"/>
-        <v>-639.38602293942199</v>
+        <f>AH10*1.03</f>
+        <v>-300.76</v>
       </c>
       <c r="AJ10" s="2">
-        <f t="shared" si="13"/>
-        <v>-658.56760362760463</v>
+        <f t="shared" ref="AJ10:AR10" si="13">AI10*1.03</f>
+        <v>-309.78280000000001</v>
       </c>
       <c r="AK10" s="2">
         <f t="shared" si="13"/>
-        <v>-678.32463173643282</v>
+        <v>-319.07628400000004</v>
       </c>
       <c r="AL10" s="2">
         <f t="shared" si="13"/>
-        <v>-698.67437068852587</v>
+        <v>-328.64857252000007</v>
       </c>
       <c r="AM10" s="2">
         <f t="shared" si="13"/>
-        <v>-719.63460180918162</v>
+        <v>-338.5080296956001</v>
       </c>
       <c r="AN10" s="2">
         <f t="shared" si="13"/>
-        <v>-741.22363986345704</v>
+        <v>-348.66327058646812</v>
+      </c>
+      <c r="AO10" s="2">
+        <f t="shared" si="13"/>
+        <v>-359.12316870406215</v>
+      </c>
+      <c r="AP10" s="2">
+        <f t="shared" si="13"/>
+        <v>-369.89686376518404</v>
+      </c>
+      <c r="AQ10" s="2">
+        <f t="shared" si="13"/>
+        <v>-380.99376967813959</v>
+      </c>
+      <c r="AR10" s="2">
+        <f t="shared" si="13"/>
+        <v>-392.42358276848381</v>
       </c>
     </row>
-    <row r="11" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -2079,72 +2140,74 @@
       <c r="U11" s="2">
         <v>17</v>
       </c>
-      <c r="V11" s="2">
-        <f t="shared" si="12"/>
-        <v>107.10000000000001</v>
-      </c>
-      <c r="Z11" s="2">
+      <c r="V11" s="13">
+        <v>29</v>
+      </c>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AD11" s="2">
         <f>SUM(C11:F11)</f>
         <v>91</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AE11" s="2">
         <f>SUM(G11:J11)</f>
         <v>132</v>
       </c>
-      <c r="AB11" s="2">
+      <c r="AF11" s="2">
         <f>SUM(K11:N11)</f>
         <v>220</v>
       </c>
-      <c r="AC11" s="2">
+      <c r="AG11" s="2">
         <f>SUM(O11:R11)</f>
         <v>352</v>
       </c>
-      <c r="AD11" s="2">
-        <f>SUM(S11:V11)</f>
-        <v>823.1</v>
-      </c>
-      <c r="AE11" s="2">
-        <f t="shared" ref="AE11:AN11" si="14">AD11*1.01</f>
-        <v>831.33100000000002</v>
-      </c>
-      <c r="AF11" s="2">
-        <f t="shared" si="14"/>
-        <v>839.64431000000002</v>
-      </c>
-      <c r="AG11" s="2">
-        <f t="shared" si="14"/>
-        <v>848.04075310000007</v>
-      </c>
       <c r="AH11" s="2">
-        <f t="shared" si="14"/>
-        <v>856.52116063100004</v>
+        <v>266</v>
       </c>
       <c r="AI11" s="2">
-        <f t="shared" si="14"/>
-        <v>865.08637223731</v>
+        <f t="shared" ref="AI11:AR11" si="14">AH11*1.01</f>
+        <v>268.66000000000003</v>
       </c>
       <c r="AJ11" s="2">
         <f t="shared" si="14"/>
-        <v>873.73723595968306</v>
+        <v>271.34660000000002</v>
       </c>
       <c r="AK11" s="2">
         <f t="shared" si="14"/>
-        <v>882.47460831927992</v>
+        <v>274.06006600000001</v>
       </c>
       <c r="AL11" s="2">
         <f t="shared" si="14"/>
-        <v>891.29935440247277</v>
+        <v>276.80066665999999</v>
       </c>
       <c r="AM11" s="2">
         <f t="shared" si="14"/>
-        <v>900.21234794649752</v>
+        <v>279.56867332659999</v>
       </c>
       <c r="AN11" s="2">
         <f t="shared" si="14"/>
-        <v>909.21447142596253</v>
+        <v>282.36436005986599</v>
+      </c>
+      <c r="AO11" s="2">
+        <f t="shared" si="14"/>
+        <v>285.18800366046463</v>
+      </c>
+      <c r="AP11" s="2">
+        <f t="shared" si="14"/>
+        <v>288.03988369706929</v>
+      </c>
+      <c r="AQ11" s="2">
+        <f t="shared" si="14"/>
+        <v>290.92028253403998</v>
+      </c>
+      <c r="AR11" s="2">
+        <f t="shared" si="14"/>
+        <v>293.82948535938039</v>
       </c>
     </row>
-    <row r="12" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12"/>
       <c r="B12" s="1" t="s">
         <v>22</v>
@@ -2227,70 +2290,74 @@
       </c>
       <c r="V12" s="7">
         <f t="shared" si="16"/>
-        <v>496.43960000000004</v>
-      </c>
-      <c r="Z12" s="7">
-        <f>Z9-Z10-Z11</f>
-        <v>249</v>
-      </c>
-      <c r="AA12" s="7">
-        <f>AA9-AA10-AA11</f>
-        <v>-370</v>
-      </c>
-      <c r="AB12" s="7">
-        <f>AB9-AB10-AB11</f>
-        <v>-505</v>
-      </c>
-      <c r="AC12" s="7">
-        <f>AC9-AC10-AC11</f>
-        <v>1341</v>
-      </c>
+        <v>1021</v>
+      </c>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
       <c r="AD12" s="7">
         <f>AD9-AD10-AD11</f>
-        <v>1699.4395999999992</v>
+        <v>249</v>
       </c>
       <c r="AE12" s="7">
-        <f t="shared" ref="AE12:AN12" si="17">AE9-AE10-AE11</f>
-        <v>1838.1254719999997</v>
+        <f>AE9-AE10-AE11</f>
+        <v>-370</v>
       </c>
       <c r="AF12" s="7">
-        <f t="shared" si="17"/>
-        <v>2231.0580681599999</v>
+        <f>AF9-AF10-AF11</f>
+        <v>-505</v>
       </c>
       <c r="AG12" s="7">
-        <f t="shared" si="17"/>
-        <v>2429.9903891680019</v>
+        <f>AG9-AG10-AG11</f>
+        <v>1341</v>
       </c>
       <c r="AH12" s="7">
-        <f t="shared" si="17"/>
-        <v>2591.1418310575223</v>
+        <f>AH9-AH10-AH11</f>
+        <v>2224</v>
       </c>
       <c r="AI12" s="7">
-        <f t="shared" si="17"/>
-        <v>2714.4487291050032</v>
+        <f t="shared" ref="AI12:AR12" si="17">AI9-AI10-AI11</f>
+        <v>2647.6225000000013</v>
       </c>
       <c r="AJ12" s="7">
         <f t="shared" si="17"/>
-        <v>2842.0804201143364</v>
+        <v>3067.3292200000005</v>
       </c>
       <c r="AK12" s="7">
         <f t="shared" si="17"/>
-        <v>2974.1763009263664</v>
+        <v>3285.2164590000011</v>
       </c>
       <c r="AL12" s="7">
         <f t="shared" si="17"/>
-        <v>3110.8801147615204</v>
+        <v>3462.3627041000009</v>
       </c>
       <c r="AM12" s="7">
         <f t="shared" si="17"/>
-        <v>3252.3400846148129</v>
+        <v>3597.7656197418019</v>
       </c>
       <c r="AN12" s="7">
         <f t="shared" si="17"/>
-        <v>3398.7090507099178</v>
+        <v>3737.701189771708</v>
+      </c>
+      <c r="AO12" s="7">
+        <f t="shared" si="17"/>
+        <v>3882.3132044220251</v>
+      </c>
+      <c r="AP12" s="7">
+        <f t="shared" si="17"/>
+        <v>4031.749907836665</v>
+      </c>
+      <c r="AQ12" s="7">
+        <f t="shared" si="17"/>
+        <v>4186.1641343325064</v>
+      </c>
+      <c r="AR12" s="7">
+        <f t="shared" si="17"/>
+        <v>4345.7134487998928</v>
       </c>
     </row>
-    <row r="13" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>23</v>
       </c>
@@ -2351,654 +2418,661 @@
       <c r="U13" s="2">
         <v>-72</v>
       </c>
-      <c r="V13" s="2">
-        <f t="shared" ref="V13" si="18">V12*0.25</f>
-        <v>124.10990000000001</v>
-      </c>
-      <c r="Z13" s="2">
+      <c r="V13" s="13">
+        <f>AH13-U13-T13-S13</f>
+        <v>-153</v>
+      </c>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AD13" s="2">
         <f>SUM(C13:F13)</f>
         <v>283</v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AE13" s="2">
         <f>SUM(G13:J13)</f>
         <v>60</v>
       </c>
-      <c r="AB13" s="2">
+      <c r="AF13" s="2">
         <f>SUM(K13:N13)</f>
         <v>27</v>
       </c>
-      <c r="AC13" s="2">
+      <c r="AG13" s="2">
         <f>SUM(O13:R13)</f>
         <v>203</v>
       </c>
-      <c r="AD13" s="2">
-        <f>SUM(S13:V13)</f>
-        <v>289.10990000000004</v>
-      </c>
-      <c r="AE13" s="2">
-        <f>AE12*0.25</f>
-        <v>459.53136799999993</v>
-      </c>
-      <c r="AF13" s="2">
-        <f t="shared" ref="AF13:AN13" si="19">AF12*0.25</f>
-        <v>557.76451703999999</v>
-      </c>
-      <c r="AG13" s="2">
-        <f t="shared" si="19"/>
-        <v>607.49759729200048</v>
-      </c>
       <c r="AH13" s="2">
-        <f t="shared" si="19"/>
-        <v>647.78545776438057</v>
+        <v>12</v>
       </c>
       <c r="AI13" s="2">
-        <f t="shared" si="19"/>
-        <v>678.61218227625079</v>
+        <f>AI12*0.25</f>
+        <v>661.90562500000033</v>
       </c>
       <c r="AJ13" s="2">
-        <f t="shared" si="19"/>
-        <v>710.52010502858411</v>
+        <f t="shared" ref="AJ13:AR13" si="18">AJ12*0.25</f>
+        <v>766.83230500000013</v>
       </c>
       <c r="AK13" s="2">
-        <f t="shared" si="19"/>
-        <v>743.54407523159159</v>
+        <f t="shared" si="18"/>
+        <v>821.30411475000028</v>
       </c>
       <c r="AL13" s="2">
-        <f t="shared" si="19"/>
-        <v>777.7200286903801</v>
+        <f t="shared" si="18"/>
+        <v>865.59067602500022</v>
       </c>
       <c r="AM13" s="2">
-        <f t="shared" si="19"/>
-        <v>813.08502115370322</v>
+        <f t="shared" si="18"/>
+        <v>899.44140493545046</v>
       </c>
       <c r="AN13" s="2">
-        <f t="shared" si="19"/>
-        <v>849.67726267747946</v>
+        <f t="shared" si="18"/>
+        <v>934.42529744292699</v>
+      </c>
+      <c r="AO13" s="2">
+        <f t="shared" si="18"/>
+        <v>970.57830110550628</v>
+      </c>
+      <c r="AP13" s="2">
+        <f t="shared" si="18"/>
+        <v>1007.9374769591662</v>
+      </c>
+      <c r="AQ13" s="2">
+        <f t="shared" si="18"/>
+        <v>1046.5410335831266</v>
+      </c>
+      <c r="AR13" s="2">
+        <f t="shared" si="18"/>
+        <v>1086.4283621999732</v>
       </c>
     </row>
-    <row r="14" spans="1:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14"/>
       <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" ref="C14:P14" si="20">C12-C13</f>
+        <f t="shared" ref="C14:P14" si="19">C12-C13</f>
         <v>23</v>
       </c>
       <c r="D14" s="7">
+        <f t="shared" si="19"/>
+        <v>-20</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" si="19"/>
+        <v>2</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="19"/>
+        <v>-39</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="19"/>
+        <v>131</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="19"/>
+        <v>-125</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="19"/>
+        <v>-166</v>
+      </c>
+      <c r="J14" s="7">
+        <f t="shared" si="19"/>
+        <v>-270</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="19"/>
+        <v>-225</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="19"/>
+        <v>-302</v>
+      </c>
+      <c r="M14" s="7">
+        <f t="shared" si="19"/>
+        <v>65</v>
+      </c>
+      <c r="N14" s="7">
+        <f t="shared" si="19"/>
+        <v>-70</v>
+      </c>
+      <c r="O14" s="7">
+        <f t="shared" si="19"/>
+        <v>197</v>
+      </c>
+      <c r="P14" s="7">
+        <f t="shared" si="19"/>
+        <v>274</v>
+      </c>
+      <c r="Q14" s="7">
+        <f t="shared" ref="Q14:R14" si="20">Q12-Q13</f>
+        <v>300</v>
+      </c>
+      <c r="R14" s="7">
         <f t="shared" si="20"/>
-        <v>-20</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" si="20"/>
-        <v>2</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" si="20"/>
-        <v>-39</v>
-      </c>
-      <c r="G14" s="7">
-        <f t="shared" si="20"/>
-        <v>131</v>
-      </c>
-      <c r="H14" s="7">
-        <f t="shared" si="20"/>
-        <v>-125</v>
-      </c>
-      <c r="I14" s="7">
-        <f t="shared" si="20"/>
-        <v>-166</v>
-      </c>
-      <c r="J14" s="7">
-        <f t="shared" si="20"/>
-        <v>-270</v>
-      </c>
-      <c r="K14" s="7">
-        <f t="shared" si="20"/>
-        <v>-225</v>
-      </c>
-      <c r="L14" s="7">
-        <f t="shared" si="20"/>
-        <v>-302</v>
-      </c>
-      <c r="M14" s="7">
-        <f t="shared" si="20"/>
-        <v>65</v>
-      </c>
-      <c r="N14" s="7">
-        <f t="shared" si="20"/>
-        <v>-70</v>
-      </c>
-      <c r="O14" s="7">
-        <f t="shared" si="20"/>
-        <v>197</v>
-      </c>
-      <c r="P14" s="7">
-        <f t="shared" si="20"/>
-        <v>274</v>
-      </c>
-      <c r="Q14" s="7">
-        <f t="shared" ref="Q14:R14" si="21">Q12-Q13</f>
-        <v>300</v>
-      </c>
-      <c r="R14" s="7">
+        <v>367</v>
+      </c>
+      <c r="S14" s="7">
+        <f t="shared" ref="S14:V14" si="21">S12-S13</f>
+        <v>225</v>
+      </c>
+      <c r="T14" s="7">
         <f t="shared" si="21"/>
-        <v>367</v>
-      </c>
-      <c r="S14" s="7">
-        <f t="shared" ref="S14:V14" si="22">S12-S13</f>
-        <v>225</v>
-      </c>
-      <c r="T14" s="7">
-        <f t="shared" si="22"/>
         <v>-86</v>
       </c>
       <c r="U14" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>899</v>
       </c>
       <c r="V14" s="7">
-        <f t="shared" si="22"/>
-        <v>372.3297</v>
-      </c>
-      <c r="Z14" s="7">
-        <f>Z12-Z13</f>
-        <v>-34</v>
-      </c>
-      <c r="AA14" s="7">
-        <f>AA12-AA13</f>
-        <v>-430</v>
-      </c>
-      <c r="AB14" s="7">
-        <f>AB12-AB13</f>
-        <v>-532</v>
-      </c>
-      <c r="AC14" s="7">
-        <f>AC12-AC13</f>
-        <v>1138</v>
-      </c>
+        <f t="shared" si="21"/>
+        <v>1174</v>
+      </c>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
       <c r="AD14" s="7">
         <f>AD12-AD13</f>
-        <v>1410.3296999999993</v>
+        <v>-34</v>
       </c>
       <c r="AE14" s="7">
-        <f t="shared" ref="AE14:AN14" si="23">AE12-AE13</f>
-        <v>1378.5941039999998</v>
+        <f>AE12-AE13</f>
+        <v>-430</v>
       </c>
       <c r="AF14" s="7">
-        <f t="shared" si="23"/>
-        <v>1673.2935511199998</v>
+        <f>AF12-AF13</f>
+        <v>-532</v>
       </c>
       <c r="AG14" s="7">
-        <f t="shared" si="23"/>
-        <v>1822.4927918760013</v>
+        <f>AG12-AG13</f>
+        <v>1138</v>
       </c>
       <c r="AH14" s="7">
-        <f t="shared" si="23"/>
-        <v>1943.3563732931416</v>
+        <f>AH12-AH13</f>
+        <v>2212</v>
       </c>
       <c r="AI14" s="7">
-        <f t="shared" si="23"/>
-        <v>2035.8365468287525</v>
+        <f t="shared" ref="AI14:AR14" si="22">AI12-AI13</f>
+        <v>1985.716875000001</v>
       </c>
       <c r="AJ14" s="7">
-        <f t="shared" si="23"/>
-        <v>2131.5603150857523</v>
+        <f t="shared" si="22"/>
+        <v>2300.4969150000006</v>
       </c>
       <c r="AK14" s="7">
-        <f t="shared" si="23"/>
-        <v>2230.6322256947747</v>
+        <f t="shared" si="22"/>
+        <v>2463.9123442500008</v>
       </c>
       <c r="AL14" s="7">
-        <f t="shared" si="23"/>
-        <v>2333.1600860711405</v>
+        <f t="shared" si="22"/>
+        <v>2596.7720280750009</v>
       </c>
       <c r="AM14" s="7">
-        <f t="shared" si="23"/>
-        <v>2439.2550634611098</v>
+        <f t="shared" si="22"/>
+        <v>2698.3242148063514</v>
       </c>
       <c r="AN14" s="7">
-        <f t="shared" si="23"/>
-        <v>2549.0317880324383</v>
-      </c>
-      <c r="AO14" s="1">
-        <f>AN14*(1+$AQ$19)</f>
-        <v>2523.541470152114</v>
-      </c>
-      <c r="AP14" s="1">
-        <f t="shared" ref="AP14:DA14" si="24">AO14*(1+$AQ$19)</f>
-        <v>2498.3060554505928</v>
-      </c>
-      <c r="AQ14" s="1">
+        <f t="shared" si="22"/>
+        <v>2803.2758923287811</v>
+      </c>
+      <c r="AO14" s="7">
+        <f t="shared" si="22"/>
+        <v>2911.7349033165187</v>
+      </c>
+      <c r="AP14" s="7">
+        <f t="shared" si="22"/>
+        <v>3023.8124308774986</v>
+      </c>
+      <c r="AQ14" s="7">
+        <f t="shared" si="22"/>
+        <v>3139.6231007493798</v>
+      </c>
+      <c r="AR14" s="7">
+        <f t="shared" si="22"/>
+        <v>3259.2850865999199</v>
+      </c>
+      <c r="AS14" s="1">
+        <f>AR14*(1+$AU$19)</f>
+        <v>3226.6922357339208</v>
+      </c>
+      <c r="AT14" s="1">
+        <f t="shared" ref="AT14:DE14" si="23">AS14*(1+$AU$19)</f>
+        <v>3194.4253133765815</v>
+      </c>
+      <c r="AU14" s="1">
+        <f t="shared" si="23"/>
+        <v>3162.4810602428156</v>
+      </c>
+      <c r="AV14" s="1">
+        <f t="shared" si="23"/>
+        <v>3130.8562496403874</v>
+      </c>
+      <c r="AW14" s="1">
+        <f t="shared" si="23"/>
+        <v>3099.5476871439837</v>
+      </c>
+      <c r="AX14" s="1">
+        <f t="shared" si="23"/>
+        <v>3068.552210272544</v>
+      </c>
+      <c r="AY14" s="1">
+        <f t="shared" si="23"/>
+        <v>3037.8666881698186</v>
+      </c>
+      <c r="AZ14" s="1">
+        <f t="shared" si="23"/>
+        <v>3007.4880212881203</v>
+      </c>
+      <c r="BA14" s="1">
+        <f t="shared" si="23"/>
+        <v>2977.4131410752389</v>
+      </c>
+      <c r="BB14" s="1">
+        <f t="shared" si="23"/>
+        <v>2947.6390096644864</v>
+      </c>
+      <c r="BC14" s="1">
+        <f t="shared" si="23"/>
+        <v>2918.1626195678414</v>
+      </c>
+      <c r="BD14" s="1">
+        <f t="shared" si="23"/>
+        <v>2888.9809933721631</v>
+      </c>
+      <c r="BE14" s="1">
+        <f t="shared" si="23"/>
+        <v>2860.0911834384415</v>
+      </c>
+      <c r="BF14" s="1">
+        <f t="shared" si="23"/>
+        <v>2831.4902716040569</v>
+      </c>
+      <c r="BG14" s="1">
+        <f t="shared" si="23"/>
+        <v>2803.1753688880162</v>
+      </c>
+      <c r="BH14" s="1">
+        <f t="shared" si="23"/>
+        <v>2775.1436151991361</v>
+      </c>
+      <c r="BI14" s="1">
+        <f t="shared" si="23"/>
+        <v>2747.3921790471445</v>
+      </c>
+      <c r="BJ14" s="1">
+        <f t="shared" si="23"/>
+        <v>2719.9182572566729</v>
+      </c>
+      <c r="BK14" s="1">
+        <f t="shared" si="23"/>
+        <v>2692.7190746841061</v>
+      </c>
+      <c r="BL14" s="1">
+        <f t="shared" si="23"/>
+        <v>2665.7918839372651</v>
+      </c>
+      <c r="BM14" s="1">
+        <f t="shared" si="23"/>
+        <v>2639.1339650978925</v>
+      </c>
+      <c r="BN14" s="1">
+        <f t="shared" si="23"/>
+        <v>2612.7426254469137</v>
+      </c>
+      <c r="BO14" s="1">
+        <f t="shared" si="23"/>
+        <v>2586.6151991924444</v>
+      </c>
+      <c r="BP14" s="1">
+        <f t="shared" si="23"/>
+        <v>2560.7490472005197</v>
+      </c>
+      <c r="BQ14" s="1">
+        <f t="shared" si="23"/>
+        <v>2535.1415567285144</v>
+      </c>
+      <c r="BR14" s="1">
+        <f t="shared" si="23"/>
+        <v>2509.7901411612293</v>
+      </c>
+      <c r="BS14" s="1">
+        <f t="shared" si="23"/>
+        <v>2484.6922397496169</v>
+      </c>
+      <c r="BT14" s="1">
+        <f t="shared" si="23"/>
+        <v>2459.8453173521207</v>
+      </c>
+      <c r="BU14" s="1">
+        <f t="shared" si="23"/>
+        <v>2435.2468641785995</v>
+      </c>
+      <c r="BV14" s="1">
+        <f t="shared" si="23"/>
+        <v>2410.8943955368136</v>
+      </c>
+      <c r="BW14" s="1">
+        <f t="shared" si="23"/>
+        <v>2386.7854515814456</v>
+      </c>
+      <c r="BX14" s="1">
+        <f t="shared" si="23"/>
+        <v>2362.9175970656311</v>
+      </c>
+      <c r="BY14" s="1">
+        <f t="shared" si="23"/>
+        <v>2339.2884210949746</v>
+      </c>
+      <c r="BZ14" s="1">
+        <f t="shared" si="23"/>
+        <v>2315.8955368840248</v>
+      </c>
+      <c r="CA14" s="1">
+        <f t="shared" si="23"/>
+        <v>2292.7365815151843</v>
+      </c>
+      <c r="CB14" s="1">
+        <f t="shared" si="23"/>
+        <v>2269.8092157000324</v>
+      </c>
+      <c r="CC14" s="1">
+        <f t="shared" si="23"/>
+        <v>2247.1111235430321</v>
+      </c>
+      <c r="CD14" s="1">
+        <f t="shared" si="23"/>
+        <v>2224.6400123076019</v>
+      </c>
+      <c r="CE14" s="1">
+        <f t="shared" si="23"/>
+        <v>2202.3936121845259</v>
+      </c>
+      <c r="CF14" s="1">
+        <f t="shared" si="23"/>
+        <v>2180.3696760626808</v>
+      </c>
+      <c r="CG14" s="1">
+        <f t="shared" si="23"/>
+        <v>2158.5659793020541</v>
+      </c>
+      <c r="CH14" s="1">
+        <f t="shared" si="23"/>
+        <v>2136.9803195090335</v>
+      </c>
+      <c r="CI14" s="1">
+        <f t="shared" si="23"/>
+        <v>2115.6105163139432</v>
+      </c>
+      <c r="CJ14" s="1">
+        <f t="shared" si="23"/>
+        <v>2094.4544111508039</v>
+      </c>
+      <c r="CK14" s="1">
+        <f t="shared" si="23"/>
+        <v>2073.5098670392958</v>
+      </c>
+      <c r="CL14" s="1">
+        <f t="shared" si="23"/>
+        <v>2052.7747683689026</v>
+      </c>
+      <c r="CM14" s="1">
+        <f t="shared" si="23"/>
+        <v>2032.2470206852136</v>
+      </c>
+      <c r="CN14" s="1">
+        <f t="shared" si="23"/>
+        <v>2011.9245504783614</v>
+      </c>
+      <c r="CO14" s="1">
+        <f t="shared" si="23"/>
+        <v>1991.8053049735779</v>
+      </c>
+      <c r="CP14" s="1">
+        <f t="shared" si="23"/>
+        <v>1971.8872519238421</v>
+      </c>
+      <c r="CQ14" s="1">
+        <f t="shared" si="23"/>
+        <v>1952.1683794046037</v>
+      </c>
+      <c r="CR14" s="1">
+        <f t="shared" si="23"/>
+        <v>1932.6466956105576</v>
+      </c>
+      <c r="CS14" s="1">
+        <f t="shared" si="23"/>
+        <v>1913.320228654452</v>
+      </c>
+      <c r="CT14" s="1">
+        <f t="shared" si="23"/>
+        <v>1894.1870263679075</v>
+      </c>
+      <c r="CU14" s="1">
+        <f t="shared" si="23"/>
+        <v>1875.2451561042285</v>
+      </c>
+      <c r="CV14" s="1">
+        <f t="shared" si="23"/>
+        <v>1856.4927045431862</v>
+      </c>
+      <c r="CW14" s="1">
+        <f t="shared" si="23"/>
+        <v>1837.9277774977543</v>
+      </c>
+      <c r="CX14" s="1">
+        <f t="shared" si="23"/>
+        <v>1819.5484997227768</v>
+      </c>
+      <c r="CY14" s="1">
+        <f t="shared" si="23"/>
+        <v>1801.353014725549</v>
+      </c>
+      <c r="CZ14" s="1">
+        <f t="shared" si="23"/>
+        <v>1783.3394845782934</v>
+      </c>
+      <c r="DA14" s="1">
+        <f t="shared" si="23"/>
+        <v>1765.5060897325104</v>
+      </c>
+      <c r="DB14" s="1">
+        <f t="shared" si="23"/>
+        <v>1747.8510288351854</v>
+      </c>
+      <c r="DC14" s="1">
+        <f t="shared" si="23"/>
+        <v>1730.3725185468336</v>
+      </c>
+      <c r="DD14" s="1">
+        <f t="shared" si="23"/>
+        <v>1713.0687933613654</v>
+      </c>
+      <c r="DE14" s="1">
+        <f t="shared" si="23"/>
+        <v>1695.9381054277517</v>
+      </c>
+      <c r="DF14" s="1">
+        <f t="shared" ref="DF14:EW14" si="24">DE14*(1+$AU$19)</f>
+        <v>1678.9787243734741</v>
+      </c>
+      <c r="DG14" s="1">
         <f t="shared" si="24"/>
-        <v>2473.322994896087</v>
-      </c>
-      <c r="AR14" s="1">
+        <v>1662.1889371297393</v>
+      </c>
+      <c r="DH14" s="1">
         <f t="shared" si="24"/>
-        <v>2448.5897649471262</v>
-      </c>
-      <c r="AS14" s="1">
+        <v>1645.567047758442</v>
+      </c>
+      <c r="DI14" s="1">
         <f t="shared" si="24"/>
-        <v>2424.1038672976551</v>
-      </c>
-      <c r="AT14" s="1">
+        <v>1629.1113772808576</v>
+      </c>
+      <c r="DJ14" s="1">
         <f t="shared" si="24"/>
-        <v>2399.8628286246785</v>
-      </c>
-      <c r="AU14" s="1">
+        <v>1612.820263508049</v>
+      </c>
+      <c r="DK14" s="1">
         <f t="shared" si="24"/>
-        <v>2375.8642003384316</v>
-      </c>
-      <c r="AV14" s="1">
+        <v>1596.6920608729686</v>
+      </c>
+      <c r="DL14" s="1">
         <f t="shared" si="24"/>
-        <v>2352.1055583350471</v>
-      </c>
-      <c r="AW14" s="1">
+        <v>1580.7251402642389</v>
+      </c>
+      <c r="DM14" s="1">
         <f t="shared" si="24"/>
-        <v>2328.5845027516966</v>
-      </c>
-      <c r="AX14" s="1">
+        <v>1564.9178888615966</v>
+      </c>
+      <c r="DN14" s="1">
         <f t="shared" si="24"/>
-        <v>2305.2986577241795</v>
-      </c>
-      <c r="AY14" s="1">
+        <v>1549.2687099729806</v>
+      </c>
+      <c r="DO14" s="1">
         <f t="shared" si="24"/>
-        <v>2282.2456711469376</v>
-      </c>
-      <c r="AZ14" s="1">
+        <v>1533.7760228732507</v>
+      </c>
+      <c r="DP14" s="1">
         <f t="shared" si="24"/>
-        <v>2259.4232144354683</v>
-      </c>
-      <c r="BA14" s="1">
+        <v>1518.4382626445181</v>
+      </c>
+      <c r="DQ14" s="1">
         <f t="shared" si="24"/>
-        <v>2236.8289822911133</v>
-      </c>
-      <c r="BB14" s="1">
+        <v>1503.253880018073</v>
+      </c>
+      <c r="DR14" s="1">
         <f t="shared" si="24"/>
-        <v>2214.4606924682021</v>
-      </c>
-      <c r="BC14" s="1">
+        <v>1488.2213412178924</v>
+      </c>
+      <c r="DS14" s="1">
         <f t="shared" si="24"/>
-        <v>2192.3160855435199</v>
-      </c>
-      <c r="BD14" s="1">
+        <v>1473.3391278057134</v>
+      </c>
+      <c r="DT14" s="1">
         <f t="shared" si="24"/>
-        <v>2170.3929246880848</v>
-      </c>
-      <c r="BE14" s="1">
+        <v>1458.6057365276563</v>
+      </c>
+      <c r="DU14" s="1">
         <f t="shared" si="24"/>
-        <v>2148.688995441204</v>
-      </c>
-      <c r="BF14" s="1">
+        <v>1444.0196791623798</v>
+      </c>
+      <c r="DV14" s="1">
         <f t="shared" si="24"/>
-        <v>2127.2021054867919</v>
-      </c>
-      <c r="BG14" s="1">
+        <v>1429.5794823707561</v>
+      </c>
+      <c r="DW14" s="1">
         <f t="shared" si="24"/>
-        <v>2105.9300844319241</v>
-      </c>
-      <c r="BH14" s="1">
+        <v>1415.2836875470484</v>
+      </c>
+      <c r="DX14" s="1">
         <f t="shared" si="24"/>
-        <v>2084.8707835876048</v>
-      </c>
-      <c r="BI14" s="1">
+        <v>1401.1308506715779</v>
+      </c>
+      <c r="DY14" s="1">
         <f t="shared" si="24"/>
-        <v>2064.0220757517286</v>
-      </c>
-      <c r="BJ14" s="1">
+        <v>1387.1195421648622</v>
+      </c>
+      <c r="DZ14" s="1">
         <f t="shared" si="24"/>
-        <v>2043.3818549942114</v>
-      </c>
-      <c r="BK14" s="1">
+        <v>1373.2483467432135</v>
+      </c>
+      <c r="EA14" s="1">
         <f t="shared" si="24"/>
-        <v>2022.9480364442693</v>
-      </c>
-      <c r="BL14" s="1">
+        <v>1359.5158632757814</v>
+      </c>
+      <c r="EB14" s="1">
         <f t="shared" si="24"/>
-        <v>2002.7185560798266</v>
-      </c>
-      <c r="BM14" s="1">
+        <v>1345.9207046430236</v>
+      </c>
+      <c r="EC14" s="1">
         <f t="shared" si="24"/>
-        <v>1982.6913705190284</v>
-      </c>
-      <c r="BN14" s="1">
+        <v>1332.4614975965933</v>
+      </c>
+      <c r="ED14" s="1">
         <f t="shared" si="24"/>
-        <v>1962.8644568138382</v>
-      </c>
-      <c r="BO14" s="1">
+        <v>1319.1368826206274</v>
+      </c>
+      <c r="EE14" s="1">
         <f t="shared" si="24"/>
-        <v>1943.2358122456997</v>
-      </c>
-      <c r="BP14" s="1">
+        <v>1305.945513794421</v>
+      </c>
+      <c r="EF14" s="1">
         <f t="shared" si="24"/>
-        <v>1923.8034541232425</v>
-      </c>
-      <c r="BQ14" s="1">
+        <v>1292.8860586564767</v>
+      </c>
+      <c r="EG14" s="1">
         <f t="shared" si="24"/>
-        <v>1904.56541958201</v>
-      </c>
-      <c r="BR14" s="1">
+        <v>1279.957198069912</v>
+      </c>
+      <c r="EH14" s="1">
         <f t="shared" si="24"/>
-        <v>1885.5197653861899</v>
-      </c>
-      <c r="BS14" s="1">
+        <v>1267.157626089213</v>
+      </c>
+      <c r="EI14" s="1">
         <f t="shared" si="24"/>
-        <v>1866.6645677323279</v>
-      </c>
-      <c r="BT14" s="1">
+        <v>1254.4860498283208</v>
+      </c>
+      <c r="EJ14" s="1">
         <f t="shared" si="24"/>
-        <v>1847.9979220550047</v>
-      </c>
-      <c r="BU14" s="1">
+        <v>1241.9411893300376</v>
+      </c>
+      <c r="EK14" s="1">
         <f t="shared" si="24"/>
-        <v>1829.5179428344545</v>
-      </c>
-      <c r="BV14" s="1">
+        <v>1229.5217774367372</v>
+      </c>
+      <c r="EL14" s="1">
         <f t="shared" si="24"/>
-        <v>1811.2227634061101</v>
-      </c>
-      <c r="BW14" s="1">
+        <v>1217.2265596623699</v>
+      </c>
+      <c r="EM14" s="1">
         <f t="shared" si="24"/>
-        <v>1793.1105357720489</v>
-      </c>
-      <c r="BX14" s="1">
+        <v>1205.0542940657463</v>
+      </c>
+      <c r="EN14" s="1">
         <f t="shared" si="24"/>
-        <v>1775.1794304143284</v>
-      </c>
-      <c r="BY14" s="1">
+        <v>1193.0037511250887</v>
+      </c>
+      <c r="EO14" s="1">
         <f t="shared" si="24"/>
-        <v>1757.4276361101852</v>
-      </c>
-      <c r="BZ14" s="1">
+        <v>1181.0737136138378</v>
+      </c>
+      <c r="EP14" s="1">
         <f t="shared" si="24"/>
-        <v>1739.8533597490832</v>
-      </c>
-      <c r="CA14" s="1">
+        <v>1169.2629764776993</v>
+      </c>
+      <c r="EQ14" s="1">
         <f t="shared" si="24"/>
-        <v>1722.4548261515924</v>
-      </c>
-      <c r="CB14" s="1">
+        <v>1157.5703467129224</v>
+      </c>
+      <c r="ER14" s="1">
         <f t="shared" si="24"/>
-        <v>1705.2302778900764</v>
-      </c>
-      <c r="CC14" s="1">
+        <v>1145.9946432457932</v>
+      </c>
+      <c r="ES14" s="1">
         <f t="shared" si="24"/>
-        <v>1688.1779751111756</v>
-      </c>
-      <c r="CD14" s="1">
+        <v>1134.5346968133354</v>
+      </c>
+      <c r="ET14" s="1">
         <f t="shared" si="24"/>
-        <v>1671.2961953600638</v>
-      </c>
-      <c r="CE14" s="1">
+        <v>1123.1893498452021</v>
+      </c>
+      <c r="EU14" s="1">
         <f t="shared" si="24"/>
-        <v>1654.5832334064633</v>
-      </c>
-      <c r="CF14" s="1">
+        <v>1111.95745634675</v>
+      </c>
+      <c r="EV14" s="1">
         <f t="shared" si="24"/>
-        <v>1638.0374010723986</v>
-      </c>
-      <c r="CG14" s="1">
+        <v>1100.8378817832825</v>
+      </c>
+      <c r="EW14" s="1">
         <f t="shared" si="24"/>
-        <v>1621.6570270616746</v>
-      </c>
-      <c r="CH14" s="1">
-        <f t="shared" si="24"/>
-        <v>1605.4404567910578</v>
-      </c>
-      <c r="CI14" s="1">
-        <f t="shared" si="24"/>
-        <v>1589.3860522231473</v>
-      </c>
-      <c r="CJ14" s="1">
-        <f t="shared" si="24"/>
-        <v>1573.4921917009158</v>
-      </c>
-      <c r="CK14" s="1">
-        <f t="shared" si="24"/>
-        <v>1557.7572697839066</v>
-      </c>
-      <c r="CL14" s="1">
-        <f t="shared" si="24"/>
-        <v>1542.1796970860676</v>
-      </c>
-      <c r="CM14" s="1">
-        <f t="shared" si="24"/>
-        <v>1526.7579001152069</v>
-      </c>
-      <c r="CN14" s="1">
-        <f t="shared" si="24"/>
-        <v>1511.4903211140547</v>
-      </c>
-      <c r="CO14" s="1">
-        <f t="shared" si="24"/>
-        <v>1496.3754179029143</v>
-      </c>
-      <c r="CP14" s="1">
-        <f t="shared" si="24"/>
-        <v>1481.4116637238851</v>
-      </c>
-      <c r="CQ14" s="1">
-        <f t="shared" si="24"/>
-        <v>1466.5975470866463</v>
-      </c>
-      <c r="CR14" s="1">
-        <f t="shared" si="24"/>
-        <v>1451.9315716157798</v>
-      </c>
-      <c r="CS14" s="1">
-        <f t="shared" si="24"/>
-        <v>1437.4122558996221</v>
-      </c>
-      <c r="CT14" s="1">
-        <f t="shared" si="24"/>
-        <v>1423.0381333406258</v>
-      </c>
-      <c r="CU14" s="1">
-        <f t="shared" si="24"/>
-        <v>1408.8077520072195</v>
-      </c>
-      <c r="CV14" s="1">
-        <f t="shared" si="24"/>
-        <v>1394.7196744871474</v>
-      </c>
-      <c r="CW14" s="1">
-        <f t="shared" si="24"/>
-        <v>1380.7724777422759</v>
-      </c>
-      <c r="CX14" s="1">
-        <f t="shared" si="24"/>
-        <v>1366.9647529648532</v>
-      </c>
-      <c r="CY14" s="1">
-        <f t="shared" si="24"/>
-        <v>1353.2951054352047</v>
-      </c>
-      <c r="CZ14" s="1">
-        <f t="shared" si="24"/>
-        <v>1339.7621543808527</v>
-      </c>
-      <c r="DA14" s="1">
-        <f t="shared" si="24"/>
-        <v>1326.3645328370442</v>
-      </c>
-      <c r="DB14" s="1">
-        <f t="shared" ref="DB14:ES14" si="25">DA14*(1+$AQ$19)</f>
-        <v>1313.1008875086736</v>
-      </c>
-      <c r="DC14" s="1">
-        <f t="shared" si="25"/>
-        <v>1299.9698786335869</v>
-      </c>
-      <c r="DD14" s="1">
-        <f t="shared" si="25"/>
-        <v>1286.9701798472511</v>
-      </c>
-      <c r="DE14" s="1">
-        <f t="shared" si="25"/>
-        <v>1274.1004780487785</v>
-      </c>
-      <c r="DF14" s="1">
-        <f t="shared" si="25"/>
-        <v>1261.3594732682907</v>
-      </c>
-      <c r="DG14" s="1">
-        <f t="shared" si="25"/>
-        <v>1248.7458785356077</v>
-      </c>
-      <c r="DH14" s="1">
-        <f t="shared" si="25"/>
-        <v>1236.2584197502517</v>
-      </c>
-      <c r="DI14" s="1">
-        <f t="shared" si="25"/>
-        <v>1223.8958355527493</v>
-      </c>
-      <c r="DJ14" s="1">
-        <f t="shared" si="25"/>
-        <v>1211.6568771972218</v>
-      </c>
-      <c r="DK14" s="1">
-        <f t="shared" si="25"/>
-        <v>1199.5403084252496</v>
-      </c>
-      <c r="DL14" s="1">
-        <f t="shared" si="25"/>
-        <v>1187.544905340997</v>
-      </c>
-      <c r="DM14" s="1">
-        <f t="shared" si="25"/>
-        <v>1175.6694562875871</v>
-      </c>
-      <c r="DN14" s="1">
-        <f t="shared" si="25"/>
-        <v>1163.9127617247111</v>
-      </c>
-      <c r="DO14" s="1">
-        <f t="shared" si="25"/>
-        <v>1152.273634107464</v>
-      </c>
-      <c r="DP14" s="1">
-        <f t="shared" si="25"/>
-        <v>1140.7508977663892</v>
-      </c>
-      <c r="DQ14" s="1">
-        <f t="shared" si="25"/>
-        <v>1129.3433887887254</v>
-      </c>
-      <c r="DR14" s="1">
-        <f t="shared" si="25"/>
-        <v>1118.0499549008382</v>
-      </c>
-      <c r="DS14" s="1">
-        <f t="shared" si="25"/>
-        <v>1106.8694553518299</v>
-      </c>
-      <c r="DT14" s="1">
-        <f t="shared" si="25"/>
-        <v>1095.8007607983116</v>
-      </c>
-      <c r="DU14" s="1">
-        <f t="shared" si="25"/>
-        <v>1084.8427531903285</v>
-      </c>
-      <c r="DV14" s="1">
-        <f t="shared" si="25"/>
-        <v>1073.9943256584252</v>
-      </c>
-      <c r="DW14" s="1">
-        <f t="shared" si="25"/>
-        <v>1063.254382401841</v>
-      </c>
-      <c r="DX14" s="1">
-        <f t="shared" si="25"/>
-        <v>1052.6218385778225</v>
-      </c>
-      <c r="DY14" s="1">
-        <f t="shared" si="25"/>
-        <v>1042.0956201920442</v>
-      </c>
-      <c r="DZ14" s="1">
-        <f t="shared" si="25"/>
-        <v>1031.6746639901237</v>
-      </c>
-      <c r="EA14" s="1">
-        <f t="shared" si="25"/>
-        <v>1021.3579173502225</v>
-      </c>
-      <c r="EB14" s="1">
-        <f t="shared" si="25"/>
-        <v>1011.1443381767202</v>
-      </c>
-      <c r="EC14" s="1">
-        <f t="shared" si="25"/>
-        <v>1001.032894794953</v>
-      </c>
-      <c r="ED14" s="1">
-        <f t="shared" si="25"/>
-        <v>991.02256584700342</v>
-      </c>
-      <c r="EE14" s="1">
-        <f t="shared" si="25"/>
-        <v>981.11234018853338</v>
-      </c>
-      <c r="EF14" s="1">
-        <f t="shared" si="25"/>
-        <v>971.30121678664807</v>
-      </c>
-      <c r="EG14" s="1">
-        <f t="shared" si="25"/>
-        <v>961.58820461878156</v>
-      </c>
-      <c r="EH14" s="1">
-        <f t="shared" si="25"/>
-        <v>951.97232257259373</v>
-      </c>
-      <c r="EI14" s="1">
-        <f t="shared" si="25"/>
-        <v>942.45259934686783</v>
-      </c>
-      <c r="EJ14" s="1">
-        <f t="shared" si="25"/>
-        <v>933.02807335339912</v>
-      </c>
-      <c r="EK14" s="1">
-        <f t="shared" si="25"/>
-        <v>923.69779261986514</v>
-      </c>
-      <c r="EL14" s="1">
-        <f t="shared" si="25"/>
-        <v>914.46081469366652</v>
-      </c>
-      <c r="EM14" s="1">
-        <f t="shared" si="25"/>
-        <v>905.31620654672986</v>
-      </c>
-      <c r="EN14" s="1">
-        <f t="shared" si="25"/>
-        <v>896.26304448126257</v>
-      </c>
-      <c r="EO14" s="1">
-        <f t="shared" si="25"/>
-        <v>887.30041403644998</v>
-      </c>
-      <c r="EP14" s="1">
-        <f t="shared" si="25"/>
-        <v>878.42740989608546</v>
-      </c>
-      <c r="EQ14" s="1">
-        <f t="shared" si="25"/>
-        <v>869.64313579712461</v>
-      </c>
-      <c r="ER14" s="1">
-        <f t="shared" si="25"/>
-        <v>860.94670443915334</v>
-      </c>
-      <c r="ES14" s="1">
-        <f t="shared" si="25"/>
-        <v>852.33723739476181</v>
+        <v>1089.8295029654496</v>
       </c>
     </row>
-    <row r="15" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>2</v>
       </c>
@@ -3062,213 +3136,221 @@
         <v>206</v>
       </c>
       <c r="V15" s="2">
-        <f>206</f>
-        <v>206</v>
-      </c>
-      <c r="Z15" s="2">
+        <f>205.8</f>
+        <v>205.8</v>
+      </c>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AD15" s="2">
         <v>200</v>
       </c>
-      <c r="AA15" s="2">
+      <c r="AE15" s="2">
         <v>193.2</v>
       </c>
-      <c r="AB15" s="2">
+      <c r="AF15" s="2">
         <v>196</v>
       </c>
-      <c r="AC15" s="2">
+      <c r="AG15" s="2">
         <f>203.8</f>
         <v>203.8</v>
       </c>
-      <c r="AD15" s="2">
-        <f>206</f>
-        <v>206</v>
-      </c>
-      <c r="AE15" s="2">
-        <f>206</f>
-        <v>206</v>
-      </c>
-      <c r="AF15" s="2">
-        <f>206</f>
-        <v>206</v>
-      </c>
-      <c r="AG15" s="2">
-        <f>206</f>
-        <v>206</v>
-      </c>
       <c r="AH15" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
       <c r="AI15" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
       <c r="AJ15" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
       <c r="AK15" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
       <c r="AL15" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
       <c r="AM15" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
       <c r="AN15" s="2">
-        <f>206</f>
-        <v>206</v>
+        <f>205.8</f>
+        <v>205.8</v>
+      </c>
+      <c r="AO15" s="2">
+        <f>205.8</f>
+        <v>205.8</v>
+      </c>
+      <c r="AP15" s="2">
+        <f>205.8</f>
+        <v>205.8</v>
+      </c>
+      <c r="AQ15" s="2">
+        <f>205.8</f>
+        <v>205.8</v>
+      </c>
+      <c r="AR15" s="2">
+        <f>205.8</f>
+        <v>205.8</v>
       </c>
     </row>
-    <row r="16" spans="1:149" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:153" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:P16" si="26">C14/C15</f>
+        <f t="shared" ref="C16:P16" si="25">C14/C15</f>
         <v>0.11923276308968377</v>
       </c>
       <c r="D16" s="8">
+        <f t="shared" si="25"/>
+        <v>-0.10368066355624676</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="25"/>
+        <v>1.0368066355624676E-2</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="25"/>
+        <v>-0.20217729393468117</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="25"/>
+        <v>0.67910834629341621</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="25"/>
+        <v>-0.6480041472265422</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="25"/>
+        <v>-0.859658208182289</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="25"/>
+        <v>-1.3975155279503106</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="25"/>
+        <v>-1.1621900826446281</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="25"/>
+        <v>-1.5534979423868311</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" si="25"/>
+        <v>0.33436213991769548</v>
+      </c>
+      <c r="N16" s="8">
+        <f t="shared" si="25"/>
+        <v>-0.35714285714285715</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="25"/>
+        <v>0.99494949494949492</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="25"/>
+        <v>1.37</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" ref="Q16:R16" si="26">Q14/Q15</f>
+        <v>1.4880952380952381</v>
+      </c>
+      <c r="R16" s="8">
         <f t="shared" si="26"/>
-        <v>-0.10368066355624676</v>
-      </c>
-      <c r="E16" s="8">
-        <f t="shared" si="26"/>
-        <v>1.0368066355624676E-2</v>
-      </c>
-      <c r="F16" s="8">
-        <f t="shared" si="26"/>
-        <v>-0.20217729393468117</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="26"/>
-        <v>0.67910834629341621</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="26"/>
-        <v>-0.6480041472265422</v>
-      </c>
-      <c r="I16" s="8">
-        <f t="shared" si="26"/>
-        <v>-0.859658208182289</v>
-      </c>
-      <c r="J16" s="8">
-        <f t="shared" si="26"/>
-        <v>-1.3975155279503106</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" si="26"/>
-        <v>-1.1621900826446281</v>
-      </c>
-      <c r="L16" s="8">
-        <f t="shared" si="26"/>
-        <v>-1.5534979423868311</v>
-      </c>
-      <c r="M16" s="8">
-        <f t="shared" si="26"/>
-        <v>0.33436213991769548</v>
-      </c>
-      <c r="N16" s="8">
-        <f t="shared" si="26"/>
-        <v>-0.35714285714285715</v>
-      </c>
-      <c r="O16" s="8">
-        <f t="shared" si="26"/>
-        <v>0.99494949494949492</v>
-      </c>
-      <c r="P16" s="8">
-        <f t="shared" si="26"/>
-        <v>1.37</v>
-      </c>
-      <c r="Q16" s="8">
-        <f t="shared" ref="Q16:R16" si="27">Q14/Q15</f>
-        <v>1.4880952380952381</v>
-      </c>
-      <c r="R16" s="8">
+        <v>1.8007850834151127</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" ref="S16:V16" si="27">S14/S15</f>
+        <v>1.1002444987775062</v>
+      </c>
+      <c r="T16" s="8">
         <f t="shared" si="27"/>
-        <v>1.8007850834151127</v>
-      </c>
-      <c r="S16" s="8">
-        <f t="shared" ref="S16:V16" si="28">S14/S15</f>
-        <v>1.1002444987775062</v>
-      </c>
-      <c r="T16" s="8">
-        <f t="shared" si="28"/>
         <v>-0.41869522882181109</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>4.3640776699029127</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="28"/>
-        <v>1.8074257281553399</v>
-      </c>
-      <c r="Z16" s="8">
-        <f>Z14/Z15</f>
-        <v>-0.17</v>
-      </c>
-      <c r="AA16" s="8">
-        <f>AA14/AA15</f>
-        <v>-2.2256728778467911</v>
-      </c>
-      <c r="AB16" s="8">
-        <f>AB14/AB15</f>
-        <v>-2.7142857142857144</v>
-      </c>
-      <c r="AC16" s="8">
-        <f>AC14/AC15</f>
-        <v>5.5839057899901858</v>
-      </c>
+        <f t="shared" si="27"/>
+        <v>5.704567541302235</v>
+      </c>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
       <c r="AD16" s="8">
         <f>AD14/AD15</f>
-        <v>6.846260679611647</v>
+        <v>-0.17</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" ref="AE16:AN16" si="29">AE14/AE15</f>
-        <v>6.6922043883495137</v>
+        <f>AE14/AE15</f>
+        <v>-2.2256728778467911</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="29"/>
-        <v>8.1227842287378635</v>
+        <f>AF14/AF15</f>
+        <v>-2.7142857142857144</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="29"/>
-        <v>8.8470523877475795</v>
+        <f>AG14/AG15</f>
+        <v>5.5839057899901858</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="29"/>
-        <v>9.4337688023938906</v>
+        <f>AH14/AH15</f>
+        <v>10.74829931972789</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="29"/>
-        <v>9.8827016836347212</v>
+        <f t="shared" ref="AI16:AR16" si="28">AI14/AI15</f>
+        <v>9.6487700437317834</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="29"/>
-        <v>10.347380170319186</v>
+        <f t="shared" si="28"/>
+        <v>11.178313483965017</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="29"/>
-        <v>10.828311775217353</v>
+        <f t="shared" si="28"/>
+        <v>11.972363188775514</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="29"/>
-        <v>11.326019835296799</v>
+        <f t="shared" si="28"/>
+        <v>12.617939883746359</v>
       </c>
       <c r="AM16" s="8">
-        <f t="shared" si="29"/>
-        <v>11.841043997384029</v>
+        <f t="shared" si="28"/>
+        <v>13.111390742499276</v>
       </c>
       <c r="AN16" s="8">
-        <f t="shared" si="29"/>
-        <v>12.37394071860407</v>
+        <f t="shared" si="28"/>
+        <v>13.621360021033921</v>
+      </c>
+      <c r="AO16" s="8">
+        <f t="shared" si="28"/>
+        <v>14.148371736231869</v>
+      </c>
+      <c r="AP16" s="8">
+        <f t="shared" si="28"/>
+        <v>14.692966136430993</v>
+      </c>
+      <c r="AQ16" s="8">
+        <f t="shared" si="28"/>
+        <v>15.25570019800476</v>
+      </c>
+      <c r="AR16" s="8">
+        <f t="shared" si="28"/>
+        <v>15.837148137025849</v>
       </c>
     </row>
-    <row r="18" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>42</v>
       </c>
@@ -3277,39 +3359,39 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9">
-        <f t="shared" ref="G18:O18" si="30">G3/C3-1</f>
+        <f t="shared" ref="G18:O18" si="29">G3/C3-1</f>
         <v>0.23940381928272014</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.2286572286572286</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.21391443422630951</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.17738936407586459</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.14317925591882741</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.10928770949720668</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.10573122529644263</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.15950726468730259</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0.19526627218934922</v>
       </c>
       <c r="P18" s="9">
@@ -3317,149 +3399,165 @@
         <v>0.19830028328611893</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" ref="Q18:R18" si="31">Q3/M3-1</f>
+        <f t="shared" ref="Q18:R18" si="30">Q3/M3-1</f>
         <v>0.18796544533809945</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0.15554344865159364</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" ref="S18" si="32">S3/O3-1</f>
+        <f t="shared" ref="S18" si="31">S3/O3-1</f>
         <v>0.1523652365236523</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18" si="33">T3/P3-1</f>
+        <f t="shared" ref="T18" si="32">T3/P3-1</f>
         <v>0.1013921723141582</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" ref="U18" si="34">U3/Q3-1</f>
+        <f t="shared" ref="U18" si="33">U3/Q3-1</f>
         <v>7.1213640922768384E-2</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" ref="V18" si="35">V3/R3-1</f>
+        <f t="shared" ref="V18" si="34">V3/R3-1</f>
+        <v>6.8128241395568168E-2</v>
+      </c>
+      <c r="W18" s="9">
+        <f t="shared" ref="W18" si="35">W3/S3-1</f>
+        <v>7.398568019093088E-2</v>
+      </c>
+      <c r="X18" s="9">
+        <f t="shared" ref="X18" si="36">X3/T3-1</f>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9" t="e">
-        <f>Y3/X3-1</f>
+      <c r="Y18" s="9">
+        <f t="shared" ref="Y18" si="37">Y3/U3-1</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="Z18" s="9">
+        <f t="shared" ref="Z18" si="38">Z3/V3-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9" t="e">
+        <f>AC3/AB3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z18" s="9" t="e">
-        <f t="shared" ref="Z18:AN18" si="36">Z3/Y3-1</f>
+      <c r="AD18" s="9" t="e">
+        <f t="shared" ref="AD18:AR18" si="39">AD3/AC3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AE18" s="9">
+        <f t="shared" si="39"/>
         <v>0.21297062474141493</v>
       </c>
-      <c r="AB18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AF18" s="9">
+        <f t="shared" si="39"/>
         <v>0.12961541741280813</v>
       </c>
-      <c r="AC18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AG18" s="9">
+        <f t="shared" si="39"/>
         <v>0.18313580433305665</v>
       </c>
-      <c r="AD18" s="9">
-        <f t="shared" si="36"/>
-        <v>9.4335481401135679E-2</v>
-      </c>
-      <c r="AE18" s="9">
-        <f t="shared" si="36"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AF18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AH18" s="9">
+        <f t="shared" si="39"/>
+        <v>9.6535443118739295E-2</v>
+      </c>
+      <c r="AI18" s="9">
+        <f t="shared" si="39"/>
+        <v>6.077330385197266E-2</v>
+      </c>
+      <c r="AJ18" s="9">
+        <f t="shared" si="39"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AG18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AK18" s="9">
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AH18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AL18" s="9">
+        <f t="shared" si="39"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AI18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AM18" s="9">
+        <f t="shared" si="39"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AJ18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AN18" s="9">
+        <f t="shared" si="39"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AK18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AO18" s="9">
+        <f t="shared" si="39"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AL18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AP18" s="9">
+        <f t="shared" si="39"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AQ18" s="9">
+        <f t="shared" si="39"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN18" s="9">
-        <f t="shared" si="36"/>
+      <c r="AR18" s="9">
+        <f t="shared" si="39"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:O19" si="37">C5/C3</f>
+        <f t="shared" ref="C19:O19" si="40">C5/C3</f>
         <v>0.25523986958546807</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.28442728442728443</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.26709316273490602</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.26478244700632203</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.25216084178880122</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.24581005586592178</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.24703557312252963</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.25300063171193937</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.2518080210387903</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.24110796348756688</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.26362823949955316</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.26695723236175428</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.27612761276127612</v>
       </c>
       <c r="P19" s="9">
@@ -3467,105 +3565,121 @@
         <v>0.29209351195166799</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" ref="Q19:R19" si="38">Q5/Q3</f>
+        <f t="shared" ref="Q19:R19" si="41">Q5/Q3</f>
         <v>0.31093279839518556</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.32248939179632247</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="39">S5/S3</f>
+        <f t="shared" ref="S19:V19" si="42">S5/S3</f>
         <v>0.31646778042959428</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.3148103982828524</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.31624531835205993</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="39"/>
-        <v>0.32</v>
-      </c>
-      <c r="X19" s="9" t="e">
-        <f t="shared" ref="X19:AN19" si="40">X5/X3</f>
+        <f t="shared" si="42"/>
+        <v>0.33083204590598103</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" ref="W19:Z19" si="43">W5/W3</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="9">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="9">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="9" t="e">
+        <f t="shared" ref="AB19:AR19" si="44">AB5/AB3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y19" s="9" t="e">
-        <f t="shared" si="40"/>
+      <c r="AC19" s="9" t="e">
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z19" s="9">
-        <f t="shared" si="40"/>
+      <c r="AD19" s="9">
+        <f t="shared" si="44"/>
         <v>0.26799751758378154</v>
       </c>
-      <c r="AA19" s="9">
-        <f t="shared" si="40"/>
+      <c r="AE19" s="9">
+        <f t="shared" si="44"/>
         <v>0.2495096785196555</v>
       </c>
-      <c r="AB19" s="9">
-        <f t="shared" si="40"/>
+      <c r="AF19" s="9">
+        <f t="shared" si="44"/>
         <v>0.25643541934022795</v>
       </c>
-      <c r="AC19" s="9">
-        <f t="shared" si="40"/>
+      <c r="AG19" s="9">
+        <f t="shared" si="44"/>
         <v>0.30141006827027372</v>
       </c>
-      <c r="AD19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.31693321641463845</v>
-      </c>
-      <c r="AE19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.32</v>
-      </c>
-      <c r="AF19" s="9">
-        <f t="shared" si="40"/>
+      <c r="AH19" s="9">
+        <f t="shared" si="44"/>
+        <v>0.31979518212498548</v>
+      </c>
+      <c r="AI19" s="9">
+        <f t="shared" si="44"/>
         <v>0.33</v>
       </c>
-      <c r="AG19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
-      </c>
-      <c r="AH19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
-      </c>
-      <c r="AI19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
-      </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
+        <f t="shared" si="44"/>
+        <v>0.34</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
+        <f t="shared" si="44"/>
+        <v>0.34</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
+        <f t="shared" si="44"/>
+        <v>0.34</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
+        <f t="shared" si="44"/>
+        <v>0.34</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" si="40"/>
-        <v>0.33</v>
-      </c>
-      <c r="AP19" t="s">
+        <f t="shared" si="44"/>
+        <v>0.34</v>
+      </c>
+      <c r="AO19" s="9">
+        <f t="shared" si="44"/>
+        <v>0.34</v>
+      </c>
+      <c r="AP19" s="9">
+        <f t="shared" si="44"/>
+        <v>0.34</v>
+      </c>
+      <c r="AQ19" s="9">
+        <f t="shared" si="44"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AR19" s="9">
+        <f t="shared" si="44"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AT19" t="s">
         <v>49</v>
       </c>
-      <c r="AQ19" s="9">
+      <c r="AU19" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="20" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>44</v>
       </c>
@@ -3574,39 +3688,39 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:O20" si="41">G6/C6-1</f>
+        <f t="shared" ref="G20:O20" si="45">G6/C6-1</f>
         <v>0.27551020408163263</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.31764705882352939</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.85576923076923084</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.64031620553359692</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.74</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.34821428571428581</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>-4.4041450777202118E-2</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.12771084337349392</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>-0.10574712643678164</v>
       </c>
       <c r="P20" s="9">
@@ -3614,155 +3728,171 @@
         <v>-0.16335540838852092</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20:R20" si="42">Q6/M6-1</f>
+        <f t="shared" ref="Q20:R20" si="46">Q6/M6-1</f>
         <v>-7.3170731707317027E-2</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>-0.19658119658119655</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20" si="43">S6/O6-1</f>
+        <f t="shared" ref="S20" si="47">S6/O6-1</f>
         <v>-2.5706940874036022E-2</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="44">T6/P6-1</f>
+        <f t="shared" ref="T20" si="48">T6/P6-1</f>
         <v>9.4986807387862804E-2</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="45">U6/Q6-1</f>
+        <f t="shared" ref="U20" si="49">U6/Q6-1</f>
         <v>-9.6491228070175405E-2</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20" si="46">V6/R6-1</f>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9" t="e">
-        <f>Y6/X6-1</f>
+        <f t="shared" ref="V20" si="50">V6/R6-1</f>
+        <v>-0.22872340425531912</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" ref="W20" si="51">W6/S6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" ref="X20" si="52">X6/T6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" ref="Y20" si="53">Y6/U6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" ref="Z20" si="54">Z6/V6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9" t="e">
+        <f>AC6/AB6-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z20" s="9" t="e">
-        <f t="shared" ref="Z20:AN20" si="47">Z6/Y6-1</f>
+      <c r="AD20" s="9" t="e">
+        <f t="shared" ref="AD20:AR20" si="55">AD6/AC6-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AE20" s="9">
+        <f t="shared" si="55"/>
         <v>0.52083333333333326</v>
       </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AF20" s="9">
+        <f t="shared" si="55"/>
         <v>0.24369142033165114</v>
       </c>
-      <c r="AC20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AG20" s="9">
+        <f t="shared" si="55"/>
         <v>-0.13855072463768114</v>
       </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="47"/>
-        <v>2.5652759084791477E-2</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AH20" s="9">
+        <f t="shared" si="55"/>
+        <v>-6.2584118438761771E-2</v>
+      </c>
+      <c r="AI20" s="9">
+        <f t="shared" si="55"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AJ20" s="9">
+        <f t="shared" si="55"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AK20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AL20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AM20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AN20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AO20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AP20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AM20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AQ20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AN20" s="9">
-        <f t="shared" si="47"/>
+      <c r="AR20" s="9">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AP20" t="s">
+      <c r="AT20" t="s">
         <v>50</v>
       </c>
-      <c r="AQ20" s="9">
+      <c r="AU20" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:O21" si="48">C7/C3</f>
+        <f t="shared" ref="C21:O21" si="56">C7/C3</f>
         <v>0.10992081974848626</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.11969111969111969</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.11195521791283487</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.12644105615470436</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.11123637730176625</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.13652234636871508</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.14229249011857709</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.14308275426405559</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.11406969099276791</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.12559017941454201</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.10574918081620495</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.1176791065104876</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>8.9108910891089105E-2</v>
       </c>
       <c r="P21" s="9">
@@ -3770,106 +3900,122 @@
         <v>9.0097189387969526E-2</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" ref="Q21:R21" si="49">Q7/Q3</f>
+        <f t="shared" ref="Q21:R21" si="57">Q7/Q3</f>
         <v>8.3249749247743227E-2</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>9.2644978783592638E-2</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="50">S7/S3</f>
+        <f t="shared" ref="S21:V21" si="58">S7/S3</f>
         <v>7.494033412887828E-2</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>8.681135225375626E-2</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>8.1694756554307121E-2</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="50"/>
-        <v>0.09</v>
-      </c>
-      <c r="X21" s="9" t="e">
-        <f t="shared" ref="X21:AN21" si="51">X7/X3</f>
+        <f t="shared" si="58"/>
+        <v>8.8060030898256453E-2</v>
+      </c>
+      <c r="W21" s="9">
+        <f t="shared" ref="W21:Z21" si="59">W7/W3</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="9" t="e">
+        <f t="shared" ref="AB21:AR21" si="60">AB7/AB3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y21" s="9" t="e">
-        <f t="shared" si="51"/>
+      <c r="AC21" s="9" t="e">
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="51"/>
+      <c r="AD21" s="9">
+        <f t="shared" si="60"/>
         <v>0.11739760033098882</v>
       </c>
-      <c r="AA21" s="9">
-        <f t="shared" si="51"/>
+      <c r="AE21" s="9">
+        <f t="shared" si="60"/>
         <v>0.13404962906114096</v>
       </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="51"/>
+      <c r="AF21" s="9">
+        <f t="shared" si="60"/>
         <v>0.11572431493923152</v>
       </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="51"/>
+      <c r="AG21" s="9">
+        <f t="shared" si="60"/>
         <v>8.88151598290053E-2</v>
       </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="51"/>
-        <v>8.347288170377902E-2</v>
-      </c>
-      <c r="AE21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
-      </c>
-      <c r="AF21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
-      </c>
-      <c r="AG21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
-      </c>
       <c r="AH21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
+        <f t="shared" si="60"/>
+        <v>8.2974514139415798E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
+        <f t="shared" si="60"/>
+        <v>0.08</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
+        <f t="shared" si="60"/>
+        <v>0.08</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
+        <f t="shared" si="60"/>
+        <v>0.08</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
+        <f t="shared" si="60"/>
+        <v>0.08</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="51"/>
-        <v>9.0000000000000011E-2</v>
+        <f t="shared" si="60"/>
+        <v>0.08</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="51"/>
-        <v>0.09</v>
-      </c>
-      <c r="AP21" t="s">
+        <f t="shared" si="60"/>
+        <v>0.08</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" si="60"/>
+        <v>0.08</v>
+      </c>
+      <c r="AP21" s="9">
+        <f t="shared" si="60"/>
+        <v>0.08</v>
+      </c>
+      <c r="AQ21" s="9">
+        <f t="shared" si="60"/>
+        <v>0.08</v>
+      </c>
+      <c r="AR21" s="9">
+        <f t="shared" si="60"/>
+        <v>0.08</v>
+      </c>
+      <c r="AT21" t="s">
         <v>51</v>
       </c>
-      <c r="AQ21" s="2">
-        <f>NPV(AQ20,AC14:ES14)</f>
-        <v>28493.182006877181</v>
+      <c r="AU21" s="2">
+        <f>NPV(AU20,AI14:EW14)</f>
+        <v>39086.370568886043</v>
       </c>
     </row>
-    <row r="22" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>46</v>
       </c>
@@ -3878,39 +4024,39 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:O22" si="52">G8/C8-1</f>
+        <f t="shared" ref="G22:O22" si="61">G8/C8-1</f>
         <v>0.28431372549019618</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>0.46153846153846145</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>0.52380952380952372</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>0.30158730158730163</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>6.8702290076335881E-2</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-5.8479532163742687E-2</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-0.19374999999999998</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-5.4878048780487854E-2</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="61"/>
         <v>-0.12142857142857144</v>
       </c>
       <c r="P22" s="9">
@@ -3918,156 +4064,172 @@
         <v>-0.22981366459627328</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22:R22" si="53">Q8/M8-1</f>
+        <f t="shared" ref="Q22:R22" si="62">Q8/M8-1</f>
         <v>-0.13178294573643412</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>-0.2129032258064516</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="54">S8/O8-1</f>
+        <f t="shared" ref="S22" si="63">S8/O8-1</f>
         <v>8.1300813008129413E-3</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="55">T8/P8-1</f>
+        <f t="shared" ref="T22" si="64">T8/P8-1</f>
         <v>8.870967741935476E-2</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="56">U8/Q8-1</f>
+        <f t="shared" ref="U22" si="65">U8/Q8-1</f>
         <v>-8.9285714285713969E-3</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="57">V8/R8-1</f>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9" t="e">
-        <f>Y8/X8-1</f>
+        <f t="shared" ref="V22" si="66">V8/R8-1</f>
+        <v>-0.10655737704918034</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" ref="W22" si="67">W8/S8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" ref="X22" si="68">X8/T8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" ref="Y22" si="69">Y8/U8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22" si="70">Z8/V8-1</f>
+        <v>-1</v>
+      </c>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9" t="e">
+        <f>AC8/AB8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z22" s="9" t="e">
-        <f t="shared" ref="Z22:AN22" si="58">Z8/Y8-1</f>
+      <c r="AD22" s="9" t="e">
+        <f t="shared" ref="AD22:AR22" si="71">AD8/AC8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AE22" s="9">
+        <f t="shared" si="71"/>
         <v>0.39111111111111119</v>
       </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AF22" s="9">
+        <f t="shared" si="71"/>
         <v>-6.5495207667731647E-2</v>
       </c>
-      <c r="AC22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AG22" s="9">
+        <f t="shared" si="71"/>
         <v>-0.17777777777777781</v>
       </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="58"/>
-        <v>5.8378378378378448E-2</v>
-      </c>
-      <c r="AE22" s="9">
-        <f t="shared" si="58"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AH22" s="9">
+        <f t="shared" si="71"/>
+        <v>-4.1580041580041582E-3</v>
+      </c>
+      <c r="AI22" s="9">
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AJ22" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AK22" s="9">
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AL22" s="9">
+        <f t="shared" si="71"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AM22" s="9">
+        <f t="shared" si="71"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AN22" s="9">
+        <f t="shared" si="71"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AO22" s="9">
+        <f t="shared" si="71"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AP22" s="9">
+        <f t="shared" si="71"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AQ22" s="9">
+        <f t="shared" si="71"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN22" s="9">
-        <f t="shared" si="58"/>
+      <c r="AR22" s="9">
+        <f t="shared" si="71"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP22" t="s">
+      <c r="AT22" t="s">
         <v>52</v>
       </c>
-      <c r="AQ22" s="2">
+      <c r="AU22" s="2">
         <f>Main!D8</f>
-        <v>10270</v>
+        <v>10190</v>
       </c>
     </row>
-    <row r="23" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:O23" si="59">C9/C3</f>
+        <f t="shared" ref="C23:O23" si="72">C9/C3</f>
         <v>6.5207265952491851E-3</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>5.1480051480051478E-3</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>2.9988004798080767E-2</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-2.6031982149497955E-3</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-2.2547914317925591E-3</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-6.773743016759777E-2</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-7.5098814229249009E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-7.2962728995578013E-2</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-5.128205128205128E-2</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-7.7746301542335541E-2</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>9.5323205242776286E-3</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>-2.0430400435848543E-2</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="72"/>
         <v>4.6204620462046202E-2</v>
       </c>
       <c r="P23" s="9">
@@ -4075,159 +4237,175 @@
         <v>6.9871289729445757E-2</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" ref="Q23:R23" si="60">Q9/Q3</f>
+        <f t="shared" ref="Q23:R23" si="73">Q9/Q3</f>
         <v>0.11384152457372117</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="73"/>
         <v>0.11244695898161244</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="61">S9/S3</f>
+        <f t="shared" ref="S23:V23" si="74">S9/S3</f>
         <v>0.12147971360381861</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="74"/>
         <v>9.6828046744574292E-2</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="74"/>
         <v>0.13623595505617977</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="61"/>
-        <v>0.10541476519619618</v>
-      </c>
-      <c r="X23" s="9" t="e">
-        <f t="shared" ref="X23:AN23" si="62">X9/X3</f>
+        <f t="shared" si="74"/>
+        <v>0.1547119841094681</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" ref="W23:Z23" si="75">W9/W3</f>
+        <v>0</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="9" t="e">
+        <f t="shared" ref="AB23:AR23" si="76">AB9/AB3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y23" s="9" t="e">
-        <f t="shared" si="62"/>
+      <c r="AC23" s="9" t="e">
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="62"/>
+      <c r="AD23" s="9">
+        <f t="shared" si="76"/>
         <v>9.722796855606123E-3</v>
       </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="62"/>
+      <c r="AE23" s="9">
+        <f t="shared" si="76"/>
         <v>-5.6195105312526646E-2</v>
       </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="62"/>
+      <c r="AF23" s="9">
+        <f t="shared" si="76"/>
         <v>-3.3668000301955159E-2</v>
       </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="62"/>
+      <c r="AG23" s="9">
+        <f t="shared" si="76"/>
         <v>8.7092451987494421E-2</v>
       </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.11491690532384297</v>
-      </c>
-      <c r="AE23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.11450282251761297</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.12777161055956734</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.13097813597215119</v>
-      </c>
       <c r="AH23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.13307471028037907</v>
+        <f t="shared" si="76"/>
+        <v>0.12789479809146981</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.1343746145486579</v>
+        <f t="shared" si="76"/>
+        <v>0.14346999114119513</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.13565681499570395</v>
+        <f t="shared" si="76"/>
+        <v>0.15674030236681041</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.13692158220990666</v>
+        <f t="shared" si="76"/>
+        <v>0.15969057944204443</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.13816918223595029</v>
+        <f t="shared" si="76"/>
+        <v>0.16161960676046663</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.13939987665614353</v>
+        <f t="shared" si="76"/>
+        <v>0.16281564141961302</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="62"/>
-        <v>0.14061392267023703</v>
-      </c>
-      <c r="AP23" t="s">
+        <f t="shared" si="76"/>
+        <v>0.1639953867090547</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" si="76"/>
+        <v>0.16515909160097758</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="76"/>
+        <v>0.16630700088680925</v>
+      </c>
+      <c r="AQ23" s="9">
+        <f t="shared" si="76"/>
+        <v>0.16743935525205228</v>
+      </c>
+      <c r="AR23" s="9">
+        <f t="shared" si="76"/>
+        <v>0.16855639134972689</v>
+      </c>
+      <c r="AT23" t="s">
         <v>53</v>
       </c>
-      <c r="AQ23" s="2">
-        <f>AQ21+AQ22</f>
-        <v>38763.182006877178</v>
+      <c r="AU23" s="2">
+        <f>AU21+AU22</f>
+        <v>49276.370568886043</v>
       </c>
     </row>
-    <row r="24" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:O24" si="63">C13/C12</f>
+        <f t="shared" ref="C24:O24" si="77">C13/C12</f>
         <v>0.73563218390804597</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>3.5</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>0.98765432098765427</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>-3.875</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>0.15483870967741936</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>-0.3888888888888889</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>-0.15277777777777779</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>7.2164948453608241E-2</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>-9.2233009708737865E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>-0.25311203319502074</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>0.1095890410958904</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>0.46564885496183206</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="77"/>
         <v>-0.13218390804597702</v>
       </c>
       <c r="P24" s="9">
@@ -4235,159 +4413,175 @@
         <v>-1.4814814814814815E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:R24" si="64">Q13/Q12</f>
+        <f t="shared" ref="Q24:R24" si="78">Q13/Q12</f>
         <v>0.24623115577889448</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="78"/>
         <v>0.26452905811623245</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:V24" si="65">S13/S12</f>
+        <f t="shared" ref="S24:V24" si="79">S13/S12</f>
         <v>0.31402439024390244</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="79"/>
         <v>2.7916666666666665</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="79"/>
         <v>-8.7061668681983076E-2</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="79"/>
+        <v>-0.14985308521057786</v>
+      </c>
+      <c r="W24" s="9" t="e">
+        <f t="shared" ref="W24:Z24" si="80">W13/W12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X24" s="9" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y24" s="9" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z24" s="9" t="e">
+        <f t="shared" si="80"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB24" s="9" t="e">
+        <f t="shared" ref="AB24:AR24" si="81">AB13/AB12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC24" s="9" t="e">
+        <f t="shared" si="81"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="81"/>
+        <v>1.1365461847389557</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="81"/>
+        <v>-0.16216216216216217</v>
+      </c>
+      <c r="AF24" s="9">
+        <f t="shared" si="81"/>
+        <v>-5.3465346534653464E-2</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="81"/>
+        <v>0.15137956748695003</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="81"/>
+        <v>5.3956834532374104E-3</v>
+      </c>
+      <c r="AI24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="X24" s="9" t="e">
-        <f t="shared" ref="X24:AN24" si="66">X13/X12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y24" s="9" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="66"/>
-        <v>1.1365461847389557</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="66"/>
-        <v>-0.16216216216216217</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="66"/>
-        <v>-5.3465346534653464E-2</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.15137956748695003</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.17012072685607665</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AJ24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AK24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AL24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AM24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AN24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AO24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AK24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AP24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AQ24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="66"/>
+      <c r="AR24" s="9">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="66"/>
-        <v>0.25</v>
-      </c>
-      <c r="AP24" t="s">
+      <c r="AT24" t="s">
         <v>58</v>
       </c>
-      <c r="AQ24" s="2">
-        <f>AQ23/Main!D15</f>
-        <v>44555.381617100204</v>
+      <c r="AU24" s="2">
+        <f>AU23/Main!D15</f>
+        <v>56639.506401018443</v>
       </c>
     </row>
-    <row r="25" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>48</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:O25" si="67">C14/C3</f>
+        <f t="shared" ref="C25:O25" si="82">C14/C3</f>
         <v>1.0712622263623661E-2</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-8.5800085800085794E-3</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>7.9968012794882047E-4</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-1.4503532911863145E-2</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>4.9229612927470877E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-4.3645251396648044E-2</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-5.4677206851119896E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-8.5281111813013261E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-7.3964497041420121E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-9.5058231035568153E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>1.9362526064938934E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>-1.9068373740125308E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="82"/>
         <v>5.4180418041804179E-2</v>
       </c>
       <c r="P25" s="9">
@@ -4395,129 +4589,145 @@
         <v>7.1972681901759913E-2</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25:R25" si="68">Q14/Q3</f>
+        <f t="shared" ref="Q25:R25" si="83">Q14/Q3</f>
         <v>7.5225677031093285E-2</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="83"/>
         <v>8.651579443658651E-2</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="69">S14/S3</f>
+        <f t="shared" ref="S25:V25" si="84">S14/S3</f>
         <v>5.3699284009546537E-2</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="84"/>
         <v>-2.0510374433579774E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="84"/>
         <v>0.21044007490636704</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="69"/>
-        <v>8.2803968402231046E-2</v>
-      </c>
-      <c r="X25" s="9" t="e">
-        <f t="shared" ref="X25:AN25" si="70">X14/X3</f>
+        <f t="shared" si="84"/>
+        <v>0.25910395056278968</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" ref="W25:Z25" si="85">W14/W3</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="9" t="e">
+        <f t="shared" ref="AB25:AR25" si="86">AB14/AB3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y25" s="9" t="e">
-        <f t="shared" si="70"/>
+      <c r="AC25" s="9" t="e">
+        <f t="shared" si="86"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="70"/>
+      <c r="AD25" s="9">
+        <f t="shared" si="86"/>
         <v>-3.5167563094745551E-3</v>
       </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="70"/>
+      <c r="AE25" s="9">
+        <f t="shared" si="86"/>
         <v>-3.6667519399675962E-2</v>
       </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="70"/>
+      <c r="AF25" s="9">
+        <f t="shared" si="86"/>
         <v>-4.0160036234619161E-2</v>
       </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="70"/>
+      <c r="AG25" s="9">
+        <f t="shared" si="86"/>
         <v>7.2608945319977025E-2</v>
       </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="70"/>
-        <v>8.2227680112316529E-2</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" si="70"/>
-        <v>7.5119039284733763E-2</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="70"/>
-        <v>8.6016126273591953E-2</v>
-      </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="70"/>
-        <v>8.9224528824939989E-2</v>
-      </c>
       <c r="AH25" s="9">
-        <f t="shared" si="70"/>
-        <v>9.1482400833160907E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.12870941463982311</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="70"/>
-        <v>9.3044517121147668E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.10892308610045286</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="70"/>
-        <v>9.4581953832786947E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.11904698504373543</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="70"/>
-        <v>9.6095135301806286E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.12143187478631157</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="70"/>
-        <v>9.7584478155271992E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.12305745579542481</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="70"/>
-        <v>9.9050391458059925E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.12414550901774184</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="70"/>
-        <v>0.10049327685457125</v>
-      </c>
-      <c r="AP25" t="s">
+        <f t="shared" si="86"/>
+        <v>0.12521763594621804</v>
+      </c>
+      <c r="AO25" s="9">
+        <f t="shared" si="86"/>
+        <v>0.12627409533458633</v>
+      </c>
+      <c r="AP25" s="9">
+        <f t="shared" si="86"/>
+        <v>0.12731514140247502</v>
+      </c>
+      <c r="AQ25" s="9">
+        <f t="shared" si="86"/>
+        <v>0.12834102391868896</v>
+      </c>
+      <c r="AR25" s="9">
+        <f t="shared" si="86"/>
+        <v>0.12935198828292008</v>
+      </c>
+      <c r="AT25" t="s">
         <v>54</v>
       </c>
-      <c r="AQ25" s="3">
-        <f>AQ24/AN15</f>
-        <v>216.28826027718546</v>
+      <c r="AU25" s="3">
+        <f>AU24/AR15</f>
+        <v>275.21626045198462</v>
       </c>
     </row>
-    <row r="26" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP26" t="s">
+    <row r="26" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="AT26" t="s">
         <v>55</v>
       </c>
-      <c r="AQ26" s="3">
+      <c r="AU26" s="3">
         <f>Main!D3</f>
-        <v>510.47</v>
+        <v>458.34</v>
       </c>
     </row>
-    <row r="27" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP27" s="1" t="s">
+    <row r="27" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="AT27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AQ27" s="10">
-        <f>AQ25/AQ26-1</f>
-        <v>-0.57629584446258264</v>
+      <c r="AU27" s="10">
+        <f>AU25/AU26-1</f>
+        <v>-0.39953689302268047</v>
       </c>
     </row>
-    <row r="28" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP28" t="s">
+    <row r="28" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="AT28" t="s">
         <v>57</v>
       </c>
-      <c r="AQ28" s="6" t="s">
-        <v>63</v>
+      <c r="AU28" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
